--- a/Planilha de controle de segurança do trabalho.xlsx
+++ b/Planilha de controle de segurança do trabalho.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://enopsengenharia.sharepoint.com/sites/sabespIntegra6a/Documentos Compartilhados/04 QSMS/03. SESMT/01 - NR 02 INSPEÇÃO/20- INSPEÇÕES DE SEGURANÇA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3063" documentId="13_ncr:1_{95D3C810-1CBF-4943-A4BA-161B382C5A82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D84F6185-945C-4B55-B6E8-A8BF0E0702CA}"/>
+  <xr:revisionPtr revIDLastSave="3323" documentId="13_ncr:1_{95D3C810-1CBF-4943-A4BA-161B382C5A82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C229EBD0-F41C-4DB5-951F-656B2869D771}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="907" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="907" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inspeções" sheetId="6" r:id="rId1"/>
-    <sheet name="Planilha1" sheetId="10" r:id="rId2"/>
-    <sheet name="DDS" sheetId="9" r:id="rId3"/>
+    <sheet name="Modelo Check-list de Inspeção" sheetId="10" r:id="rId2"/>
+    <sheet name="Indicador Pro-ativo" sheetId="9" r:id="rId3"/>
     <sheet name="Listas" sheetId="2" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">DDS!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Inspeções!$A$1:$I$588</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">DDS!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Indicador Pro-ativo'!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Inspeções!$A$1:$I$600</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Indicador Pro-ativo'!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Inspeções!$A$1:$I$161</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3139" uniqueCount="971">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3240" uniqueCount="1009">
   <si>
     <t>DATA</t>
   </si>
@@ -3517,9 +3517,6 @@
     <t>D1. Impróprias para o serviço;</t>
   </si>
   <si>
-    <t>B7. Pés e pernas; B4</t>
-  </si>
-  <si>
     <t>Erosão no solo lateral ao PV com risco de desmoronamento.</t>
   </si>
   <si>
@@ -3535,9 +3532,6 @@
     <t>Gerador sem aterramento adequado, uso de tomada inapropriada e ligação improvisada.</t>
   </si>
   <si>
-    <t>D3.; A5</t>
-  </si>
-  <si>
     <t>Corda do sistema de resgate 4x4 danificada (cortes na estrutura).</t>
   </si>
   <si>
@@ -3565,12 +3559,6 @@
     <t>Ausência de retrovisor, sirene de ré inoperante, extintor ausente, para-brisa trincado.</t>
   </si>
   <si>
-    <t>A1.Bater contra / Ser atingidor por; G2</t>
-  </si>
-  <si>
-    <t>A3.Risco de Queda; D3</t>
-  </si>
-  <si>
     <t>A2.Ficar Preso / Soterramento</t>
   </si>
   <si>
@@ -3580,20 +3568,147 @@
     <t>D3.Em condições inseguras;</t>
   </si>
   <si>
-    <t>D3.Em condições inseguras; e1</t>
-  </si>
-  <si>
     <t>D1.Improprias para o serviço;</t>
   </si>
   <si>
     <t>E1.Retroescavadeira / Caminhão em condições inadequadas; E2. Condições Inseguras (Materiais em solo instável/sem travamento)</t>
+  </si>
+  <si>
+    <t>B7. Pés e pernas; B4.Ouvidos</t>
+  </si>
+  <si>
+    <t>D3.Em condições inseguras; E1. Retroescavadeira / Caminhão em condições inadequadas</t>
+  </si>
+  <si>
+    <t>D3.Em condições inseguras; A5.Risco de Choque Elétrico</t>
+  </si>
+  <si>
+    <t>A1.Bater contra / Ser atingidor por; G2.Local desorganizado</t>
+  </si>
+  <si>
+    <t>A3.Risco de Queda; D3.Em condições inseguras</t>
+  </si>
+  <si>
+    <t>JANEIRO</t>
+  </si>
+  <si>
+    <t>FEVEREIRO</t>
+  </si>
+  <si>
+    <t>MARÇO</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>MAIO</t>
+  </si>
+  <si>
+    <t>JUNHO</t>
+  </si>
+  <si>
+    <t>JULHO</t>
+  </si>
+  <si>
+    <t>AGOSTO</t>
+  </si>
+  <si>
+    <t>SETEMBRO</t>
+  </si>
+  <si>
+    <t>OUTUBRO</t>
+  </si>
+  <si>
+    <t>NOVEMBRO</t>
+  </si>
+  <si>
+    <t>DEZEMBRO</t>
+  </si>
+  <si>
+    <t>MÊS</t>
+  </si>
+  <si>
+    <t>QUANTIDADE
+DDS</t>
+  </si>
+  <si>
+    <t>QUANTIDADE CAMPANHAS</t>
+  </si>
+  <si>
+    <t>Indicadores Pró-Ativo - 2026</t>
+  </si>
+  <si>
+    <t>CT Rauzito</t>
+  </si>
+  <si>
+    <t>Material escavado próximo à vala (&lt; 1m) e Local sem isolamento</t>
+  </si>
+  <si>
+    <t>C1. Sem isolamento ou Insuficiente (Ex: falta de tapumes/grades na vala); G4.Resíduos dispostos incorretamente (Ex: Solo escavado depositado na borda da vala)</t>
+  </si>
+  <si>
+    <t>Rogério Gonçalves</t>
+  </si>
+  <si>
+    <t>Sem aterramento (bomba de concreto), sem parada de emergência, sem extintor e sem identificação de operadores.</t>
+  </si>
+  <si>
+    <t>A5, E1, D3</t>
+  </si>
+  <si>
+    <t>CR ITI15</t>
+  </si>
+  <si>
+    <t>Guarda-corpo deficiente, ajudante sem talabarte, ausência de Plano de Rigging.</t>
+  </si>
+  <si>
+    <t>D3, E4, F2</t>
+  </si>
+  <si>
+    <t>Concha da retroescavadeira sem ponto de içamento certificado.</t>
+  </si>
+  <si>
+    <t>Falta de maca e mochila de resgate em PVs específicos (PV-5 e PV-6).</t>
+  </si>
+  <si>
+    <t>Pendências documentais, sem crachá, sem cinto, sem trava-quedas, sem detector de gases, sem área de vivência.</t>
+  </si>
+  <si>
+    <t>D3, F2, G2</t>
+  </si>
+  <si>
+    <t>Tubos sem amarração, falta de rota de pedestres, ausência de placas de EPI, escada sem fita antiderrapante, falta de extintores.</t>
+  </si>
+  <si>
+    <t>C5, C7, G3, G4</t>
+  </si>
+  <si>
+    <t>Escada sem fixação, extintor despressurizado, placa de sinalização ausente.</t>
+  </si>
+  <si>
+    <t>D3, E1</t>
+  </si>
+  <si>
+    <t>Colaborador da empresa MR Locações sem integração obrigatória e sem cadastro no sistema Wehandler</t>
+  </si>
+  <si>
+    <t>Curto-circuito e princípio de incêndio em bomba de rebaixamento.</t>
+  </si>
+  <si>
+    <t>Lanterna dianteira e luz de freio traseira inoperantes em caminhão Vacal, falhas intermitentes no sistema de freios.</t>
+  </si>
+  <si>
+    <t>Ausência de vigia durante atividade executada por equipe da empresa LVL.</t>
+  </si>
+  <si>
+    <t>Atividade executada sem o devido isolamento e sinalização da área, em desacordo com a NR 18.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3714,8 +3829,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3749,6 +3877,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4011,7 +4145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4194,6 +4328,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4208,90 +4355,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4317,222 +4380,98 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
+  <dxfs count="33">
     <dxf>
       <font>
         <b val="0"/>
@@ -4885,6 +4824,355 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
       <border>
         <top style="thin">
           <color indexed="64"/>
@@ -4981,8 +5269,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFCFEAFD"/>
       <color rgb="FF99CCFF"/>
-      <color rgb="FFCFEAFD"/>
       <color rgb="FF00A5E4"/>
       <color rgb="FFFDE9D9"/>
       <color rgb="FF004994"/>
@@ -6225,28 +6513,40 @@
 <file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
 <namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <namedSheetView name="Exibição 1" id="{7E18E321-69E3-48FD-94EA-92056B8EA073}">
-    <nsvFilter filterId="{E025FF00-BBD4-447E-8A48-23C9F77BFED5}" ref="A1:I588" tableId="5"/>
+    <nsvFilter filterId="{E025FF00-BBD4-447E-8A48-23C9F77BFED5}" ref="A1:I600" tableId="5"/>
   </namedSheetView>
 </namedSheetViews>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{40B8F08B-7B44-41C0-9727-D6D3A9E412E0}" name="Tabela5" displayName="Tabela5" ref="A1:I589" totalsRowCount="1" headerRowDxfId="22" totalsRowDxfId="19" headerRowBorderDxfId="21" tableBorderDxfId="20" totalsRowBorderDxfId="18">
-  <autoFilter ref="A1:I588" xr:uid="{E025FF00-BBD4-447E-8A48-23C9F77BFED5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{40B8F08B-7B44-41C0-9727-D6D3A9E412E0}" name="Tabela5" displayName="Tabela5" ref="A1:I601" totalsRowCount="1" headerRowDxfId="32" totalsRowDxfId="29" headerRowBorderDxfId="31" tableBorderDxfId="30" totalsRowBorderDxfId="28">
+  <autoFilter ref="A1:I600" xr:uid="{E025FF00-BBD4-447E-8A48-23C9F77BFED5}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{0B057C41-AC10-4F67-ABDF-C4EAAD7F8F2D}" name="DATA" totalsRowLabel="Total" dataDxfId="8" totalsRowDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{8A16FC14-C82C-43F3-BF15-DD9697EAFA57}" name="LOCAL" totalsRowFunction="count" dataDxfId="7" totalsRowDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{BE44A91D-706C-471A-8BDF-D29BE353B2BC}" name="ENCARREGADO OU LIDER DE EQUIPE" totalsRowFunction="count" dataDxfId="6" totalsRowDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{00DF3209-2326-42C6-8699-CDCB435BB747}" name="QUANTIDADE DESVIOS" totalsRowFunction="custom" dataDxfId="5" totalsRowDxfId="14">
-      <totalsRowFormula>SUM(D2:D588)</totalsRowFormula>
+    <tableColumn id="1" xr3:uid="{0B057C41-AC10-4F67-ABDF-C4EAAD7F8F2D}" name="DATA" totalsRowLabel="Total" dataDxfId="27" totalsRowDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{8A16FC14-C82C-43F3-BF15-DD9697EAFA57}" name="LOCAL" totalsRowFunction="count" dataDxfId="26" totalsRowDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{BE44A91D-706C-471A-8BDF-D29BE353B2BC}" name="ENCARREGADO OU LIDER DE EQUIPE" totalsRowFunction="count" dataDxfId="25" totalsRowDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{00DF3209-2326-42C6-8699-CDCB435BB747}" name="QUANTIDADE DESVIOS" totalsRowFunction="custom" dataDxfId="24" totalsRowDxfId="5">
+      <totalsRowFormula>SUM(D2:D600)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{30D85C45-EA9B-41E7-AB22-9C5FACAC4A3A}" name="DESCRIÇÃO" totalsRowFunction="count" dataDxfId="4" totalsRowDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{AFDBCEF9-AD84-4AF6-A78C-ADD27299479E}" name="STATUS" dataDxfId="3" totalsRowDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{F60BA8D5-B8CC-4468-B665-77CD1CD38176}" name="CLASSIFICAÇÃO" totalsRowFunction="count" dataDxfId="2" totalsRowDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{EE5A703F-BAA2-4AAB-A2E6-C2D3F12BF651}" name="QUANTIDADE INSPEÇÕES" totalsRowFunction="sum" dataDxfId="1" totalsRowDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{6AC59D75-1383-42D7-8A9B-B4B44FEEFFC1}" name="TÉCNICO DE SEGURANÇA  APLICADOR" totalsRowFunction="count" dataDxfId="0" totalsRowDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{30D85C45-EA9B-41E7-AB22-9C5FACAC4A3A}" name="DESCRIÇÃO" totalsRowFunction="count" dataDxfId="23" totalsRowDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{AFDBCEF9-AD84-4AF6-A78C-ADD27299479E}" name="STATUS" dataDxfId="22" totalsRowDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{F60BA8D5-B8CC-4468-B665-77CD1CD38176}" name="CLASSIFICAÇÃO" totalsRowFunction="count" dataDxfId="21" totalsRowDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{EE5A703F-BAA2-4AAB-A2E6-C2D3F12BF651}" name="QUANTIDADE INSPEÇÕES" totalsRowFunction="sum" dataDxfId="20" totalsRowDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{6AC59D75-1383-42D7-8A9B-B4B44FEEFFC1}" name="TÉCNICO DE SEGURANÇA  APLICADOR" totalsRowFunction="count" dataDxfId="19" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{952762BD-56C9-484C-9E77-FCE66DB4640E}" name="Tabela1" displayName="Tabela1" ref="A2:C15" totalsRowCount="1" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16" totalsRowBorderDxfId="15">
+  <autoFilter ref="A2:C14" xr:uid="{952762BD-56C9-484C-9E77-FCE66DB4640E}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{41C10721-F7E4-4BCF-A498-D3EC0835BFEA}" name="MÊS" totalsRowLabel="Total" dataDxfId="14" totalsRowDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{0FEB78B2-7C7C-418B-BF73-42BE97E3E034}" name="QUANTIDADE_x000a_DDS" totalsRowFunction="sum" dataDxfId="12" totalsRowDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{7B989E42-8D41-444B-9D85-834753A5661B}" name="QUANTIDADE CAMPANHAS" totalsRowFunction="sum" dataDxfId="10" totalsRowDxfId="9"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -6609,7 +6909,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E025FF00-BBD4-447E-8A48-23C9F77BFED5}">
-  <dimension ref="A1:X589"/>
+  <dimension ref="A1:X601"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.88671875" style="16" customWidth="1"/>
@@ -6667,22 +6967,22 @@
       <c r="I1" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="68" t="s">
+      <c r="K1" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="69"/>
-      <c r="M1" s="69"/>
-      <c r="N1" s="69"/>
-      <c r="O1" s="69"/>
-      <c r="P1" s="69"/>
-      <c r="Q1" s="69"/>
-      <c r="R1" s="69"/>
-      <c r="S1" s="69"/>
-      <c r="T1" s="69"/>
-      <c r="U1" s="69"/>
-      <c r="V1" s="69"/>
-      <c r="W1" s="69"/>
-      <c r="X1" s="70"/>
+      <c r="L1" s="74"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="74"/>
+      <c r="P1" s="74"/>
+      <c r="Q1" s="74"/>
+      <c r="R1" s="74"/>
+      <c r="S1" s="74"/>
+      <c r="T1" s="74"/>
+      <c r="U1" s="74"/>
+      <c r="V1" s="74"/>
+      <c r="W1" s="74"/>
+      <c r="X1" s="75"/>
     </row>
     <row r="2" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="17">
@@ -6712,34 +7012,34 @@
       <c r="I2" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="66" t="s">
+      <c r="K2" s="71" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="67"/>
-      <c r="M2" s="66" t="s">
+      <c r="L2" s="72"/>
+      <c r="M2" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="67"/>
-      <c r="O2" s="66" t="s">
+      <c r="N2" s="72"/>
+      <c r="O2" s="71" t="s">
         <v>616</v>
       </c>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="66" t="s">
+      <c r="P2" s="72"/>
+      <c r="Q2" s="71" t="s">
         <v>617</v>
       </c>
-      <c r="R2" s="67"/>
-      <c r="S2" s="66" t="s">
+      <c r="R2" s="72"/>
+      <c r="S2" s="71" t="s">
         <v>618</v>
       </c>
-      <c r="T2" s="67"/>
-      <c r="U2" s="66" t="s">
+      <c r="T2" s="72"/>
+      <c r="U2" s="71" t="s">
         <v>619</v>
       </c>
-      <c r="V2" s="67"/>
-      <c r="W2" s="66" t="s">
+      <c r="V2" s="72"/>
+      <c r="W2" s="71" t="s">
         <v>620</v>
       </c>
-      <c r="X2" s="67"/>
+      <c r="X2" s="72"/>
     </row>
     <row r="3" spans="1:24" ht="48" x14ac:dyDescent="0.3">
       <c r="A3" s="17">
@@ -7257,7 +7557,7 @@
       <c r="W10" s="35"/>
       <c r="X10" s="36"/>
     </row>
-    <row r="11" spans="1:24" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="17">
         <v>45798</v>
       </c>
@@ -7286,7 +7586,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="17">
         <v>45798</v>
       </c>
@@ -7315,7 +7615,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="17">
         <v>45800</v>
       </c>
@@ -7373,7 +7673,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15" s="17">
         <v>45804</v>
       </c>
@@ -7402,7 +7702,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" s="17">
         <v>45805</v>
       </c>
@@ -7431,7 +7731,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="17">
         <v>45818</v>
       </c>
@@ -7663,7 +7963,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="17">
         <v>45832</v>
       </c>
@@ -7692,7 +7992,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="17">
         <v>45833</v>
       </c>
@@ -7721,7 +8021,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="17">
         <v>45835</v>
       </c>
@@ -8040,7 +8340,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A38" s="17">
         <v>45890</v>
       </c>
@@ -8562,7 +8862,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A56" s="20">
         <v>45915</v>
       </c>
@@ -8707,7 +9007,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="20">
         <v>45921</v>
       </c>
@@ -8852,7 +9152,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="20">
         <v>45930</v>
       </c>
@@ -8881,7 +9181,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A67" s="20">
         <v>45930</v>
       </c>
@@ -9026,7 +9326,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A72" s="20">
         <v>45944</v>
       </c>
@@ -9142,7 +9442,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="20">
         <v>45951</v>
       </c>
@@ -9490,7 +9790,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A88" s="20">
         <v>46002</v>
       </c>
@@ -9780,7 +10080,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" s="20">
         <v>46009</v>
       </c>
@@ -9838,7 +10138,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A100" s="20">
         <v>46020</v>
       </c>
@@ -9983,7 +10283,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" s="20">
         <v>46029</v>
       </c>
@@ -10186,7 +10486,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" s="20">
         <v>46034</v>
       </c>
@@ -10621,7 +10921,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="127" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" s="20">
         <v>46043</v>
       </c>
@@ -10650,7 +10950,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" s="20">
         <v>46043</v>
       </c>
@@ -11549,7 +11849,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" s="20">
         <v>46085</v>
       </c>
@@ -12017,7 +12317,7 @@
       <c r="A175" s="20">
         <v>46113</v>
       </c>
-      <c r="B175" s="107" t="s">
+      <c r="B175" s="66" t="s">
         <v>247</v>
       </c>
       <c r="C175" s="21" t="s">
@@ -12071,7 +12371,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="177" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A177" s="20">
         <v>46114</v>
       </c>
@@ -12361,7 +12661,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="187" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" s="20">
         <v>46120</v>
       </c>
@@ -12448,7 +12748,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="190" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A190" s="20">
         <v>46121</v>
       </c>
@@ -12622,7 +12922,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="196" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" s="20">
         <v>46121</v>
       </c>
@@ -13202,7 +13502,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A216" s="17">
         <v>46126</v>
       </c>
@@ -13260,7 +13560,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="218" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218" s="17">
         <v>46126</v>
       </c>
@@ -13463,7 +13763,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="225" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A225" s="17">
         <v>46127</v>
       </c>
@@ -13695,7 +13995,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="233" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A233" s="17">
         <v>46130</v>
       </c>
@@ -13840,7 +14140,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="238" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A238" s="17">
         <v>46132</v>
       </c>
@@ -13869,7 +14169,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="239" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A239" s="17">
         <v>46132</v>
       </c>
@@ -14304,7 +14604,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="254" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A254" s="17">
         <v>46134</v>
       </c>
@@ -14362,7 +14662,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="256" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256" s="17">
         <v>46134</v>
       </c>
@@ -14884,7 +15184,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="274" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A274" s="17">
         <v>46137</v>
       </c>
@@ -14971,7 +15271,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="277" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A277" s="17">
         <v>46137</v>
       </c>
@@ -15087,7 +15387,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="281" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A281" s="20">
         <v>46139</v>
       </c>
@@ -15435,7 +15735,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="293" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A293" s="20">
         <v>46142</v>
       </c>
@@ -15580,7 +15880,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="298" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A298" s="20">
         <v>46143</v>
       </c>
@@ -15928,7 +16228,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="310" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A310" s="20">
         <v>46147</v>
       </c>
@@ -16392,7 +16692,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="326" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A326" s="20">
         <v>46153</v>
       </c>
@@ -16595,7 +16895,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="333" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A333" s="20">
         <v>46154</v>
       </c>
@@ -17523,7 +17823,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="365" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A365" s="20">
         <v>46162</v>
       </c>
@@ -18161,7 +18461,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="387" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A387" s="20">
         <v>46168</v>
       </c>
@@ -18219,7 +18519,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="389" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A389" s="20">
         <v>46168</v>
       </c>
@@ -18645,7 +18945,7 @@
         <v>861</v>
       </c>
       <c r="G403" s="24" t="s">
-        <v>947</v>
+        <v>966</v>
       </c>
       <c r="H403" s="18">
         <v>1</v>
@@ -18703,7 +19003,7 @@
         <v>861</v>
       </c>
       <c r="G405" s="24" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="H405" s="18">
         <v>1</v>
@@ -18712,7 +19012,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A406" s="20">
         <v>46176</v>
       </c>
@@ -18726,13 +19026,13 @@
         <v>2</v>
       </c>
       <c r="E406" s="24" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="F406" s="18" t="s">
         <v>861</v>
       </c>
       <c r="G406" s="24" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H406" s="18">
         <v>1</v>
@@ -18741,33 +19041,33 @@
         <v>500</v>
       </c>
     </row>
-    <row r="407" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A407" s="20">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="B407" s="18" t="s">
-        <v>408</v>
+        <v>91</v>
       </c>
       <c r="C407" s="18" t="s">
-        <v>155</v>
+        <v>10</v>
       </c>
       <c r="D407" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E407" s="24" t="s">
-        <v>878</v>
+        <v>1002</v>
       </c>
       <c r="F407" s="18" t="s">
-        <v>804</v>
+        <v>861</v>
       </c>
       <c r="G407" s="24" t="s">
-        <v>147</v>
+        <v>1003</v>
       </c>
       <c r="H407" s="18">
         <v>1</v>
       </c>
       <c r="I407" s="18" t="s">
-        <v>52</v>
+        <v>500</v>
       </c>
     </row>
     <row r="408" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -18775,16 +19075,16 @@
         <v>46177</v>
       </c>
       <c r="B408" s="18" t="s">
-        <v>879</v>
+        <v>408</v>
       </c>
       <c r="C408" s="18" t="s">
-        <v>74</v>
+        <v>155</v>
       </c>
       <c r="D408" s="18">
         <v>0</v>
       </c>
       <c r="E408" s="24" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="F408" s="18" t="s">
         <v>804</v>
@@ -18804,16 +19104,16 @@
         <v>46177</v>
       </c>
       <c r="B409" s="18" t="s">
-        <v>408</v>
+        <v>879</v>
       </c>
       <c r="C409" s="18" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="D409" s="18">
         <v>0</v>
       </c>
       <c r="E409" s="24" t="s">
-        <v>907</v>
+        <v>881</v>
       </c>
       <c r="F409" s="18" t="s">
         <v>804</v>
@@ -18825,30 +19125,30 @@
         <v>1</v>
       </c>
       <c r="I409" s="18" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="410" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A410" s="20">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="B410" s="18" t="s">
         <v>408</v>
       </c>
       <c r="C410" s="18" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D410" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E410" s="24" t="s">
-        <v>862</v>
+        <v>907</v>
       </c>
       <c r="F410" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G410" s="24" t="s">
-        <v>683</v>
+        <v>147</v>
       </c>
       <c r="H410" s="18">
         <v>1</v>
@@ -18857,21 +19157,21 @@
         <v>64</v>
       </c>
     </row>
-    <row r="411" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A411" s="20">
-        <v>46179</v>
+        <v>46178</v>
       </c>
       <c r="B411" s="18" t="s">
-        <v>91</v>
+        <v>408</v>
       </c>
       <c r="C411" s="18" t="s">
-        <v>10</v>
+        <v>113</v>
       </c>
       <c r="D411" s="18">
         <v>1</v>
       </c>
       <c r="E411" s="24" t="s">
-        <v>958</v>
+        <v>862</v>
       </c>
       <c r="F411" s="18" t="s">
         <v>861</v>
@@ -18883,36 +19183,36 @@
         <v>1</v>
       </c>
       <c r="I411" s="18" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="412" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="412" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A412" s="20">
         <v>46179</v>
       </c>
       <c r="B412" s="18" t="s">
-        <v>408</v>
+        <v>91</v>
       </c>
       <c r="C412" s="18" t="s">
-        <v>76</v>
+        <v>10</v>
       </c>
       <c r="D412" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E412" s="24" t="s">
-        <v>877</v>
+        <v>956</v>
       </c>
       <c r="F412" s="18" t="s">
-        <v>804</v>
+        <v>861</v>
       </c>
       <c r="G412" s="24" t="s">
-        <v>147</v>
+        <v>683</v>
       </c>
       <c r="H412" s="18">
         <v>1</v>
       </c>
       <c r="I412" s="18" t="s">
-        <v>52</v>
+        <v>500</v>
       </c>
     </row>
     <row r="413" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -18923,19 +19223,19 @@
         <v>408</v>
       </c>
       <c r="C413" s="18" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="D413" s="18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E413" s="24" t="s">
-        <v>871</v>
+        <v>877</v>
       </c>
       <c r="F413" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G413" s="24" t="s">
-        <v>872</v>
+        <v>147</v>
       </c>
       <c r="H413" s="18">
         <v>1</v>
@@ -18952,83 +19252,83 @@
         <v>408</v>
       </c>
       <c r="C414" s="18" t="s">
-        <v>193</v>
+        <v>113</v>
       </c>
       <c r="D414" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E414" s="24" t="s">
-        <v>884</v>
+        <v>871</v>
       </c>
       <c r="F414" s="18" t="s">
         <v>861</v>
       </c>
       <c r="G414" s="24" t="s">
-        <v>738</v>
+        <v>872</v>
       </c>
       <c r="H414" s="18">
         <v>1</v>
       </c>
       <c r="I414" s="18" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="415" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="415" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A415" s="20">
         <v>46179</v>
       </c>
       <c r="B415" s="18" t="s">
-        <v>247</v>
+        <v>408</v>
       </c>
       <c r="C415" s="18" t="s">
-        <v>113</v>
+        <v>193</v>
       </c>
       <c r="D415" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E415" s="24" t="s">
-        <v>903</v>
+        <v>884</v>
       </c>
       <c r="F415" s="18" t="s">
         <v>861</v>
       </c>
       <c r="G415" s="24" t="s">
-        <v>904</v>
+        <v>738</v>
       </c>
       <c r="H415" s="18">
         <v>1</v>
       </c>
       <c r="I415" s="18" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="416" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A416" s="20">
-        <v>46181</v>
+        <v>46179</v>
       </c>
       <c r="B416" s="18" t="s">
-        <v>412</v>
+        <v>247</v>
       </c>
       <c r="C416" s="18" t="s">
-        <v>311</v>
+        <v>113</v>
       </c>
       <c r="D416" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E416" s="24" t="s">
-        <v>945</v>
+        <v>903</v>
       </c>
       <c r="F416" s="18" t="s">
         <v>861</v>
       </c>
       <c r="G416" s="24" t="s">
-        <v>946</v>
+        <v>904</v>
       </c>
       <c r="H416" s="18">
         <v>1</v>
       </c>
       <c r="I416" s="18" t="s">
-        <v>500</v>
+        <v>115</v>
       </c>
     </row>
     <row r="417" spans="1:9" x14ac:dyDescent="0.3">
@@ -19036,57 +19336,57 @@
         <v>46181</v>
       </c>
       <c r="B417" s="18" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C417" s="18" t="s">
-        <v>113</v>
+        <v>311</v>
       </c>
       <c r="D417" s="18">
         <v>1</v>
       </c>
       <c r="E417" s="24" t="s">
-        <v>869</v>
+        <v>945</v>
       </c>
       <c r="F417" s="18" t="s">
         <v>861</v>
       </c>
       <c r="G417" s="24" t="s">
-        <v>870</v>
+        <v>946</v>
       </c>
       <c r="H417" s="18">
         <v>1</v>
       </c>
       <c r="I417" s="18" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="418" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="418" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A418" s="20">
         <v>46181</v>
       </c>
       <c r="B418" s="18" t="s">
-        <v>882</v>
+        <v>408</v>
       </c>
       <c r="C418" s="18" t="s">
-        <v>193</v>
+        <v>113</v>
       </c>
       <c r="D418" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E418" s="24" t="s">
-        <v>883</v>
+        <v>869</v>
       </c>
       <c r="F418" s="18" t="s">
-        <v>804</v>
+        <v>861</v>
       </c>
       <c r="G418" s="24" t="s">
-        <v>147</v>
+        <v>870</v>
       </c>
       <c r="H418" s="18">
         <v>1</v>
       </c>
       <c r="I418" s="18" t="s">
-        <v>500</v>
+        <v>52</v>
       </c>
     </row>
     <row r="419" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -19103,7 +19403,7 @@
         <v>0</v>
       </c>
       <c r="E419" s="24" t="s">
-        <v>918</v>
+        <v>883</v>
       </c>
       <c r="F419" s="18" t="s">
         <v>804</v>
@@ -19118,27 +19418,27 @@
         <v>500</v>
       </c>
     </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A420" s="20">
         <v>46181</v>
       </c>
       <c r="B420" s="18" t="s">
-        <v>91</v>
+        <v>882</v>
       </c>
       <c r="C420" s="18" t="s">
-        <v>113</v>
+        <v>193</v>
       </c>
       <c r="D420" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E420" s="24" t="s">
-        <v>959</v>
+        <v>918</v>
       </c>
       <c r="F420" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G420" s="24" t="s">
-        <v>969</v>
+        <v>147</v>
       </c>
       <c r="H420" s="18">
         <v>1</v>
@@ -19152,28 +19452,28 @@
         <v>46181</v>
       </c>
       <c r="B421" s="18" t="s">
-        <v>412</v>
+        <v>91</v>
       </c>
       <c r="C421" s="18" t="s">
-        <v>266</v>
+        <v>113</v>
       </c>
       <c r="D421" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E421" s="24" t="s">
-        <v>952</v>
+        <v>957</v>
       </c>
       <c r="F421" s="18" t="s">
         <v>861</v>
       </c>
       <c r="G421" s="24" t="s">
-        <v>953</v>
+        <v>964</v>
       </c>
       <c r="H421" s="18">
         <v>1</v>
       </c>
       <c r="I421" s="18" t="s">
-        <v>252</v>
+        <v>500</v>
       </c>
     </row>
     <row r="422" spans="1:9" x14ac:dyDescent="0.3">
@@ -19181,89 +19481,89 @@
         <v>46181</v>
       </c>
       <c r="B422" s="18" t="s">
-        <v>91</v>
+        <v>412</v>
       </c>
       <c r="C422" s="18" t="s">
-        <v>10</v>
+        <v>266</v>
       </c>
       <c r="D422" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E422" s="24" t="s">
-        <v>960</v>
+        <v>951</v>
       </c>
       <c r="F422" s="18" t="s">
         <v>861</v>
       </c>
       <c r="G422" s="24" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="H422" s="18">
         <v>1</v>
       </c>
       <c r="I422" s="18" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="423" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A423" s="20">
+        <v>46181</v>
+      </c>
+      <c r="B423" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C423" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D423" s="18">
+        <v>1</v>
+      </c>
+      <c r="E423" s="24" t="s">
+        <v>958</v>
+      </c>
+      <c r="F423" s="18" t="s">
+        <v>861</v>
+      </c>
+      <c r="G423" s="24" t="s">
+        <v>963</v>
+      </c>
+      <c r="H423" s="18">
+        <v>1</v>
+      </c>
+      <c r="I423" s="18" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="423" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A423" s="20">
-        <v>46182</v>
-      </c>
-      <c r="B423" s="18" t="s">
-        <v>879</v>
-      </c>
-      <c r="C423" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="D423" s="18">
-        <v>0</v>
-      </c>
-      <c r="E423" s="24" t="s">
-        <v>880</v>
-      </c>
-      <c r="F423" s="18" t="s">
-        <v>804</v>
-      </c>
-      <c r="G423" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="H423" s="18">
-        <v>1</v>
-      </c>
-      <c r="I423" s="18" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="424" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A424" s="20">
         <v>46182</v>
       </c>
       <c r="B424" s="18" t="s">
-        <v>408</v>
+        <v>879</v>
       </c>
       <c r="C424" s="18" t="s">
-        <v>155</v>
+        <v>74</v>
       </c>
       <c r="D424" s="18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E424" s="24" t="s">
-        <v>908</v>
+        <v>880</v>
       </c>
       <c r="F424" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G424" s="24" t="s">
-        <v>909</v>
+        <v>147</v>
       </c>
       <c r="H424" s="18">
         <v>1</v>
       </c>
       <c r="I424" s="18" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="425" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="425" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A425" s="20">
         <v>46182</v>
       </c>
@@ -19271,19 +19571,19 @@
         <v>408</v>
       </c>
       <c r="C425" s="18" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="D425" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E425" s="24" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="F425" s="18" t="s">
-        <v>804</v>
+        <v>861</v>
       </c>
       <c r="G425" s="24" t="s">
-        <v>147</v>
+        <v>909</v>
       </c>
       <c r="H425" s="18">
         <v>1</v>
@@ -19303,16 +19603,16 @@
         <v>179</v>
       </c>
       <c r="D426" s="18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E426" s="24" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F426" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G426" s="24" t="s">
-        <v>912</v>
+        <v>147</v>
       </c>
       <c r="H426" s="18">
         <v>1</v>
@@ -19321,65 +19621,65 @@
         <v>64</v>
       </c>
     </row>
-    <row r="427" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A427" s="20">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="B427" s="18" t="s">
-        <v>91</v>
+        <v>408</v>
       </c>
       <c r="C427" s="18" t="s">
-        <v>10</v>
+        <v>179</v>
       </c>
       <c r="D427" s="18">
         <v>2</v>
       </c>
       <c r="E427" s="24" t="s">
-        <v>955</v>
+        <v>911</v>
       </c>
       <c r="F427" s="18" t="s">
         <v>861</v>
       </c>
       <c r="G427" s="24" t="s">
-        <v>963</v>
+        <v>912</v>
       </c>
       <c r="H427" s="18">
         <v>1</v>
       </c>
       <c r="I427" s="18" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="428" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="428" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A428" s="20">
         <v>46183</v>
       </c>
       <c r="B428" s="18" t="s">
-        <v>408</v>
+        <v>91</v>
       </c>
       <c r="C428" s="18" t="s">
-        <v>113</v>
+        <v>10</v>
       </c>
       <c r="D428" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E428" s="24" t="s">
-        <v>913</v>
+        <v>953</v>
       </c>
       <c r="F428" s="18" t="s">
         <v>861</v>
       </c>
       <c r="G428" s="24" t="s">
-        <v>683</v>
+        <v>969</v>
       </c>
       <c r="H428" s="18">
         <v>1</v>
       </c>
       <c r="I428" s="18" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="429" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="429" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A429" s="20">
         <v>46183</v>
       </c>
@@ -19390,16 +19690,16 @@
         <v>113</v>
       </c>
       <c r="D429" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E429" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F429" s="18" t="s">
         <v>861</v>
       </c>
       <c r="G429" s="24" t="s">
-        <v>915</v>
+        <v>683</v>
       </c>
       <c r="H429" s="18">
         <v>1</v>
@@ -19408,7 +19708,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A430" s="20">
         <v>46183</v>
       </c>
@@ -19416,19 +19716,19 @@
         <v>408</v>
       </c>
       <c r="C430" s="18" t="s">
-        <v>896</v>
+        <v>113</v>
       </c>
       <c r="D430" s="18">
         <v>2</v>
       </c>
       <c r="E430" s="24" t="s">
-        <v>961</v>
+        <v>914</v>
       </c>
       <c r="F430" s="18" t="s">
         <v>861</v>
       </c>
       <c r="G430" s="24" t="s">
-        <v>964</v>
+        <v>915</v>
       </c>
       <c r="H430" s="18">
         <v>1</v>
@@ -19439,25 +19739,25 @@
     </row>
     <row r="431" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A431" s="20">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="B431" s="18" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C431" s="18" t="s">
-        <v>113</v>
+        <v>896</v>
       </c>
       <c r="D431" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E431" s="24" t="s">
-        <v>949</v>
+        <v>959</v>
       </c>
       <c r="F431" s="18" t="s">
         <v>861</v>
       </c>
       <c r="G431" s="24" t="s">
-        <v>683</v>
+        <v>970</v>
       </c>
       <c r="H431" s="18">
         <v>1</v>
@@ -19466,7 +19766,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="432" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A432" s="20">
         <v>46184</v>
       </c>
@@ -19474,19 +19774,19 @@
         <v>412</v>
       </c>
       <c r="C432" s="18" t="s">
-        <v>311</v>
+        <v>113</v>
       </c>
       <c r="D432" s="18">
         <v>1</v>
       </c>
       <c r="E432" s="24" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="F432" s="18" t="s">
         <v>861</v>
       </c>
       <c r="G432" s="24" t="s">
-        <v>932</v>
+        <v>683</v>
       </c>
       <c r="H432" s="18">
         <v>1</v>
@@ -19500,22 +19800,22 @@
         <v>46184</v>
       </c>
       <c r="B433" s="18" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C433" s="18" t="s">
-        <v>200</v>
+        <v>311</v>
       </c>
       <c r="D433" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E433" s="24" t="s">
-        <v>899</v>
+        <v>949</v>
       </c>
       <c r="F433" s="18" t="s">
         <v>861</v>
       </c>
       <c r="G433" s="24" t="s">
-        <v>900</v>
+        <v>932</v>
       </c>
       <c r="H433" s="18">
         <v>1</v>
@@ -19529,22 +19829,22 @@
         <v>46184</v>
       </c>
       <c r="B434" s="18" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C434" s="18" t="s">
-        <v>311</v>
+        <v>200</v>
       </c>
       <c r="D434" s="18">
         <v>2</v>
       </c>
       <c r="E434" s="24" t="s">
-        <v>962</v>
+        <v>899</v>
       </c>
       <c r="F434" s="18" t="s">
         <v>861</v>
       </c>
       <c r="G434" s="24" t="s">
-        <v>970</v>
+        <v>900</v>
       </c>
       <c r="H434" s="18">
         <v>1</v>
@@ -19553,27 +19853,27 @@
         <v>64</v>
       </c>
     </row>
-    <row r="435" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A435" s="20">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="B435" s="18" t="s">
-        <v>882</v>
+        <v>412</v>
       </c>
       <c r="C435" s="18" t="s">
-        <v>193</v>
+        <v>311</v>
       </c>
       <c r="D435" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E435" s="24" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="F435" s="18" t="s">
-        <v>804</v>
+        <v>861</v>
       </c>
       <c r="G435" s="24" t="s">
-        <v>147</v>
+        <v>965</v>
       </c>
       <c r="H435" s="18">
         <v>1</v>
@@ -19587,60 +19887,60 @@
         <v>46185</v>
       </c>
       <c r="B436" s="18" t="s">
-        <v>247</v>
+        <v>882</v>
       </c>
       <c r="C436" s="18" t="s">
-        <v>892</v>
+        <v>193</v>
       </c>
       <c r="D436" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E436" s="24" t="s">
         <v>954</v>
       </c>
       <c r="F436" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G436" s="24" t="s">
-        <v>967</v>
+        <v>147</v>
       </c>
       <c r="H436" s="18">
         <v>1</v>
       </c>
       <c r="I436" s="18" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="437" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="437" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A437" s="20">
         <v>46185</v>
       </c>
       <c r="B437" s="18" t="s">
-        <v>882</v>
+        <v>247</v>
       </c>
       <c r="C437" s="18" t="s">
-        <v>193</v>
+        <v>892</v>
       </c>
       <c r="D437" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E437" s="24" t="s">
-        <v>916</v>
+        <v>952</v>
       </c>
       <c r="F437" s="18" t="s">
-        <v>804</v>
+        <v>861</v>
       </c>
       <c r="G437" s="24" t="s">
-        <v>147</v>
+        <v>963</v>
       </c>
       <c r="H437" s="18">
         <v>1</v>
       </c>
       <c r="I437" s="18" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="438" spans="1:9" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="438" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A438" s="20">
         <v>46185</v>
       </c>
@@ -19648,13 +19948,13 @@
         <v>882</v>
       </c>
       <c r="C438" s="18" t="s">
-        <v>942</v>
+        <v>193</v>
       </c>
       <c r="D438" s="18">
         <v>0</v>
       </c>
       <c r="E438" s="24" t="s">
-        <v>943</v>
+        <v>916</v>
       </c>
       <c r="F438" s="18" t="s">
         <v>804</v>
@@ -19669,27 +19969,27 @@
         <v>64</v>
       </c>
     </row>
-    <row r="439" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A439" s="20">
         <v>46185</v>
       </c>
       <c r="B439" s="18" t="s">
-        <v>91</v>
+        <v>882</v>
       </c>
       <c r="C439" s="18" t="s">
-        <v>10</v>
+        <v>942</v>
       </c>
       <c r="D439" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E439" s="24" t="s">
-        <v>885</v>
+        <v>943</v>
       </c>
       <c r="F439" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G439" s="24" t="s">
-        <v>886</v>
+        <v>147</v>
       </c>
       <c r="H439" s="18">
         <v>1</v>
@@ -19698,62 +19998,62 @@
         <v>64</v>
       </c>
     </row>
-    <row r="440" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A440" s="20">
-        <v>46188</v>
+        <v>46185</v>
       </c>
       <c r="B440" s="18" t="s">
-        <v>408</v>
+        <v>91</v>
       </c>
       <c r="C440" s="18" t="s">
-        <v>113</v>
+        <v>10</v>
       </c>
       <c r="D440" s="18">
         <v>1</v>
       </c>
       <c r="E440" s="24" t="s">
-        <v>951</v>
+        <v>885</v>
       </c>
       <c r="F440" s="18" t="s">
         <v>861</v>
       </c>
       <c r="G440" s="24" t="s">
-        <v>969</v>
+        <v>886</v>
       </c>
       <c r="H440" s="18">
         <v>1</v>
       </c>
       <c r="I440" s="18" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="441" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="441" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A441" s="20">
         <v>46188</v>
       </c>
       <c r="B441" s="18" t="s">
-        <v>247</v>
+        <v>408</v>
       </c>
       <c r="C441" s="18" t="s">
-        <v>892</v>
+        <v>113</v>
       </c>
       <c r="D441" s="18">
         <v>1</v>
       </c>
       <c r="E441" s="24" t="s">
-        <v>921</v>
+        <v>950</v>
       </c>
       <c r="F441" s="18" t="s">
         <v>861</v>
       </c>
       <c r="G441" s="24" t="s">
-        <v>762</v>
+        <v>964</v>
       </c>
       <c r="H441" s="18">
         <v>1</v>
       </c>
       <c r="I441" s="18" t="s">
-        <v>64</v>
+        <v>252</v>
       </c>
     </row>
     <row r="442" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
@@ -19767,16 +20067,16 @@
         <v>892</v>
       </c>
       <c r="D442" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E442" s="24" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="F442" s="18" t="s">
         <v>861</v>
       </c>
       <c r="G442" s="24" t="s">
-        <v>920</v>
+        <v>762</v>
       </c>
       <c r="H442" s="18">
         <v>1</v>
@@ -19785,33 +20085,33 @@
         <v>64</v>
       </c>
     </row>
-    <row r="443" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A443" s="20">
         <v>46188</v>
       </c>
       <c r="B443" s="18" t="s">
-        <v>412</v>
+        <v>247</v>
       </c>
       <c r="C443" s="18" t="s">
-        <v>155</v>
+        <v>892</v>
       </c>
       <c r="D443" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E443" s="24" t="s">
-        <v>876</v>
+        <v>919</v>
       </c>
       <c r="F443" s="18" t="s">
-        <v>804</v>
+        <v>861</v>
       </c>
       <c r="G443" s="24" t="s">
-        <v>147</v>
+        <v>920</v>
       </c>
       <c r="H443" s="18">
         <v>1</v>
       </c>
       <c r="I443" s="18" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
     </row>
     <row r="444" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -19822,25 +20122,25 @@
         <v>412</v>
       </c>
       <c r="C444" s="18" t="s">
-        <v>301</v>
+        <v>155</v>
       </c>
       <c r="D444" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E444" s="24" t="s">
-        <v>863</v>
+        <v>876</v>
       </c>
       <c r="F444" s="18" t="s">
         <v>804</v>
       </c>
       <c r="G444" s="24" t="s">
-        <v>757</v>
+        <v>147</v>
       </c>
       <c r="H444" s="18">
         <v>1</v>
       </c>
       <c r="I444" s="18" t="s">
-        <v>240</v>
+        <v>52</v>
       </c>
     </row>
     <row r="445" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -19851,19 +20151,19 @@
         <v>412</v>
       </c>
       <c r="C445" s="18" t="s">
-        <v>866</v>
+        <v>301</v>
       </c>
       <c r="D445" s="18">
         <v>1</v>
       </c>
       <c r="E445" s="24" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="F445" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G445" s="24" t="s">
-        <v>868</v>
+        <v>757</v>
       </c>
       <c r="H445" s="18">
         <v>1</v>
@@ -19880,25 +20180,25 @@
         <v>412</v>
       </c>
       <c r="C446" s="18" t="s">
-        <v>301</v>
+        <v>866</v>
       </c>
       <c r="D446" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E446" s="24" t="s">
-        <v>901</v>
+        <v>867</v>
       </c>
       <c r="F446" s="18" t="s">
         <v>861</v>
       </c>
       <c r="G446" s="24" t="s">
-        <v>902</v>
+        <v>868</v>
       </c>
       <c r="H446" s="18">
         <v>1</v>
       </c>
       <c r="I446" s="18" t="s">
-        <v>52</v>
+        <v>240</v>
       </c>
     </row>
     <row r="447" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -19906,28 +20206,28 @@
         <v>46188</v>
       </c>
       <c r="B447" s="18" t="s">
-        <v>247</v>
+        <v>412</v>
       </c>
       <c r="C447" s="18" t="s">
-        <v>892</v>
+        <v>301</v>
       </c>
       <c r="D447" s="18">
         <v>2</v>
       </c>
       <c r="E447" s="24" t="s">
-        <v>917</v>
+        <v>901</v>
       </c>
       <c r="F447" s="18" t="s">
         <v>861</v>
       </c>
       <c r="G447" s="24" t="s">
-        <v>912</v>
+        <v>902</v>
       </c>
       <c r="H447" s="18">
         <v>1</v>
       </c>
       <c r="I447" s="18" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="448" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -19938,19 +20238,19 @@
         <v>247</v>
       </c>
       <c r="C448" s="18" t="s">
-        <v>923</v>
+        <v>892</v>
       </c>
       <c r="D448" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E448" s="24" t="s">
-        <v>939</v>
+        <v>917</v>
       </c>
       <c r="F448" s="18" t="s">
-        <v>804</v>
+        <v>861</v>
       </c>
       <c r="G448" s="24" t="s">
-        <v>757</v>
+        <v>912</v>
       </c>
       <c r="H448" s="18">
         <v>1</v>
@@ -19961,7 +20261,7 @@
     </row>
     <row r="449" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A449" s="20">
-        <v>46189</v>
+        <v>46188</v>
       </c>
       <c r="B449" s="18" t="s">
         <v>247</v>
@@ -19973,13 +20273,13 @@
         <v>1</v>
       </c>
       <c r="E449" s="24" t="s">
-        <v>924</v>
+        <v>939</v>
       </c>
       <c r="F449" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G449" s="24" t="s">
-        <v>925</v>
+        <v>757</v>
       </c>
       <c r="H449" s="18">
         <v>1</v>
@@ -19999,16 +20299,16 @@
         <v>923</v>
       </c>
       <c r="D450" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E450" s="24" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="F450" s="18" t="s">
         <v>861</v>
       </c>
       <c r="G450" s="24" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="H450" s="18">
         <v>1</v>
@@ -20031,13 +20331,13 @@
         <v>2</v>
       </c>
       <c r="E451" s="24" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="F451" s="18" t="s">
         <v>861</v>
       </c>
       <c r="G451" s="24" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="H451" s="18">
         <v>1</v>
@@ -20051,28 +20351,28 @@
         <v>46189</v>
       </c>
       <c r="B452" s="18" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C452" s="18" t="s">
-        <v>930</v>
+        <v>923</v>
       </c>
       <c r="D452" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E452" s="24" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="F452" s="18" t="s">
         <v>861</v>
       </c>
       <c r="G452" s="24" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="H452" s="18">
         <v>1</v>
       </c>
       <c r="I452" s="18" t="s">
-        <v>252</v>
+        <v>64</v>
       </c>
     </row>
     <row r="453" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -20089,13 +20389,13 @@
         <v>1</v>
       </c>
       <c r="E453" s="24" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="F453" s="18" t="s">
         <v>861</v>
       </c>
       <c r="G453" s="24" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="H453" s="18">
         <v>1</v>
@@ -20118,13 +20418,13 @@
         <v>1</v>
       </c>
       <c r="E454" s="24" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="F454" s="18" t="s">
         <v>861</v>
       </c>
       <c r="G454" s="24" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="H454" s="18">
         <v>1</v>
@@ -20133,27 +20433,27 @@
         <v>252</v>
       </c>
     </row>
-    <row r="455" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A455" s="20">
-        <v>46190</v>
+        <v>46189</v>
       </c>
       <c r="B455" s="18" t="s">
-        <v>408</v>
+        <v>243</v>
       </c>
       <c r="C455" s="18" t="s">
-        <v>116</v>
+        <v>930</v>
       </c>
       <c r="D455" s="18">
         <v>1</v>
       </c>
       <c r="E455" s="24" t="s">
-        <v>948</v>
+        <v>935</v>
       </c>
       <c r="F455" s="18" t="s">
         <v>861</v>
       </c>
       <c r="G455" s="24" t="s">
-        <v>965</v>
+        <v>936</v>
       </c>
       <c r="H455" s="18">
         <v>1</v>
@@ -20162,33 +20462,33 @@
         <v>252</v>
       </c>
     </row>
-    <row r="456" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A456" s="20">
-        <v>46191</v>
+        <v>46190</v>
       </c>
       <c r="B456" s="18" t="s">
-        <v>247</v>
+        <v>408</v>
       </c>
       <c r="C456" s="18" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D456" s="18">
         <v>1</v>
       </c>
       <c r="E456" s="24" t="s">
-        <v>937</v>
+        <v>947</v>
       </c>
       <c r="F456" s="18" t="s">
         <v>861</v>
       </c>
       <c r="G456" s="24" t="s">
-        <v>938</v>
+        <v>961</v>
       </c>
       <c r="H456" s="18">
         <v>1</v>
       </c>
       <c r="I456" s="18" t="s">
-        <v>64</v>
+        <v>252</v>
       </c>
     </row>
     <row r="457" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -20199,19 +20499,19 @@
         <v>247</v>
       </c>
       <c r="C457" s="18" t="s">
-        <v>892</v>
+        <v>113</v>
       </c>
       <c r="D457" s="18">
         <v>1</v>
       </c>
       <c r="E457" s="24" t="s">
-        <v>922</v>
+        <v>937</v>
       </c>
       <c r="F457" s="18" t="s">
         <v>861</v>
       </c>
       <c r="G457" s="24" t="s">
-        <v>762</v>
+        <v>938</v>
       </c>
       <c r="H457" s="18">
         <v>1</v>
@@ -20220,7 +20520,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="458" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A458" s="20">
         <v>46191</v>
       </c>
@@ -20231,16 +20531,16 @@
         <v>892</v>
       </c>
       <c r="D458" s="18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E458" s="24" t="s">
-        <v>891</v>
+        <v>922</v>
       </c>
       <c r="F458" s="18" t="s">
         <v>861</v>
       </c>
       <c r="G458" s="24" t="s">
-        <v>893</v>
+        <v>762</v>
       </c>
       <c r="H458" s="18">
         <v>1</v>
@@ -20249,50 +20549,50 @@
         <v>64</v>
       </c>
     </row>
-    <row r="459" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A459" s="20">
         <v>46191</v>
       </c>
       <c r="B459" s="18" t="s">
-        <v>860</v>
+        <v>247</v>
       </c>
       <c r="C459" s="18" t="s">
-        <v>205</v>
+        <v>892</v>
       </c>
       <c r="D459" s="18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E459" s="24" t="s">
-        <v>874</v>
+        <v>891</v>
       </c>
       <c r="F459" s="18" t="s">
-        <v>804</v>
+        <v>861</v>
       </c>
       <c r="G459" s="24" t="s">
-        <v>147</v>
+        <v>893</v>
       </c>
       <c r="H459" s="18">
         <v>1</v>
       </c>
       <c r="I459" s="18" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
     </row>
     <row r="460" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A460" s="20">
-        <v>46192</v>
+        <v>46191</v>
       </c>
       <c r="B460" s="18" t="s">
-        <v>412</v>
+        <v>860</v>
       </c>
       <c r="C460" s="18" t="s">
-        <v>155</v>
+        <v>205</v>
       </c>
       <c r="D460" s="18">
         <v>0</v>
       </c>
       <c r="E460" s="24" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="F460" s="18" t="s">
         <v>804</v>
@@ -20307,12 +20607,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="461" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A461" s="20">
-        <v>46195</v>
+        <v>46192</v>
       </c>
       <c r="B461" s="18" t="s">
-        <v>247</v>
+        <v>412</v>
       </c>
       <c r="C461" s="18" t="s">
         <v>155</v>
@@ -20321,7 +20621,7 @@
         <v>0</v>
       </c>
       <c r="E461" s="24" t="s">
-        <v>430</v>
+        <v>873</v>
       </c>
       <c r="F461" s="18" t="s">
         <v>804</v>
@@ -20333,70 +20633,70 @@
         <v>1</v>
       </c>
       <c r="I461" s="18" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="462" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="462" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A462" s="20">
         <v>46195</v>
       </c>
       <c r="B462" s="18" t="s">
-        <v>412</v>
+        <v>247</v>
       </c>
       <c r="C462" s="18" t="s">
-        <v>442</v>
+        <v>155</v>
       </c>
       <c r="D462" s="18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E462" s="24" t="s">
-        <v>864</v>
+        <v>430</v>
       </c>
       <c r="F462" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G462" s="24" t="s">
-        <v>865</v>
+        <v>147</v>
       </c>
       <c r="H462" s="18">
         <v>1</v>
       </c>
       <c r="I462" s="18" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="463" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="463" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A463" s="20">
         <v>46195</v>
       </c>
       <c r="B463" s="18" t="s">
-        <v>247</v>
+        <v>412</v>
       </c>
       <c r="C463" s="18" t="s">
-        <v>155</v>
+        <v>442</v>
       </c>
       <c r="D463" s="18">
         <v>2</v>
       </c>
       <c r="E463" s="24" t="s">
-        <v>895</v>
+        <v>864</v>
       </c>
       <c r="F463" s="18" t="s">
         <v>861</v>
       </c>
       <c r="G463" s="24" t="s">
-        <v>894</v>
+        <v>865</v>
       </c>
       <c r="H463" s="18">
         <v>1</v>
       </c>
       <c r="I463" s="18" t="s">
-        <v>64</v>
+        <v>240</v>
       </c>
     </row>
     <row r="464" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A464" s="20">
-        <v>46196</v>
+        <v>46195</v>
       </c>
       <c r="B464" s="18" t="s">
         <v>247</v>
@@ -20408,13 +20708,13 @@
         <v>2</v>
       </c>
       <c r="E464" s="24" t="s">
-        <v>888</v>
+        <v>895</v>
       </c>
       <c r="F464" s="18" t="s">
         <v>861</v>
       </c>
       <c r="G464" s="24" t="s">
-        <v>887</v>
+        <v>894</v>
       </c>
       <c r="H464" s="18">
         <v>1</v>
@@ -20423,7 +20723,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="465" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A465" s="20">
         <v>46196</v>
       </c>
@@ -20431,19 +20731,19 @@
         <v>247</v>
       </c>
       <c r="C465" s="18" t="s">
-        <v>892</v>
+        <v>155</v>
       </c>
       <c r="D465" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E465" s="24" t="s">
-        <v>940</v>
+        <v>888</v>
       </c>
       <c r="F465" s="18" t="s">
-        <v>804</v>
+        <v>861</v>
       </c>
       <c r="G465" s="24" t="s">
-        <v>941</v>
+        <v>887</v>
       </c>
       <c r="H465" s="18">
         <v>1</v>
@@ -20452,187 +20752,411 @@
         <v>64</v>
       </c>
     </row>
-    <row r="466" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A466" s="20"/>
-      <c r="B466" s="18"/>
-      <c r="C466" s="18"/>
+    <row r="466" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A466" s="20">
+        <v>46196</v>
+      </c>
+      <c r="B466" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="C466" s="18" t="s">
+        <v>892</v>
+      </c>
       <c r="D466" s="18">
-        <v>0</v>
-      </c>
-      <c r="E466" s="24"/>
-      <c r="F466" s="18"/>
-      <c r="G466" s="24"/>
-      <c r="H466" s="18"/>
-      <c r="I466" s="18"/>
+        <v>1</v>
+      </c>
+      <c r="E466" s="24" t="s">
+        <v>940</v>
+      </c>
+      <c r="F466" s="18" t="s">
+        <v>804</v>
+      </c>
+      <c r="G466" s="24" t="s">
+        <v>941</v>
+      </c>
+      <c r="H466" s="18">
+        <v>1</v>
+      </c>
+      <c r="I466" s="18" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="467" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A467" s="20"/>
-      <c r="B467" s="18"/>
-      <c r="C467" s="18"/>
+      <c r="A467" s="20">
+        <v>46198</v>
+      </c>
+      <c r="B467" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="C467" s="18" t="s">
+        <v>155</v>
+      </c>
       <c r="D467" s="18">
-        <v>0</v>
-      </c>
-      <c r="E467" s="24"/>
-      <c r="F467" s="18"/>
-      <c r="G467" s="24"/>
-      <c r="H467" s="18"/>
-      <c r="I467" s="18"/>
+        <v>2</v>
+      </c>
+      <c r="E467" s="24" t="s">
+        <v>1005</v>
+      </c>
+      <c r="F467" s="18" t="s">
+        <v>861</v>
+      </c>
+      <c r="G467" s="24" t="s">
+        <v>1003</v>
+      </c>
+      <c r="H467" s="18">
+        <v>1</v>
+      </c>
+      <c r="I467" s="18" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="468" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A468" s="20"/>
-      <c r="B468" s="18"/>
-      <c r="C468" s="18"/>
+      <c r="A468" s="20">
+        <v>46198</v>
+      </c>
+      <c r="B468" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="C468" s="18" t="s">
+        <v>155</v>
+      </c>
       <c r="D468" s="18">
-        <v>0</v>
-      </c>
-      <c r="E468" s="24"/>
-      <c r="F468" s="18"/>
-      <c r="G468" s="24"/>
-      <c r="H468" s="18"/>
-      <c r="I468" s="18"/>
+        <v>4</v>
+      </c>
+      <c r="E468" s="24" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F468" s="18" t="s">
+        <v>861</v>
+      </c>
+      <c r="G468" s="24" t="s">
+        <v>1001</v>
+      </c>
+      <c r="H468" s="18">
+        <v>1</v>
+      </c>
+      <c r="I468" s="18" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="469" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A469" s="20"/>
-      <c r="B469" s="18"/>
-      <c r="C469" s="18"/>
+      <c r="A469" s="20">
+        <v>46198</v>
+      </c>
+      <c r="B469" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="C469" s="18" t="s">
+        <v>155</v>
+      </c>
       <c r="D469" s="18">
-        <v>0</v>
-      </c>
-      <c r="E469" s="24"/>
-      <c r="F469" s="18"/>
-      <c r="G469" s="24"/>
-      <c r="H469" s="18"/>
-      <c r="I469" s="18"/>
+        <v>1</v>
+      </c>
+      <c r="E469" s="24" t="s">
+        <v>1006</v>
+      </c>
+      <c r="F469" s="18" t="s">
+        <v>861</v>
+      </c>
+      <c r="G469" s="24" t="s">
+        <v>626</v>
+      </c>
+      <c r="H469" s="18">
+        <v>1</v>
+      </c>
+      <c r="I469" s="18" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="470" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A470" s="20"/>
-      <c r="B470" s="18"/>
-      <c r="C470" s="18"/>
+      <c r="A470" s="20">
+        <v>46198</v>
+      </c>
+      <c r="B470" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="C470" s="18" t="s">
+        <v>155</v>
+      </c>
       <c r="D470" s="18">
-        <v>0</v>
-      </c>
-      <c r="E470" s="24"/>
-      <c r="F470" s="18"/>
-      <c r="G470" s="24"/>
-      <c r="H470" s="18"/>
-      <c r="I470" s="18"/>
+        <v>1</v>
+      </c>
+      <c r="E470" s="24" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F470" s="18" t="s">
+        <v>861</v>
+      </c>
+      <c r="G470" s="24" t="s">
+        <v>625</v>
+      </c>
+      <c r="H470" s="18">
+        <v>1</v>
+      </c>
+      <c r="I470" s="18" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="471" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A471" s="20"/>
-      <c r="B471" s="18"/>
-      <c r="C471" s="18"/>
+      <c r="A471" s="20">
+        <v>46198</v>
+      </c>
+      <c r="B471" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="C471" s="18" t="s">
+        <v>442</v>
+      </c>
       <c r="D471" s="18">
-        <v>0</v>
-      </c>
-      <c r="E471" s="24"/>
-      <c r="F471" s="18"/>
-      <c r="G471" s="24"/>
-      <c r="H471" s="18"/>
-      <c r="I471" s="18"/>
+        <v>1</v>
+      </c>
+      <c r="E471" s="24" t="s">
+        <v>1008</v>
+      </c>
+      <c r="F471" s="18" t="s">
+        <v>861</v>
+      </c>
+      <c r="G471" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="H471" s="18">
+        <v>1</v>
+      </c>
+      <c r="I471" s="18" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="472" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A472" s="20"/>
-      <c r="B472" s="18"/>
-      <c r="C472" s="18"/>
+      <c r="A472" s="20">
+        <v>46199</v>
+      </c>
+      <c r="B472" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="C472" s="18" t="s">
+        <v>155</v>
+      </c>
       <c r="D472" s="18">
-        <v>0</v>
-      </c>
-      <c r="E472" s="24"/>
-      <c r="F472" s="18"/>
-      <c r="G472" s="24"/>
-      <c r="H472" s="18"/>
-      <c r="I472" s="18"/>
+        <v>1</v>
+      </c>
+      <c r="E472" s="24" t="s">
+        <v>1004</v>
+      </c>
+      <c r="F472" s="18" t="s">
+        <v>861</v>
+      </c>
+      <c r="G472" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="H472" s="18">
+        <v>1</v>
+      </c>
+      <c r="I472" s="18" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="473" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A473" s="20"/>
-      <c r="B473" s="18"/>
-      <c r="C473" s="18"/>
+      <c r="A473" s="20">
+        <v>46200</v>
+      </c>
+      <c r="B473" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="C473" s="18" t="s">
+        <v>923</v>
+      </c>
       <c r="D473" s="18">
-        <v>0</v>
-      </c>
-      <c r="E473" s="24"/>
-      <c r="F473" s="18"/>
-      <c r="G473" s="24"/>
-      <c r="H473" s="18"/>
-      <c r="I473" s="18"/>
+        <v>1</v>
+      </c>
+      <c r="E473" s="24" t="s">
+        <v>998</v>
+      </c>
+      <c r="F473" s="18" t="s">
+        <v>861</v>
+      </c>
+      <c r="G473" s="24" t="s">
+        <v>999</v>
+      </c>
+      <c r="H473" s="18">
+        <v>1</v>
+      </c>
+      <c r="I473" s="18" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="474" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A474" s="20"/>
-      <c r="B474" s="18"/>
-      <c r="C474" s="18"/>
+      <c r="A474" s="20">
+        <v>46200</v>
+      </c>
+      <c r="B474" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="C474" s="18" t="s">
+        <v>155</v>
+      </c>
       <c r="D474" s="18">
-        <v>0</v>
-      </c>
-      <c r="E474" s="24"/>
-      <c r="F474" s="18"/>
-      <c r="G474" s="24"/>
-      <c r="H474" s="18"/>
-      <c r="I474" s="18"/>
+        <v>1</v>
+      </c>
+      <c r="E474" s="24" t="s">
+        <v>997</v>
+      </c>
+      <c r="F474" s="18" t="s">
+        <v>861</v>
+      </c>
+      <c r="G474" s="24" t="s">
+        <v>835</v>
+      </c>
+      <c r="H474" s="18">
+        <v>1</v>
+      </c>
+      <c r="I474" s="18" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="475" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A475" s="20"/>
-      <c r="B475" s="18"/>
-      <c r="C475" s="18"/>
+      <c r="A475" s="20">
+        <v>46200</v>
+      </c>
+      <c r="B475" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="C475" s="18" t="s">
+        <v>155</v>
+      </c>
       <c r="D475" s="18">
-        <v>0</v>
-      </c>
-      <c r="E475" s="24"/>
-      <c r="F475" s="18"/>
-      <c r="G475" s="24"/>
-      <c r="H475" s="18"/>
-      <c r="I475" s="18"/>
+        <v>1</v>
+      </c>
+      <c r="E475" s="24" t="s">
+        <v>996</v>
+      </c>
+      <c r="F475" s="18" t="s">
+        <v>861</v>
+      </c>
+      <c r="G475" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="H475" s="18">
+        <v>1</v>
+      </c>
+      <c r="I475" s="18" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="476" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A476" s="20"/>
-      <c r="B476" s="18"/>
-      <c r="C476" s="18"/>
+      <c r="A476" s="20">
+        <v>46201</v>
+      </c>
+      <c r="B476" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="C476" s="18" t="s">
+        <v>990</v>
+      </c>
       <c r="D476" s="18">
-        <v>0</v>
-      </c>
-      <c r="E476" s="24"/>
-      <c r="F476" s="18"/>
-      <c r="G476" s="24"/>
-      <c r="H476" s="18"/>
-      <c r="I476" s="18"/>
+        <v>3</v>
+      </c>
+      <c r="E476" s="24" t="s">
+        <v>991</v>
+      </c>
+      <c r="F476" s="18" t="s">
+        <v>861</v>
+      </c>
+      <c r="G476" s="24" t="s">
+        <v>992</v>
+      </c>
+      <c r="H476" s="18">
+        <v>1</v>
+      </c>
+      <c r="I476" s="18" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="477" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A477" s="20"/>
-      <c r="B477" s="18"/>
-      <c r="C477" s="18"/>
+      <c r="A477" s="20">
+        <v>46201</v>
+      </c>
+      <c r="B477" s="18" t="s">
+        <v>993</v>
+      </c>
+      <c r="C477" s="18" t="s">
+        <v>942</v>
+      </c>
       <c r="D477" s="18">
-        <v>0</v>
-      </c>
-      <c r="E477" s="24"/>
-      <c r="F477" s="18"/>
-      <c r="G477" s="24"/>
-      <c r="H477" s="18"/>
-      <c r="I477" s="18"/>
-    </row>
-    <row r="478" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A478" s="20"/>
-      <c r="B478" s="18"/>
-      <c r="C478" s="18"/>
+        <v>3</v>
+      </c>
+      <c r="E477" s="24" t="s">
+        <v>994</v>
+      </c>
+      <c r="F477" s="18" t="s">
+        <v>861</v>
+      </c>
+      <c r="G477" s="24" t="s">
+        <v>995</v>
+      </c>
+      <c r="H477" s="18">
+        <v>1</v>
+      </c>
+      <c r="I477" s="18" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="478" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A478" s="20">
+        <v>46203</v>
+      </c>
+      <c r="B478" s="18" t="s">
+        <v>987</v>
+      </c>
+      <c r="C478" s="18" t="s">
+        <v>10</v>
+      </c>
       <c r="D478" s="18">
-        <v>0</v>
-      </c>
-      <c r="E478" s="24"/>
-      <c r="F478" s="18"/>
-      <c r="G478" s="24"/>
-      <c r="H478" s="18"/>
-      <c r="I478" s="18"/>
+        <v>2</v>
+      </c>
+      <c r="E478" s="24" t="s">
+        <v>988</v>
+      </c>
+      <c r="F478" s="18" t="s">
+        <v>861</v>
+      </c>
+      <c r="G478" s="24" t="s">
+        <v>989</v>
+      </c>
+      <c r="H478" s="18">
+        <v>1</v>
+      </c>
+      <c r="I478" s="18" t="s">
+        <v>500</v>
+      </c>
     </row>
     <row r="479" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A479" s="20"/>
-      <c r="B479" s="18"/>
-      <c r="C479" s="18"/>
+      <c r="A479" s="20">
+        <v>46203</v>
+      </c>
+      <c r="B479" s="18" t="s">
+        <v>882</v>
+      </c>
+      <c r="C479" s="18" t="s">
+        <v>193</v>
+      </c>
       <c r="D479" s="18">
         <v>0</v>
       </c>
-      <c r="E479" s="24"/>
-      <c r="F479" s="18"/>
-      <c r="G479" s="24"/>
-      <c r="H479" s="18"/>
-      <c r="I479" s="18"/>
+      <c r="E479" s="24" t="s">
+        <v>430</v>
+      </c>
+      <c r="F479" s="18" t="s">
+        <v>804</v>
+      </c>
+      <c r="G479" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="H479" s="18">
+        <v>1</v>
+      </c>
+      <c r="I479" s="18" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="480" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A480" s="20"/>
@@ -22051,38 +22575,194 @@
       <c r="H588" s="18"/>
       <c r="I588" s="18"/>
     </row>
-    <row r="589" spans="1:9" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A589" s="33" t="s">
+    <row r="589" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A589" s="20"/>
+      <c r="B589" s="18"/>
+      <c r="C589" s="18"/>
+      <c r="D589" s="18">
+        <v>0</v>
+      </c>
+      <c r="E589" s="24"/>
+      <c r="F589" s="18"/>
+      <c r="G589" s="24"/>
+      <c r="H589" s="18"/>
+      <c r="I589" s="18"/>
+    </row>
+    <row r="590" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A590" s="20"/>
+      <c r="B590" s="18"/>
+      <c r="C590" s="18"/>
+      <c r="D590" s="18">
+        <v>0</v>
+      </c>
+      <c r="E590" s="24"/>
+      <c r="F590" s="18"/>
+      <c r="G590" s="24"/>
+      <c r="H590" s="18"/>
+      <c r="I590" s="18"/>
+    </row>
+    <row r="591" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A591" s="20"/>
+      <c r="B591" s="18"/>
+      <c r="C591" s="18"/>
+      <c r="D591" s="18">
+        <v>0</v>
+      </c>
+      <c r="E591" s="24"/>
+      <c r="F591" s="18"/>
+      <c r="G591" s="24"/>
+      <c r="H591" s="18"/>
+      <c r="I591" s="18"/>
+    </row>
+    <row r="592" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A592" s="20"/>
+      <c r="B592" s="18"/>
+      <c r="C592" s="18"/>
+      <c r="D592" s="18">
+        <v>0</v>
+      </c>
+      <c r="E592" s="24"/>
+      <c r="F592" s="18"/>
+      <c r="G592" s="24"/>
+      <c r="H592" s="18"/>
+      <c r="I592" s="18"/>
+    </row>
+    <row r="593" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A593" s="20"/>
+      <c r="B593" s="18"/>
+      <c r="C593" s="18"/>
+      <c r="D593" s="18">
+        <v>0</v>
+      </c>
+      <c r="E593" s="24"/>
+      <c r="F593" s="18"/>
+      <c r="G593" s="24"/>
+      <c r="H593" s="18"/>
+      <c r="I593" s="18"/>
+    </row>
+    <row r="594" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A594" s="20"/>
+      <c r="B594" s="18"/>
+      <c r="C594" s="18"/>
+      <c r="D594" s="18">
+        <v>0</v>
+      </c>
+      <c r="E594" s="24"/>
+      <c r="F594" s="18"/>
+      <c r="G594" s="24"/>
+      <c r="H594" s="18"/>
+      <c r="I594" s="18"/>
+    </row>
+    <row r="595" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A595" s="20"/>
+      <c r="B595" s="18"/>
+      <c r="C595" s="18"/>
+      <c r="D595" s="18">
+        <v>0</v>
+      </c>
+      <c r="E595" s="24"/>
+      <c r="F595" s="18"/>
+      <c r="G595" s="24"/>
+      <c r="H595" s="18"/>
+      <c r="I595" s="18"/>
+    </row>
+    <row r="596" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A596" s="20"/>
+      <c r="B596" s="18"/>
+      <c r="C596" s="18"/>
+      <c r="D596" s="18">
+        <v>0</v>
+      </c>
+      <c r="E596" s="24"/>
+      <c r="F596" s="18"/>
+      <c r="G596" s="24"/>
+      <c r="H596" s="18"/>
+      <c r="I596" s="18"/>
+    </row>
+    <row r="597" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A597" s="20"/>
+      <c r="B597" s="18"/>
+      <c r="C597" s="18"/>
+      <c r="D597" s="18">
+        <v>0</v>
+      </c>
+      <c r="E597" s="24"/>
+      <c r="F597" s="18"/>
+      <c r="G597" s="24"/>
+      <c r="H597" s="18"/>
+      <c r="I597" s="18"/>
+    </row>
+    <row r="598" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A598" s="20"/>
+      <c r="B598" s="18"/>
+      <c r="C598" s="18"/>
+      <c r="D598" s="18">
+        <v>0</v>
+      </c>
+      <c r="E598" s="24"/>
+      <c r="F598" s="18"/>
+      <c r="G598" s="24"/>
+      <c r="H598" s="18"/>
+      <c r="I598" s="18"/>
+    </row>
+    <row r="599" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A599" s="20"/>
+      <c r="B599" s="18"/>
+      <c r="C599" s="18"/>
+      <c r="D599" s="18">
+        <v>0</v>
+      </c>
+      <c r="E599" s="24"/>
+      <c r="F599" s="18"/>
+      <c r="G599" s="24"/>
+      <c r="H599" s="18"/>
+      <c r="I599" s="18"/>
+    </row>
+    <row r="600" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A600" s="20"/>
+      <c r="B600" s="18"/>
+      <c r="C600" s="18"/>
+      <c r="D600" s="18">
+        <v>0</v>
+      </c>
+      <c r="E600" s="24"/>
+      <c r="F600" s="18"/>
+      <c r="G600" s="24"/>
+      <c r="H600" s="18"/>
+      <c r="I600" s="18"/>
+    </row>
+    <row r="601" spans="1:9" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A601" s="33" t="s">
         <v>513</v>
       </c>
-      <c r="B589" s="33">
+      <c r="B601" s="33">
         <f>SUBTOTAL(103,Tabela5[LOCAL])</f>
-        <v>464</v>
-      </c>
-      <c r="C589" s="33">
+        <v>478</v>
+      </c>
+      <c r="C601" s="33">
         <f>SUBTOTAL(103,Tabela5[ENCARREGADO OU LIDER DE EQUIPE])</f>
-        <v>464</v>
-      </c>
-      <c r="D589" s="33">
-        <f>SUM(D2:D588)</f>
-        <v>696</v>
-      </c>
-      <c r="E589" s="33">
+        <v>478</v>
+      </c>
+      <c r="D601" s="33">
+        <f>SUM(D2:D600)</f>
+        <v>719</v>
+      </c>
+      <c r="E601" s="33">
         <f>SUBTOTAL(103,Tabela5[DESCRIÇÃO])</f>
-        <v>464</v>
-      </c>
-      <c r="F589" s="33"/>
-      <c r="G589" s="33">
+        <v>478</v>
+      </c>
+      <c r="F601" s="33"/>
+      <c r="G601" s="33">
         <f>SUBTOTAL(103,Tabela5[CLASSIFICAÇÃO])</f>
-        <v>464</v>
-      </c>
-      <c r="H589" s="33">
+        <v>478</v>
+      </c>
+      <c r="H601" s="33">
         <f>SUBTOTAL(109,Tabela5[QUANTIDADE INSPEÇÕES])</f>
-        <v>464</v>
-      </c>
-      <c r="I589" s="33">
+        <v>478</v>
+      </c>
+      <c r="I601" s="33">
         <f>SUBTOTAL(103,Tabela5[TÉCNICO DE SEGURANÇA  APLICADOR])</f>
-        <v>464</v>
+        <v>478</v>
       </c>
     </row>
   </sheetData>
@@ -22141,79 +22821,79 @@
       <c r="I1" s="84"/>
     </row>
     <row r="2" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="85" t="s">
         <v>809</v>
       </c>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
+      <c r="B2" s="85"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
       <c r="F2" s="40" t="s">
         <v>824</v>
       </c>
-      <c r="G2" s="74" t="s">
+      <c r="G2" s="85" t="s">
         <v>820</v>
       </c>
-      <c r="H2" s="74"/>
+      <c r="H2" s="85"/>
       <c r="I2" s="34" t="s">
         <v>822</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="85" t="s">
         <v>810</v>
       </c>
-      <c r="B3" s="74"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
+      <c r="B3" s="85"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="85"/>
       <c r="F3" s="40" t="s">
         <v>823</v>
       </c>
-      <c r="G3" s="74" t="s">
+      <c r="G3" s="85" t="s">
         <v>821</v>
       </c>
-      <c r="H3" s="74"/>
+      <c r="H3" s="85"/>
       <c r="I3" s="22"/>
     </row>
     <row r="4" spans="1:9" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="105" t="s">
+      <c r="A4" s="82" t="s">
         <v>819</v>
       </c>
-      <c r="B4" s="106"/>
-      <c r="C4" s="106"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
-      <c r="F4" s="106"/>
-      <c r="G4" s="106"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
+      <c r="B4" s="83"/>
+      <c r="C4" s="83"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="83"/>
+      <c r="I4" s="83"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="102" t="s">
+      <c r="A5" s="79" t="s">
         <v>811</v>
       </c>
-      <c r="B5" s="103"/>
-      <c r="C5" s="103"/>
-      <c r="D5" s="103"/>
-      <c r="E5" s="103"/>
-      <c r="F5" s="103"/>
-      <c r="G5" s="103"/>
-      <c r="H5" s="103"/>
-      <c r="I5" s="104"/>
+      <c r="B5" s="80"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="80"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="81"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="99" t="s">
+      <c r="A6" s="76" t="s">
         <v>812</v>
       </c>
-      <c r="B6" s="100"/>
-      <c r="C6" s="100"/>
-      <c r="D6" s="100"/>
-      <c r="E6" s="100"/>
-      <c r="F6" s="100"/>
-      <c r="G6" s="100"/>
-      <c r="H6" s="100"/>
-      <c r="I6" s="101"/>
+      <c r="B6" s="77"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="77"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="78"/>
     </row>
     <row r="7" spans="1:9" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="53"/>
@@ -22254,16 +22934,16 @@
       <c r="I9" s="39"/>
     </row>
     <row r="10" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="95" t="s">
+      <c r="A10" s="86" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="95"/>
-      <c r="C10" s="95"/>
-      <c r="D10" s="95" t="s">
+      <c r="B10" s="86"/>
+      <c r="C10" s="86"/>
+      <c r="D10" s="86" t="s">
         <v>832</v>
       </c>
-      <c r="E10" s="95"/>
-      <c r="F10" s="95"/>
+      <c r="E10" s="86"/>
+      <c r="F10" s="86"/>
       <c r="G10" s="19" t="s">
         <v>641</v>
       </c>
@@ -22353,11 +23033,11 @@
       <c r="F16" s="48" t="s">
         <v>674</v>
       </c>
-      <c r="G16" s="95" t="s">
+      <c r="G16" s="86" t="s">
         <v>619</v>
       </c>
-      <c r="H16" s="95"/>
-      <c r="I16" s="95"/>
+      <c r="H16" s="86"/>
+      <c r="I16" s="86"/>
     </row>
     <row r="17" spans="1:9" ht="4.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="60"/>
@@ -22519,11 +23199,11 @@
       <c r="I27" s="61"/>
     </row>
     <row r="28" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="95" t="s">
+      <c r="A28" s="86" t="s">
         <v>831</v>
       </c>
-      <c r="B28" s="95"/>
-      <c r="C28" s="95"/>
+      <c r="B28" s="86"/>
+      <c r="C28" s="86"/>
       <c r="D28" s="46" t="s">
         <v>833</v>
       </c>
@@ -22586,11 +23266,11 @@
       <c r="F32" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="G32" s="95" t="s">
+      <c r="G32" s="86" t="s">
         <v>834</v>
       </c>
-      <c r="H32" s="95"/>
-      <c r="I32" s="95"/>
+      <c r="H32" s="86"/>
+      <c r="I32" s="86"/>
     </row>
     <row r="33" spans="1:9" ht="4.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="60"/>
@@ -22665,11 +23345,11 @@
       <c r="C38" s="48" t="s">
         <v>649</v>
       </c>
-      <c r="D38" s="95" t="s">
+      <c r="D38" s="86" t="s">
         <v>618</v>
       </c>
-      <c r="E38" s="95"/>
-      <c r="F38" s="95"/>
+      <c r="E38" s="86"/>
+      <c r="F38" s="86"/>
       <c r="G38" s="19" t="s">
         <v>642</v>
       </c>
@@ -22735,17 +23415,17 @@
       <c r="I43" s="39"/>
     </row>
     <row r="44" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="96" t="s">
+      <c r="A44" s="87" t="s">
         <v>846</v>
       </c>
-      <c r="B44" s="97"/>
-      <c r="C44" s="97"/>
-      <c r="D44" s="97"/>
-      <c r="E44" s="97"/>
-      <c r="F44" s="97"/>
-      <c r="G44" s="97"/>
-      <c r="H44" s="97"/>
-      <c r="I44" s="98"/>
+      <c r="B44" s="88"/>
+      <c r="C44" s="88"/>
+      <c r="D44" s="88"/>
+      <c r="E44" s="88"/>
+      <c r="F44" s="88"/>
+      <c r="G44" s="88"/>
+      <c r="H44" s="88"/>
+      <c r="I44" s="89"/>
     </row>
     <row r="45" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="90" t="s">
@@ -22796,34 +23476,34 @@
       <c r="I48" s="94"/>
     </row>
     <row r="49" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="87" t="s">
+      <c r="A49" s="101" t="s">
         <v>849</v>
       </c>
-      <c r="B49" s="87"/>
-      <c r="C49" s="87"/>
-      <c r="D49" s="87"/>
-      <c r="E49" s="87"/>
-      <c r="F49" s="87" t="s">
+      <c r="B49" s="101"/>
+      <c r="C49" s="101"/>
+      <c r="D49" s="101"/>
+      <c r="E49" s="101"/>
+      <c r="F49" s="101" t="s">
         <v>850</v>
       </c>
-      <c r="G49" s="87"/>
-      <c r="H49" s="87"/>
-      <c r="I49" s="87"/>
+      <c r="G49" s="101"/>
+      <c r="H49" s="101"/>
+      <c r="I49" s="101"/>
     </row>
     <row r="50" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>851</v>
       </c>
       <c r="B50" s="22"/>
-      <c r="C50" s="71"/>
-      <c r="D50" s="72"/>
-      <c r="E50" s="72"/>
-      <c r="F50" s="88" t="s">
+      <c r="C50" s="97"/>
+      <c r="D50" s="98"/>
+      <c r="E50" s="98"/>
+      <c r="F50" s="102" t="s">
         <v>851</v>
       </c>
-      <c r="G50" s="88"/>
-      <c r="H50" s="88"/>
-      <c r="I50" s="89"/>
+      <c r="G50" s="102"/>
+      <c r="H50" s="102"/>
+      <c r="I50" s="103"/>
     </row>
     <row r="51" spans="1:9" ht="4.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4"/>
@@ -22837,15 +23517,15 @@
         <v>851</v>
       </c>
       <c r="B52" s="22"/>
-      <c r="C52" s="75"/>
-      <c r="D52" s="76"/>
-      <c r="E52" s="76"/>
-      <c r="F52" s="85" t="s">
+      <c r="C52" s="99"/>
+      <c r="D52" s="100"/>
+      <c r="E52" s="100"/>
+      <c r="F52" s="95" t="s">
         <v>851</v>
       </c>
-      <c r="G52" s="85"/>
-      <c r="H52" s="85"/>
-      <c r="I52" s="86"/>
+      <c r="G52" s="95"/>
+      <c r="H52" s="95"/>
+      <c r="I52" s="96"/>
     </row>
     <row r="53" spans="1:9" ht="4.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4"/>
@@ -22859,15 +23539,15 @@
         <v>851</v>
       </c>
       <c r="B54" s="22"/>
-      <c r="C54" s="75"/>
-      <c r="D54" s="76"/>
-      <c r="E54" s="76"/>
-      <c r="F54" s="85" t="s">
+      <c r="C54" s="99"/>
+      <c r="D54" s="100"/>
+      <c r="E54" s="100"/>
+      <c r="F54" s="95" t="s">
         <v>851</v>
       </c>
-      <c r="G54" s="85"/>
-      <c r="H54" s="85"/>
-      <c r="I54" s="86"/>
+      <c r="G54" s="95"/>
+      <c r="H54" s="95"/>
+      <c r="I54" s="96"/>
     </row>
     <row r="55" spans="1:9" ht="4.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4"/>
@@ -22881,15 +23561,15 @@
         <v>851</v>
       </c>
       <c r="B56" s="22"/>
-      <c r="C56" s="75"/>
-      <c r="D56" s="76"/>
-      <c r="E56" s="76"/>
-      <c r="F56" s="85" t="s">
+      <c r="C56" s="99"/>
+      <c r="D56" s="100"/>
+      <c r="E56" s="100"/>
+      <c r="F56" s="95" t="s">
         <v>851</v>
       </c>
-      <c r="G56" s="85"/>
-      <c r="H56" s="85"/>
-      <c r="I56" s="86"/>
+      <c r="G56" s="95"/>
+      <c r="H56" s="95"/>
+      <c r="I56" s="96"/>
     </row>
     <row r="57" spans="1:9" ht="4.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4"/>
@@ -22903,15 +23583,15 @@
         <v>851</v>
       </c>
       <c r="B58" s="22"/>
-      <c r="C58" s="75"/>
-      <c r="D58" s="76"/>
-      <c r="E58" s="76"/>
-      <c r="F58" s="85" t="s">
+      <c r="C58" s="99"/>
+      <c r="D58" s="100"/>
+      <c r="E58" s="100"/>
+      <c r="F58" s="95" t="s">
         <v>851</v>
       </c>
-      <c r="G58" s="85"/>
-      <c r="H58" s="85"/>
-      <c r="I58" s="86"/>
+      <c r="G58" s="95"/>
+      <c r="H58" s="95"/>
+      <c r="I58" s="96"/>
     </row>
     <row r="59" spans="1:9" ht="4.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4"/>
@@ -22925,32 +23605,32 @@
         <v>851</v>
       </c>
       <c r="B60" s="22"/>
-      <c r="C60" s="75"/>
-      <c r="D60" s="76"/>
-      <c r="E60" s="76"/>
-      <c r="F60" s="85" t="s">
+      <c r="C60" s="99"/>
+      <c r="D60" s="100"/>
+      <c r="E60" s="100"/>
+      <c r="F60" s="95" t="s">
         <v>851</v>
       </c>
-      <c r="G60" s="85"/>
-      <c r="H60" s="85"/>
-      <c r="I60" s="86"/>
+      <c r="G60" s="95"/>
+      <c r="H60" s="95"/>
+      <c r="I60" s="96"/>
     </row>
     <row r="61" spans="1:9" ht="4.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="57"/>
       <c r="I61" s="39"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="87" t="s">
+      <c r="A62" s="101" t="s">
         <v>852</v>
       </c>
-      <c r="B62" s="87"/>
-      <c r="C62" s="87"/>
-      <c r="D62" s="87"/>
-      <c r="E62" s="87"/>
-      <c r="F62" s="87"/>
-      <c r="G62" s="87"/>
-      <c r="H62" s="87"/>
-      <c r="I62" s="87"/>
+      <c r="B62" s="101"/>
+      <c r="C62" s="101"/>
+      <c r="D62" s="101"/>
+      <c r="E62" s="101"/>
+      <c r="F62" s="101"/>
+      <c r="G62" s="101"/>
+      <c r="H62" s="101"/>
+      <c r="I62" s="101"/>
     </row>
     <row r="63" spans="1:9" ht="3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="57"/>
@@ -22961,9 +23641,9 @@
         <v>851</v>
       </c>
       <c r="B64" s="22"/>
-      <c r="C64" s="75"/>
-      <c r="D64" s="76"/>
-      <c r="E64" s="76"/>
+      <c r="C64" s="99"/>
+      <c r="D64" s="100"/>
+      <c r="E64" s="100"/>
       <c r="F64" s="50" t="s">
         <v>851</v>
       </c>
@@ -22979,9 +23659,9 @@
         <v>851</v>
       </c>
       <c r="B66" s="22"/>
-      <c r="C66" s="75"/>
-      <c r="D66" s="76"/>
-      <c r="E66" s="76"/>
+      <c r="C66" s="99"/>
+      <c r="D66" s="100"/>
+      <c r="E66" s="100"/>
       <c r="F66" s="50" t="s">
         <v>851</v>
       </c>
@@ -22997,9 +23677,9 @@
         <v>851</v>
       </c>
       <c r="B68" s="22"/>
-      <c r="C68" s="75"/>
-      <c r="D68" s="76"/>
-      <c r="E68" s="76"/>
+      <c r="C68" s="99"/>
+      <c r="D68" s="100"/>
+      <c r="E68" s="100"/>
       <c r="F68" s="50" t="s">
         <v>851</v>
       </c>
@@ -23010,39 +23690,39 @@
       <c r="I69" s="39"/>
     </row>
     <row r="70" spans="1:9" ht="1.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="77" t="s">
+      <c r="A70" s="104" t="s">
         <v>853</v>
       </c>
-      <c r="B70" s="78"/>
-      <c r="C70" s="78"/>
-      <c r="D70" s="78"/>
-      <c r="E70" s="78"/>
-      <c r="F70" s="78"/>
-      <c r="G70" s="78"/>
-      <c r="H70" s="78"/>
-      <c r="I70" s="79"/>
+      <c r="B70" s="105"/>
+      <c r="C70" s="105"/>
+      <c r="D70" s="105"/>
+      <c r="E70" s="105"/>
+      <c r="F70" s="105"/>
+      <c r="G70" s="105"/>
+      <c r="H70" s="105"/>
+      <c r="I70" s="106"/>
     </row>
     <row r="71" spans="1:9" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="80"/>
-      <c r="B71" s="78"/>
-      <c r="C71" s="78"/>
-      <c r="D71" s="78"/>
-      <c r="E71" s="78"/>
-      <c r="F71" s="78"/>
-      <c r="G71" s="78"/>
-      <c r="H71" s="78"/>
-      <c r="I71" s="79"/>
+      <c r="A71" s="107"/>
+      <c r="B71" s="105"/>
+      <c r="C71" s="105"/>
+      <c r="D71" s="105"/>
+      <c r="E71" s="105"/>
+      <c r="F71" s="105"/>
+      <c r="G71" s="105"/>
+      <c r="H71" s="105"/>
+      <c r="I71" s="106"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A72" s="81"/>
-      <c r="B72" s="82"/>
-      <c r="C72" s="82"/>
-      <c r="D72" s="82"/>
-      <c r="E72" s="82"/>
-      <c r="F72" s="82"/>
-      <c r="G72" s="82"/>
-      <c r="H72" s="82"/>
-      <c r="I72" s="83"/>
+      <c r="A72" s="108"/>
+      <c r="B72" s="109"/>
+      <c r="C72" s="109"/>
+      <c r="D72" s="109"/>
+      <c r="E72" s="109"/>
+      <c r="F72" s="109"/>
+      <c r="G72" s="109"/>
+      <c r="H72" s="109"/>
+      <c r="I72" s="110"/>
     </row>
     <row r="73" spans="1:9" ht="5.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="74" spans="1:9" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -23059,51 +23739,51 @@
       <c r="I74" s="84"/>
     </row>
     <row r="75" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="74" t="s">
+      <c r="A75" s="85" t="s">
         <v>809</v>
       </c>
-      <c r="B75" s="74"/>
-      <c r="C75" s="74"/>
-      <c r="D75" s="74"/>
-      <c r="E75" s="74"/>
+      <c r="B75" s="85"/>
+      <c r="C75" s="85"/>
+      <c r="D75" s="85"/>
+      <c r="E75" s="85"/>
       <c r="F75" s="40" t="s">
         <v>824</v>
       </c>
-      <c r="G75" s="74" t="s">
+      <c r="G75" s="85" t="s">
         <v>820</v>
       </c>
-      <c r="H75" s="74"/>
+      <c r="H75" s="85"/>
       <c r="I75" s="34" t="s">
         <v>822</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="74" t="s">
+      <c r="A76" s="85" t="s">
         <v>810</v>
       </c>
-      <c r="B76" s="74"/>
-      <c r="C76" s="74"/>
-      <c r="D76" s="74"/>
-      <c r="E76" s="74"/>
+      <c r="B76" s="85"/>
+      <c r="C76" s="85"/>
+      <c r="D76" s="85"/>
+      <c r="E76" s="85"/>
       <c r="F76" s="40" t="s">
         <v>823</v>
       </c>
-      <c r="G76" s="74" t="s">
+      <c r="G76" s="85" t="s">
         <v>821</v>
       </c>
-      <c r="H76" s="74"/>
+      <c r="H76" s="85"/>
       <c r="I76" s="22"/>
     </row>
     <row r="77" spans="1:9" ht="282.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="71"/>
-      <c r="B77" s="72"/>
-      <c r="C77" s="72"/>
-      <c r="D77" s="72"/>
-      <c r="E77" s="73"/>
-      <c r="F77" s="72"/>
-      <c r="G77" s="72"/>
-      <c r="H77" s="72"/>
-      <c r="I77" s="73"/>
+      <c r="A77" s="97"/>
+      <c r="B77" s="98"/>
+      <c r="C77" s="98"/>
+      <c r="D77" s="98"/>
+      <c r="E77" s="111"/>
+      <c r="F77" s="98"/>
+      <c r="G77" s="98"/>
+      <c r="H77" s="98"/>
+      <c r="I77" s="111"/>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" s="63" t="s">
@@ -23119,15 +23799,15 @@
       <c r="I78" s="39"/>
     </row>
     <row r="79" spans="1:9" ht="282.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="71"/>
-      <c r="B79" s="72"/>
-      <c r="C79" s="72"/>
-      <c r="D79" s="72"/>
-      <c r="E79" s="73"/>
-      <c r="F79" s="72"/>
-      <c r="G79" s="72"/>
-      <c r="H79" s="72"/>
-      <c r="I79" s="73"/>
+      <c r="A79" s="97"/>
+      <c r="B79" s="98"/>
+      <c r="C79" s="98"/>
+      <c r="D79" s="98"/>
+      <c r="E79" s="111"/>
+      <c r="F79" s="98"/>
+      <c r="G79" s="98"/>
+      <c r="H79" s="98"/>
+      <c r="I79" s="111"/>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" s="63" t="s">
@@ -23143,15 +23823,15 @@
       <c r="I80" s="39"/>
     </row>
     <row r="81" spans="1:9" ht="282.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="71"/>
-      <c r="B81" s="72"/>
-      <c r="C81" s="72"/>
-      <c r="D81" s="72"/>
-      <c r="E81" s="73"/>
-      <c r="F81" s="72"/>
-      <c r="G81" s="72"/>
-      <c r="H81" s="72"/>
-      <c r="I81" s="73"/>
+      <c r="A81" s="97"/>
+      <c r="B81" s="98"/>
+      <c r="C81" s="98"/>
+      <c r="D81" s="98"/>
+      <c r="E81" s="111"/>
+      <c r="F81" s="98"/>
+      <c r="G81" s="98"/>
+      <c r="H81" s="98"/>
+      <c r="I81" s="111"/>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" s="63" t="s">
@@ -23170,40 +23850,12 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="A6:I6"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A44:I44"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="A45:I45"/>
-    <mergeCell ref="A46:I46"/>
-    <mergeCell ref="A47:I47"/>
-    <mergeCell ref="A48:I48"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="F56:I56"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="A49:E49"/>
-    <mergeCell ref="F49:I49"/>
-    <mergeCell ref="F50:I50"/>
-    <mergeCell ref="F52:I52"/>
-    <mergeCell ref="F54:I54"/>
-    <mergeCell ref="F58:I58"/>
-    <mergeCell ref="F60:I60"/>
-    <mergeCell ref="A62:I62"/>
-    <mergeCell ref="C58:E58"/>
-    <mergeCell ref="C60:E60"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="F77:I77"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="F79:I79"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="F81:I81"/>
     <mergeCell ref="A75:E75"/>
     <mergeCell ref="G75:H75"/>
     <mergeCell ref="A76:E76"/>
@@ -23213,12 +23865,40 @@
     <mergeCell ref="C68:E68"/>
     <mergeCell ref="A70:I72"/>
     <mergeCell ref="A74:I74"/>
-    <mergeCell ref="A77:E77"/>
-    <mergeCell ref="F77:I77"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="F79:I79"/>
-    <mergeCell ref="A81:E81"/>
-    <mergeCell ref="F81:I81"/>
+    <mergeCell ref="F58:I58"/>
+    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="A62:I62"/>
+    <mergeCell ref="C58:E58"/>
+    <mergeCell ref="C60:E60"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="F49:I49"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="F52:I52"/>
+    <mergeCell ref="F54:I54"/>
+    <mergeCell ref="F56:I56"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="A45:I45"/>
+    <mergeCell ref="A46:I46"/>
+    <mergeCell ref="A47:I47"/>
+    <mergeCell ref="A48:I48"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A44:I44"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G3:H3"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" scale="73" fitToHeight="0" orientation="portrait" r:id="rId1"/>
@@ -23228,22 +23908,169 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA1CDF08-A88B-4229-8CCC-EBDF483B0FB1}">
-  <dimension ref="A1:A808"/>
+  <dimension ref="A1:C809"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.5546875" customWidth="1"/>
+    <col min="2" max="2" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="19" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="770" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="796" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="800" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="804" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="806" ht="31.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="808" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="112" t="s">
+        <v>986</v>
+      </c>
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+    </row>
+    <row r="2" spans="1:3" s="19" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A2" s="67" t="s">
+        <v>983</v>
+      </c>
+      <c r="B2" s="67" t="s">
+        <v>984</v>
+      </c>
+      <c r="C2" s="67" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="22" t="s">
+        <v>971</v>
+      </c>
+      <c r="B3" s="69">
+        <v>295</v>
+      </c>
+      <c r="C3" s="69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="22" t="s">
+        <v>972</v>
+      </c>
+      <c r="B4" s="69">
+        <v>260</v>
+      </c>
+      <c r="C4" s="69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="22" t="s">
+        <v>973</v>
+      </c>
+      <c r="B5" s="69">
+        <v>410</v>
+      </c>
+      <c r="C5" s="69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="22" t="s">
+        <v>974</v>
+      </c>
+      <c r="B6" s="69">
+        <v>196</v>
+      </c>
+      <c r="C6" s="69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="22" t="s">
+        <v>975</v>
+      </c>
+      <c r="B7" s="69">
+        <v>301</v>
+      </c>
+      <c r="C7" s="69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="22" t="s">
+        <v>976</v>
+      </c>
+      <c r="B8" s="69"/>
+      <c r="C8" s="69"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="22" t="s">
+        <v>977</v>
+      </c>
+      <c r="B9" s="69"/>
+      <c r="C9" s="69"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="22" t="s">
+        <v>978</v>
+      </c>
+      <c r="B10" s="69"/>
+      <c r="C10" s="69"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="22" t="s">
+        <v>979</v>
+      </c>
+      <c r="B11" s="69"/>
+      <c r="C11" s="69"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="22" t="s">
+        <v>980</v>
+      </c>
+      <c r="B12" s="69"/>
+      <c r="C12" s="69"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="22" t="s">
+        <v>981</v>
+      </c>
+      <c r="B13" s="69"/>
+      <c r="C13" s="69"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="22" t="s">
+        <v>982</v>
+      </c>
+      <c r="B14" s="69"/>
+      <c r="C14" s="69"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="68" t="s">
+        <v>513</v>
+      </c>
+      <c r="B15" s="14">
+        <f>SUBTOTAL(109,Tabela1[QUANTIDADE
+DDS])</f>
+        <v>1462</v>
+      </c>
+      <c r="C15" s="70">
+        <f>SUBTOTAL(109,Tabela1[QUANTIDADE CAMPANHAS])</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="771" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="797" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="801" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="805" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="807" ht="31.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="809" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" scale="78" orientation="portrait" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="192" max="16383" man="1"/>
+    <brk id="193" max="16383" man="1"/>
   </rowBreaks>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -23708,15 +24535,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100547A52244DFCC9488E5B66DD2EAE55E4" ma:contentTypeVersion="18" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="936731ce312a4e8ead8ad97bcf9b70b3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="84c92d79-736b-434d-a6de-4a5b6bb0f72c" xmlns:ns3="de022bf3-4aff-41f6-a825-e7793343a5a1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fdc18dfd3044d82758640420f33afd2f" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -23972,6 +24790,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -23994,14 +24821,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B012FB3-DD8F-4CAA-8133-13B526BC83FE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A86827D-F12F-464B-8BAA-37C9BCDB40FD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -24021,6 +24840,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B012FB3-DD8F-4CAA-8133-13B526BC83FE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F09844F-2517-46B1-8B13-9F10D5CE2474}">
   <ds:schemaRefs>

--- a/Planilha de controle de segurança do trabalho.xlsx
+++ b/Planilha de controle de segurança do trabalho.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://enopsengenharia.sharepoint.com/sites/sabespIntegra6a/Documentos Compartilhados/04 QSMS/03. SESMT/01 - NR 02 INSPEÇÃO/20- INSPEÇÕES DE SEGURANÇA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Integra 6\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3323" documentId="13_ncr:1_{95D3C810-1CBF-4943-A4BA-161B382C5A82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C229EBD0-F41C-4DB5-951F-656B2869D771}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E3B8F7D-63AE-4B73-B6D6-824A91B908FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="907" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3240" uniqueCount="1009">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3240" uniqueCount="1008">
   <si>
     <t>DATA</t>
   </si>
@@ -3257,9 +3257,6 @@
   </si>
   <si>
     <t>CT Machado</t>
-  </si>
-  <si>
-    <t>Pendente</t>
   </si>
   <si>
     <t>Caminhão Basculante Placa FOJ3H13 com pneus carecas (risco de perda de tração), dificuldade de engate da 1ª mudança e assento da cabine secundária com encosto partido.</t>
@@ -4356,6 +4353,90 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4380,90 +4461,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4472,357 +4469,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="33">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="20"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF99CCFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="20"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF99CCFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="20"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF99CCFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="20"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF99CCFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="20"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF99CCFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="20"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF99CCFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="20"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF99CCFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="20"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF99CCFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="20"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF99CCFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -4965,8 +4611,30 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF99CCFF"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -4979,12 +4647,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -5011,8 +4673,30 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF99CCFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -5025,12 +4709,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -5057,6 +4735,45 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF99CCFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -5077,6 +4794,45 @@
         <horizontal style="thin">
           <color indexed="64"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF99CCFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -5103,6 +4859,107 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF99CCFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF99CCFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -5126,6 +4983,45 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF99CCFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -5146,6 +5042,107 @@
         <horizontal style="thin">
           <color indexed="64"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF99CCFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF99CCFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -6520,31 +6517,37 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{40B8F08B-7B44-41C0-9727-D6D3A9E412E0}" name="Tabela5" displayName="Tabela5" ref="A1:I601" totalsRowCount="1" headerRowDxfId="32" totalsRowDxfId="29" headerRowBorderDxfId="31" tableBorderDxfId="30" totalsRowBorderDxfId="28">
-  <autoFilter ref="A1:I600" xr:uid="{E025FF00-BBD4-447E-8A48-23C9F77BFED5}"/>
+  <autoFilter ref="A1:I600" xr:uid="{E025FF00-BBD4-447E-8A48-23C9F77BFED5}">
+    <filterColumn colId="0">
+      <filters>
+        <dateGroupItem year="2026" month="6" dateTimeGrouping="month"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{0B057C41-AC10-4F67-ABDF-C4EAAD7F8F2D}" name="DATA" totalsRowLabel="Total" dataDxfId="27" totalsRowDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{8A16FC14-C82C-43F3-BF15-DD9697EAFA57}" name="LOCAL" totalsRowFunction="count" dataDxfId="26" totalsRowDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{BE44A91D-706C-471A-8BDF-D29BE353B2BC}" name="ENCARREGADO OU LIDER DE EQUIPE" totalsRowFunction="count" dataDxfId="25" totalsRowDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{00DF3209-2326-42C6-8699-CDCB435BB747}" name="QUANTIDADE DESVIOS" totalsRowFunction="custom" dataDxfId="24" totalsRowDxfId="5">
+    <tableColumn id="1" xr3:uid="{0B057C41-AC10-4F67-ABDF-C4EAAD7F8F2D}" name="DATA" totalsRowLabel="Total" dataDxfId="27" totalsRowDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{8A16FC14-C82C-43F3-BF15-DD9697EAFA57}" name="LOCAL" totalsRowFunction="count" dataDxfId="25" totalsRowDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{BE44A91D-706C-471A-8BDF-D29BE353B2BC}" name="ENCARREGADO OU LIDER DE EQUIPE" totalsRowFunction="count" dataDxfId="23" totalsRowDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{00DF3209-2326-42C6-8699-CDCB435BB747}" name="QUANTIDADE DESVIOS" totalsRowFunction="custom" dataDxfId="21" totalsRowDxfId="20">
       <totalsRowFormula>SUM(D2:D600)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{30D85C45-EA9B-41E7-AB22-9C5FACAC4A3A}" name="DESCRIÇÃO" totalsRowFunction="count" dataDxfId="23" totalsRowDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{AFDBCEF9-AD84-4AF6-A78C-ADD27299479E}" name="STATUS" dataDxfId="22" totalsRowDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{F60BA8D5-B8CC-4468-B665-77CD1CD38176}" name="CLASSIFICAÇÃO" totalsRowFunction="count" dataDxfId="21" totalsRowDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{EE5A703F-BAA2-4AAB-A2E6-C2D3F12BF651}" name="QUANTIDADE INSPEÇÕES" totalsRowFunction="sum" dataDxfId="20" totalsRowDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{6AC59D75-1383-42D7-8A9B-B4B44FEEFFC1}" name="TÉCNICO DE SEGURANÇA  APLICADOR" totalsRowFunction="count" dataDxfId="19" totalsRowDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{30D85C45-EA9B-41E7-AB22-9C5FACAC4A3A}" name="DESCRIÇÃO" totalsRowFunction="count" dataDxfId="19" totalsRowDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{AFDBCEF9-AD84-4AF6-A78C-ADD27299479E}" name="STATUS" dataDxfId="17" totalsRowDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{F60BA8D5-B8CC-4468-B665-77CD1CD38176}" name="CLASSIFICAÇÃO" totalsRowFunction="count" dataDxfId="15" totalsRowDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{EE5A703F-BAA2-4AAB-A2E6-C2D3F12BF651}" name="QUANTIDADE INSPEÇÕES" totalsRowFunction="sum" dataDxfId="13" totalsRowDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{6AC59D75-1383-42D7-8A9B-B4B44FEEFFC1}" name="TÉCNICO DE SEGURANÇA  APLICADOR" totalsRowFunction="count" dataDxfId="11" totalsRowDxfId="10"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{952762BD-56C9-484C-9E77-FCE66DB4640E}" name="Tabela1" displayName="Tabela1" ref="A2:C15" totalsRowCount="1" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16" totalsRowBorderDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{952762BD-56C9-484C-9E77-FCE66DB4640E}" name="Tabela1" displayName="Tabela1" ref="A2:C15" totalsRowCount="1" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7" totalsRowBorderDxfId="6">
   <autoFilter ref="A2:C14" xr:uid="{952762BD-56C9-484C-9E77-FCE66DB4640E}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{41C10721-F7E4-4BCF-A498-D3EC0835BFEA}" name="MÊS" totalsRowLabel="Total" dataDxfId="14" totalsRowDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{0FEB78B2-7C7C-418B-BF73-42BE97E3E034}" name="QUANTIDADE_x000a_DDS" totalsRowFunction="sum" dataDxfId="12" totalsRowDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{7B989E42-8D41-444B-9D85-834753A5661B}" name="QUANTIDADE CAMPANHAS" totalsRowFunction="sum" dataDxfId="10" totalsRowDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{41C10721-F7E4-4BCF-A498-D3EC0835BFEA}" name="MÊS" totalsRowLabel="Total" dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{0FEB78B2-7C7C-418B-BF73-42BE97E3E034}" name="QUANTIDADE_x000a_DDS" totalsRowFunction="sum" dataDxfId="3" totalsRowDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{7B989E42-8D41-444B-9D85-834753A5661B}" name="QUANTIDADE CAMPANHAS" totalsRowFunction="sum" dataDxfId="1" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6984,7 +6987,7 @@
       <c r="W1" s="74"/>
       <c r="X1" s="75"/>
     </row>
-    <row r="2" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17">
         <v>45780</v>
       </c>
@@ -7041,7 +7044,7 @@
       </c>
       <c r="X2" s="72"/>
     </row>
-    <row r="3" spans="1:24" ht="48" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" ht="48" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17">
         <v>45782</v>
       </c>
@@ -7112,7 +7115,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="36" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17">
         <v>45784</v>
       </c>
@@ -7183,7 +7186,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="36" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17">
         <v>45784</v>
       </c>
@@ -7254,7 +7257,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" ht="50.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17">
         <v>45789</v>
       </c>
@@ -7325,7 +7328,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17">
         <v>45789</v>
       </c>
@@ -7388,7 +7391,7 @@
       <c r="W7" s="35"/>
       <c r="X7" s="36"/>
     </row>
-    <row r="8" spans="1:24" ht="24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17">
         <v>45790</v>
       </c>
@@ -7447,7 +7450,7 @@
       <c r="W8" s="35"/>
       <c r="X8" s="36"/>
     </row>
-    <row r="9" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="17">
         <v>45792</v>
       </c>
@@ -7506,7 +7509,7 @@
       <c r="W9" s="35"/>
       <c r="X9" s="36"/>
     </row>
-    <row r="10" spans="1:24" ht="24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17">
         <v>45798</v>
       </c>
@@ -7557,7 +7560,7 @@
       <c r="W10" s="35"/>
       <c r="X10" s="36"/>
     </row>
-    <row r="11" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="17">
         <v>45798</v>
       </c>
@@ -7586,7 +7589,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17">
         <v>45798</v>
       </c>
@@ -7615,7 +7618,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="17">
         <v>45800</v>
       </c>
@@ -7644,7 +7647,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="17">
         <v>45803</v>
       </c>
@@ -7673,7 +7676,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17">
         <v>45804</v>
       </c>
@@ -7702,7 +7705,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="17">
         <v>45805</v>
       </c>
@@ -7731,7 +7734,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="17">
         <v>45818</v>
       </c>
@@ -7760,7 +7763,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="17">
         <v>45818</v>
       </c>
@@ -7789,7 +7792,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="17">
         <v>45818</v>
       </c>
@@ -7818,7 +7821,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17">
         <v>45823</v>
       </c>
@@ -7847,7 +7850,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="17">
         <v>45829</v>
       </c>
@@ -7876,7 +7879,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="17">
         <v>45832</v>
       </c>
@@ -7905,7 +7908,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17">
         <v>45832</v>
       </c>
@@ -7934,7 +7937,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="17">
         <v>45832</v>
       </c>
@@ -7963,7 +7966,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="17">
         <v>45832</v>
       </c>
@@ -7992,7 +7995,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="17">
         <v>45833</v>
       </c>
@@ -8021,7 +8024,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="17">
         <v>45835</v>
       </c>
@@ -8050,7 +8053,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="201.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="20">
         <v>45842</v>
       </c>
@@ -8079,7 +8082,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="20">
         <v>45853</v>
       </c>
@@ -8108,7 +8111,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="20">
         <v>45853</v>
       </c>
@@ -8137,7 +8140,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="20">
         <v>45854</v>
       </c>
@@ -8166,7 +8169,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20">
         <v>45855</v>
       </c>
@@ -8195,7 +8198,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="20">
         <v>45859</v>
       </c>
@@ -8224,7 +8227,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="20">
         <v>45860</v>
       </c>
@@ -8253,7 +8256,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="17">
         <v>45875</v>
       </c>
@@ -8282,7 +8285,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="17">
         <v>45878</v>
       </c>
@@ -8311,7 +8314,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="17">
         <v>45890</v>
       </c>
@@ -8340,7 +8343,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="17">
         <v>45890</v>
       </c>
@@ -8369,7 +8372,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="17">
         <v>45891</v>
       </c>
@@ -8398,7 +8401,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="17">
         <v>45891</v>
       </c>
@@ -8427,7 +8430,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="17">
         <v>45891</v>
       </c>
@@ -8456,7 +8459,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="17">
         <v>45893</v>
       </c>
@@ -8485,7 +8488,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="17">
         <v>45898</v>
       </c>
@@ -8514,7 +8517,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="20">
         <v>45901</v>
       </c>
@@ -8543,7 +8546,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="20">
         <v>45902</v>
       </c>
@@ -8572,7 +8575,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="20">
         <v>45903</v>
       </c>
@@ -8601,7 +8604,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="20">
         <v>45903</v>
       </c>
@@ -8630,7 +8633,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="20">
         <v>45903</v>
       </c>
@@ -8659,7 +8662,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="20">
         <v>45904</v>
       </c>
@@ -8688,7 +8691,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="20">
         <v>45904</v>
       </c>
@@ -8717,7 +8720,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="20">
         <v>45906</v>
       </c>
@@ -8746,7 +8749,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="20">
         <v>45907</v>
       </c>
@@ -8775,7 +8778,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="20">
         <v>45910</v>
       </c>
@@ -8804,7 +8807,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="20">
         <v>45910</v>
       </c>
@@ -8833,7 +8836,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="20">
         <v>45910</v>
       </c>
@@ -8862,7 +8865,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="20">
         <v>45915</v>
       </c>
@@ -8891,7 +8894,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="20">
         <v>45915</v>
       </c>
@@ -8920,7 +8923,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="20">
         <v>45917</v>
       </c>
@@ -8949,7 +8952,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="20">
         <v>45917</v>
       </c>
@@ -8978,7 +8981,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="20">
         <v>45919</v>
       </c>
@@ -9007,7 +9010,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="20">
         <v>45921</v>
       </c>
@@ -9036,7 +9039,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" ht="40.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="20">
         <v>45923</v>
       </c>
@@ -9065,7 +9068,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="20">
         <v>45925</v>
       </c>
@@ -9094,7 +9097,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="20">
         <v>45925</v>
       </c>
@@ -9123,7 +9126,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="20">
         <v>45925</v>
       </c>
@@ -9152,7 +9155,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="20">
         <v>45930</v>
       </c>
@@ -9181,7 +9184,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="20">
         <v>45930</v>
       </c>
@@ -9210,7 +9213,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" ht="33.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="20">
         <v>45930</v>
       </c>
@@ -9239,7 +9242,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="20">
         <v>45934</v>
       </c>
@@ -9268,7 +9271,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="20">
         <v>45938</v>
       </c>
@@ -9297,7 +9300,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="20">
         <v>45944</v>
       </c>
@@ -9326,7 +9329,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="20">
         <v>45944</v>
       </c>
@@ -9355,7 +9358,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="20">
         <v>45944</v>
       </c>
@@ -9384,7 +9387,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="20">
         <v>45946</v>
       </c>
@@ -9413,7 +9416,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="20">
         <v>45948</v>
       </c>
@@ -9442,7 +9445,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="20">
         <v>45951</v>
       </c>
@@ -9471,7 +9474,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="20">
         <v>45952</v>
       </c>
@@ -9500,7 +9503,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="20">
         <v>45966</v>
       </c>
@@ -9529,7 +9532,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="20">
         <v>45971</v>
       </c>
@@ -9558,7 +9561,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="20">
         <v>45975</v>
       </c>
@@ -9587,7 +9590,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="20">
         <v>45979</v>
       </c>
@@ -9616,7 +9619,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="20">
         <v>45985</v>
       </c>
@@ -9645,7 +9648,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="20">
         <v>45986</v>
       </c>
@@ -9674,7 +9677,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="20">
         <v>45988</v>
       </c>
@@ -9703,7 +9706,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="20">
         <v>46001</v>
       </c>
@@ -9732,7 +9735,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" ht="18.600000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="20">
         <v>46002</v>
       </c>
@@ -9761,7 +9764,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="20">
         <v>46002</v>
       </c>
@@ -9790,7 +9793,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="20">
         <v>46002</v>
       </c>
@@ -9819,7 +9822,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="20">
         <v>46003</v>
       </c>
@@ -9848,7 +9851,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="20">
         <v>46004</v>
       </c>
@@ -9877,7 +9880,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="20">
         <v>46006</v>
       </c>
@@ -9906,7 +9909,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="20">
         <v>46007</v>
       </c>
@@ -9935,7 +9938,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="20">
         <v>46007</v>
       </c>
@@ -9964,7 +9967,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="20">
         <v>46007</v>
       </c>
@@ -9993,7 +9996,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="20">
         <v>46008</v>
       </c>
@@ -10022,7 +10025,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="20">
         <v>46009</v>
       </c>
@@ -10051,7 +10054,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="20">
         <v>46009</v>
       </c>
@@ -10080,7 +10083,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="20">
         <v>46009</v>
       </c>
@@ -10109,7 +10112,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="20">
         <v>46013</v>
       </c>
@@ -10138,7 +10141,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="20">
         <v>46020</v>
       </c>
@@ -10167,7 +10170,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="20">
         <v>46020</v>
       </c>
@@ -10196,7 +10199,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="20">
         <v>46025</v>
       </c>
@@ -10225,7 +10228,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="20">
         <v>46028</v>
       </c>
@@ -10254,7 +10257,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="20">
         <v>46028</v>
       </c>
@@ -10283,7 +10286,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="20">
         <v>46029</v>
       </c>
@@ -10312,7 +10315,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="20">
         <v>46030</v>
       </c>
@@ -10341,7 +10344,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="20">
         <v>46030</v>
       </c>
@@ -10370,7 +10373,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="20">
         <v>46031</v>
       </c>
@@ -10399,7 +10402,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="20">
         <v>46034</v>
       </c>
@@ -10428,7 +10431,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="20">
         <v>46034</v>
       </c>
@@ -10457,7 +10460,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="20">
         <v>46034</v>
       </c>
@@ -10486,7 +10489,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="20">
         <v>46034</v>
       </c>
@@ -10515,7 +10518,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="20">
         <v>46035</v>
       </c>
@@ -10544,7 +10547,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="20">
         <v>46035</v>
       </c>
@@ -10573,7 +10576,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="20">
         <v>46035</v>
       </c>
@@ -10602,7 +10605,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="20">
         <v>46036</v>
       </c>
@@ -10631,7 +10634,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="20">
         <v>46036</v>
       </c>
@@ -10660,7 +10663,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="20">
         <v>46036</v>
       </c>
@@ -10689,7 +10692,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="20">
         <v>46036</v>
       </c>
@@ -10718,7 +10721,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="20">
         <v>46037</v>
       </c>
@@ -10747,7 +10750,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="20">
         <v>46038</v>
       </c>
@@ -10776,7 +10779,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="20">
         <v>46038</v>
       </c>
@@ -10805,7 +10808,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="20">
         <v>46039</v>
       </c>
@@ -10834,7 +10837,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="20">
         <v>46039</v>
       </c>
@@ -10863,7 +10866,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="20">
         <v>46041</v>
       </c>
@@ -10892,7 +10895,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="20">
         <v>46042</v>
       </c>
@@ -10921,7 +10924,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="20">
         <v>46043</v>
       </c>
@@ -10950,7 +10953,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="20">
         <v>46043</v>
       </c>
@@ -10979,7 +10982,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="20">
         <v>46043</v>
       </c>
@@ -11008,7 +11011,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="20">
         <v>46043</v>
       </c>
@@ -11037,7 +11040,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="20">
         <v>46044</v>
       </c>
@@ -11066,7 +11069,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="20">
         <v>46044</v>
       </c>
@@ -11095,7 +11098,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="20">
         <v>46045</v>
       </c>
@@ -11124,7 +11127,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="20">
         <v>46046</v>
       </c>
@@ -11153,7 +11156,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="20">
         <v>46048</v>
       </c>
@@ -11182,7 +11185,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="20">
         <v>46056</v>
       </c>
@@ -11211,7 +11214,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="20">
         <v>46056</v>
       </c>
@@ -11240,7 +11243,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" ht="19.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="20">
         <v>46057</v>
       </c>
@@ -11269,7 +11272,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="20">
         <v>46058</v>
       </c>
@@ -11298,7 +11301,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9" ht="20.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="20">
         <v>46058</v>
       </c>
@@ -11327,7 +11330,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="20">
         <v>46058</v>
       </c>
@@ -11356,7 +11359,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="20">
         <v>46058</v>
       </c>
@@ -11385,7 +11388,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="20">
         <v>46062</v>
       </c>
@@ -11414,7 +11417,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="20">
         <v>46062</v>
       </c>
@@ -11443,7 +11446,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="20">
         <v>46064</v>
       </c>
@@ -11472,7 +11475,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="20">
         <v>46064</v>
       </c>
@@ -11501,7 +11504,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="147" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="20">
         <v>46064</v>
       </c>
@@ -11530,7 +11533,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="20">
         <v>46064</v>
       </c>
@@ -11559,7 +11562,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="20">
         <v>46065</v>
       </c>
@@ -11588,7 +11591,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="20">
         <v>46065</v>
       </c>
@@ -11617,7 +11620,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="20">
         <v>46066</v>
       </c>
@@ -11646,7 +11649,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="20">
         <v>46067</v>
       </c>
@@ -11675,7 +11678,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="153" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:9" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="20">
         <v>46067</v>
       </c>
@@ -11704,7 +11707,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="20">
         <v>46068</v>
       </c>
@@ -11733,7 +11736,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="20">
         <v>46072</v>
       </c>
@@ -11762,7 +11765,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="20">
         <v>46072</v>
       </c>
@@ -11791,7 +11794,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="20">
         <v>46073</v>
       </c>
@@ -11820,7 +11823,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="20">
         <v>46085</v>
       </c>
@@ -11849,7 +11852,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="20">
         <v>46085</v>
       </c>
@@ -11878,7 +11881,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="20">
         <v>46094</v>
       </c>
@@ -11907,7 +11910,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="161" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="20">
         <v>46097</v>
       </c>
@@ -11936,7 +11939,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="162" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:9" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="20">
         <v>46098</v>
       </c>
@@ -11965,7 +11968,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="163" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="20">
         <v>46099</v>
       </c>
@@ -11994,7 +11997,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="164" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="20">
         <v>46099</v>
       </c>
@@ -12023,7 +12026,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="20">
         <v>46104</v>
       </c>
@@ -12052,7 +12055,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="20">
         <v>46104</v>
       </c>
@@ -12081,7 +12084,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:9" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="20">
         <v>46105</v>
       </c>
@@ -12110,7 +12113,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="168" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:9" ht="17.399999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="20">
         <v>46106</v>
       </c>
@@ -12139,7 +12142,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="20">
         <v>46106</v>
       </c>
@@ -12168,7 +12171,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="170" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:9" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="20">
         <v>46106</v>
       </c>
@@ -12197,7 +12200,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="171" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:9" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="20">
         <v>46107</v>
       </c>
@@ -12226,7 +12229,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="172" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:9" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="20">
         <v>46108</v>
       </c>
@@ -12255,7 +12258,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="20">
         <v>46108</v>
       </c>
@@ -12284,7 +12287,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="174" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:9" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="20">
         <v>46108</v>
       </c>
@@ -12313,7 +12316,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="20">
         <v>46113</v>
       </c>
@@ -12342,7 +12345,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:9" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="20">
         <v>46113</v>
       </c>
@@ -12371,7 +12374,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="177" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="20">
         <v>46114</v>
       </c>
@@ -12400,7 +12403,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="178" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="20">
         <v>46118</v>
       </c>
@@ -12429,7 +12432,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="179" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="20">
         <v>46118</v>
       </c>
@@ -12458,7 +12461,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="20">
         <v>46118</v>
       </c>
@@ -12487,7 +12490,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="181" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="20">
         <v>46119</v>
       </c>
@@ -12516,7 +12519,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="182" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="20">
         <v>46119</v>
       </c>
@@ -12545,7 +12548,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="20">
         <v>46119</v>
       </c>
@@ -12574,7 +12577,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="184" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="20">
         <v>46119</v>
       </c>
@@ -12603,7 +12606,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="185" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="20">
         <v>46119</v>
       </c>
@@ -12632,7 +12635,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="186" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="20">
         <v>46120</v>
       </c>
@@ -12661,7 +12664,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="20">
         <v>46120</v>
       </c>
@@ -12690,7 +12693,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="188" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="20">
         <v>46120</v>
       </c>
@@ -12719,7 +12722,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="189" spans="1:9" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9" ht="13.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="20">
         <v>46120</v>
       </c>
@@ -12748,7 +12751,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="190" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="20">
         <v>46121</v>
       </c>
@@ -12777,7 +12780,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="20">
         <v>46121</v>
       </c>
@@ -12806,7 +12809,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="192" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="20">
         <v>46121</v>
       </c>
@@ -12835,7 +12838,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="20">
         <v>46121</v>
       </c>
@@ -12864,7 +12867,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="194" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="20">
         <v>46121</v>
       </c>
@@ -12893,7 +12896,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="195" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="20">
         <v>46121</v>
       </c>
@@ -12922,7 +12925,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="20">
         <v>46121</v>
       </c>
@@ -12951,7 +12954,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="197" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="20">
         <v>46122</v>
       </c>
@@ -12980,7 +12983,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="198" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="20">
         <v>46122</v>
       </c>
@@ -13009,7 +13012,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="199" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="17">
         <v>46122</v>
       </c>
@@ -13038,7 +13041,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="17">
         <v>46123</v>
       </c>
@@ -13067,7 +13070,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="17">
         <v>46123</v>
       </c>
@@ -13096,7 +13099,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="17">
         <v>46123</v>
       </c>
@@ -13125,7 +13128,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="17">
         <v>46123</v>
       </c>
@@ -13154,7 +13157,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="204" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="17">
         <v>46124</v>
       </c>
@@ -13183,7 +13186,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="205" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="17">
         <v>46124</v>
       </c>
@@ -13212,7 +13215,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="206" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="17">
         <v>46124</v>
       </c>
@@ -13241,7 +13244,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="17">
         <v>46124</v>
       </c>
@@ -13270,7 +13273,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="208" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:9" ht="16.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="17">
         <v>46125</v>
       </c>
@@ -13299,7 +13302,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="17">
         <v>46125</v>
       </c>
@@ -13328,7 +13331,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="210" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="17">
         <v>46125</v>
       </c>
@@ -13357,7 +13360,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="17">
         <v>46125</v>
       </c>
@@ -13386,7 +13389,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="212" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:9" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="17">
         <v>46125</v>
       </c>
@@ -13415,7 +13418,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="17">
         <v>46125</v>
       </c>
@@ -13444,7 +13447,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="17">
         <v>46125</v>
       </c>
@@ -13473,7 +13476,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="17">
         <v>46125</v>
       </c>
@@ -13502,7 +13505,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="17">
         <v>46126</v>
       </c>
@@ -13531,7 +13534,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="217" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" s="17">
         <v>46126</v>
       </c>
@@ -13560,7 +13563,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="17">
         <v>46126</v>
       </c>
@@ -13589,7 +13592,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="219" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="17">
         <v>46126</v>
       </c>
@@ -13618,7 +13621,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="220" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="17">
         <v>46126</v>
       </c>
@@ -13647,7 +13650,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="221" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="17">
         <v>46126</v>
       </c>
@@ -13676,7 +13679,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" s="17">
         <v>46126</v>
       </c>
@@ -13705,7 +13708,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="223" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="17">
         <v>46127</v>
       </c>
@@ -13734,7 +13737,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="224" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="17">
         <v>46127</v>
       </c>
@@ -13763,7 +13766,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="225" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="17">
         <v>46127</v>
       </c>
@@ -13792,7 +13795,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="226" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="17">
         <v>46128</v>
       </c>
@@ -13821,7 +13824,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="227" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="20">
         <v>46128</v>
       </c>
@@ -13850,7 +13853,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="228" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="17">
         <v>46128</v>
       </c>
@@ -13879,7 +13882,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="229" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="17">
         <v>46128</v>
       </c>
@@ -13908,7 +13911,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="230" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:9" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="17">
         <v>46128</v>
       </c>
@@ -13937,7 +13940,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="231" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:9" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="17">
         <v>46128</v>
       </c>
@@ -13966,7 +13969,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="232" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="17">
         <v>46130</v>
       </c>
@@ -13995,7 +13998,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="17">
         <v>46130</v>
       </c>
@@ -14024,7 +14027,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="234" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:9" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="17">
         <v>46130</v>
       </c>
@@ -14053,7 +14056,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="235" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="17">
         <v>46130</v>
       </c>
@@ -14082,7 +14085,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="236" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="17">
         <v>46132</v>
       </c>
@@ -14111,7 +14114,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="17">
         <v>46132</v>
       </c>
@@ -14140,7 +14143,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="238" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="17">
         <v>46132</v>
       </c>
@@ -14169,7 +14172,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="239" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="17">
         <v>46132</v>
       </c>
@@ -14198,7 +14201,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="240" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="17">
         <v>46132</v>
       </c>
@@ -14227,7 +14230,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="17">
         <v>46133</v>
       </c>
@@ -14256,7 +14259,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="17">
         <v>46133</v>
       </c>
@@ -14285,7 +14288,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="17">
         <v>46133</v>
       </c>
@@ -14314,7 +14317,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="244" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="17">
         <v>46133</v>
       </c>
@@ -14343,7 +14346,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="245" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" s="17">
         <v>46133</v>
       </c>
@@ -14372,7 +14375,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="246" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="17">
         <v>46133</v>
       </c>
@@ -14401,7 +14404,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="17">
         <v>46133</v>
       </c>
@@ -14430,7 +14433,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="248" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="17">
         <v>46133</v>
       </c>
@@ -14459,7 +14462,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="17">
         <v>46134</v>
       </c>
@@ -14488,7 +14491,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="250" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="17">
         <v>46134</v>
       </c>
@@ -14517,7 +14520,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="17">
         <v>46134</v>
       </c>
@@ -14546,7 +14549,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="17">
         <v>46134</v>
       </c>
@@ -14575,7 +14578,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="17">
         <v>46134</v>
       </c>
@@ -14604,7 +14607,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="17">
         <v>46134</v>
       </c>
@@ -14633,7 +14636,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="255" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="17">
         <v>46134</v>
       </c>
@@ -14662,7 +14665,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="17">
         <v>46134</v>
       </c>
@@ -14691,7 +14694,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="17">
         <v>46134</v>
       </c>
@@ -14720,7 +14723,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="258" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:9" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="17">
         <v>46134</v>
       </c>
@@ -14749,7 +14752,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="17">
         <v>46134</v>
       </c>
@@ -14778,7 +14781,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="260" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="17">
         <v>46135</v>
       </c>
@@ -14807,7 +14810,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="261" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="17">
         <v>46135</v>
       </c>
@@ -14836,7 +14839,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="17">
         <v>46135</v>
       </c>
@@ -14865,7 +14868,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="263" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:9" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="17">
         <v>46135</v>
       </c>
@@ -14894,7 +14897,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="17">
         <v>46135</v>
       </c>
@@ -14923,7 +14926,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="265" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="17">
         <v>46135</v>
       </c>
@@ -14952,7 +14955,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="266" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:9" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" s="17">
         <v>46135</v>
       </c>
@@ -14981,7 +14984,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="267" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" s="17">
         <v>46135</v>
       </c>
@@ -15010,7 +15013,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="268" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:9" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" s="17">
         <v>46136</v>
       </c>
@@ -15039,7 +15042,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="269" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:9" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="17">
         <v>46136</v>
       </c>
@@ -15068,7 +15071,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="270" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="17">
         <v>46136</v>
       </c>
@@ -15097,7 +15100,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="271" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="17">
         <v>46136</v>
       </c>
@@ -15126,7 +15129,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="272" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="17">
         <v>46136</v>
       </c>
@@ -15155,7 +15158,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="273" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:9" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" s="17">
         <v>46136</v>
       </c>
@@ -15184,7 +15187,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" s="17">
         <v>46137</v>
       </c>
@@ -15213,7 +15216,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" s="17">
         <v>46137</v>
       </c>
@@ -15242,7 +15245,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="276" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" s="17">
         <v>46139</v>
       </c>
@@ -15271,7 +15274,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="277" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" s="17">
         <v>46137</v>
       </c>
@@ -15300,7 +15303,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="278" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" s="20">
         <v>46139</v>
       </c>
@@ -15329,7 +15332,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="279" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:9" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" s="20">
         <v>46139</v>
       </c>
@@ -15358,7 +15361,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" s="20">
         <v>46139</v>
       </c>
@@ -15387,7 +15390,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="281" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" s="20">
         <v>46139</v>
       </c>
@@ -15416,7 +15419,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="282" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" s="20">
         <v>46139</v>
       </c>
@@ -15445,7 +15448,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="283" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" s="20">
         <v>46139</v>
       </c>
@@ -15474,7 +15477,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="284" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" s="20">
         <v>46139</v>
       </c>
@@ -15503,7 +15506,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="285" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" s="20">
         <v>46140</v>
       </c>
@@ -15532,7 +15535,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" s="20">
         <v>46140</v>
       </c>
@@ -15561,7 +15564,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="287" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" s="20">
         <v>46140</v>
       </c>
@@ -15590,7 +15593,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="288" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" s="20">
         <v>46141</v>
       </c>
@@ -15619,7 +15622,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="289" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" s="20">
         <v>46118</v>
       </c>
@@ -15648,7 +15651,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="290" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" s="20">
         <v>46142</v>
       </c>
@@ -15677,7 +15680,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="291" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" s="20">
         <v>46142</v>
       </c>
@@ -15706,7 +15709,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="292" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" s="20">
         <v>46142</v>
       </c>
@@ -15735,7 +15738,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" s="20">
         <v>46142</v>
       </c>
@@ -15764,7 +15767,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="294" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="20">
         <v>46142</v>
       </c>
@@ -15793,7 +15796,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="295" spans="1:9" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:9" ht="129.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="20">
         <v>46142</v>
       </c>
@@ -15822,7 +15825,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="296" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="20">
         <v>46143</v>
       </c>
@@ -15851,7 +15854,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="20">
         <v>46143</v>
       </c>
@@ -15880,7 +15883,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="298" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" s="20">
         <v>46143</v>
       </c>
@@ -15909,7 +15912,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="299" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" s="20">
         <v>46143</v>
       </c>
@@ -15938,7 +15941,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" s="20">
         <v>46144</v>
       </c>
@@ -15967,7 +15970,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" s="20">
         <v>46146</v>
       </c>
@@ -15996,7 +15999,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" s="20">
         <v>46146</v>
       </c>
@@ -16025,7 +16028,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" s="20">
         <v>46146</v>
       </c>
@@ -16054,7 +16057,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" s="20">
         <v>46146</v>
       </c>
@@ -16083,7 +16086,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="305" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" s="20">
         <v>46146</v>
       </c>
@@ -16112,7 +16115,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" s="20">
         <v>46146</v>
       </c>
@@ -16141,7 +16144,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="307" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" s="20">
         <v>46146</v>
       </c>
@@ -16170,7 +16173,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" s="20">
         <v>46147</v>
       </c>
@@ -16199,7 +16202,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="309" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="20">
         <v>46147</v>
       </c>
@@ -16228,7 +16231,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" s="20">
         <v>46147</v>
       </c>
@@ -16257,7 +16260,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" s="20">
         <v>46147</v>
       </c>
@@ -16286,7 +16289,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="312" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" s="20">
         <v>46147</v>
       </c>
@@ -16315,7 +16318,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" s="20">
         <v>46147</v>
       </c>
@@ -16344,7 +16347,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" s="20">
         <v>46148</v>
       </c>
@@ -16373,7 +16376,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="315" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" s="20">
         <v>46148</v>
       </c>
@@ -16402,7 +16405,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" s="20">
         <v>46148</v>
       </c>
@@ -16431,7 +16434,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" s="20">
         <v>46148</v>
       </c>
@@ -16460,7 +16463,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="318" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" s="20">
         <v>46148</v>
       </c>
@@ -16489,7 +16492,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="319" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" s="20">
         <v>46148</v>
       </c>
@@ -16518,7 +16521,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="320" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" s="20">
         <v>46149</v>
       </c>
@@ -16547,7 +16550,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" s="20">
         <v>46149</v>
       </c>
@@ -16576,7 +16579,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" s="20">
         <v>46149</v>
       </c>
@@ -16605,7 +16608,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" s="20">
         <v>46149</v>
       </c>
@@ -16634,7 +16637,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" s="20">
         <v>46149</v>
       </c>
@@ -16663,7 +16666,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" s="20">
         <v>46150</v>
       </c>
@@ -16692,7 +16695,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" s="20">
         <v>46153</v>
       </c>
@@ -16721,7 +16724,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" s="20">
         <v>46153</v>
       </c>
@@ -16750,7 +16753,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="328" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" s="20">
         <v>46153</v>
       </c>
@@ -16779,7 +16782,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" s="20">
         <v>46154</v>
       </c>
@@ -16808,7 +16811,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" s="20">
         <v>46154</v>
       </c>
@@ -16837,7 +16840,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" s="20">
         <v>46154</v>
       </c>
@@ -16866,7 +16869,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="332" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" s="20">
         <v>46154</v>
       </c>
@@ -16895,7 +16898,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="333" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:9" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" s="20">
         <v>46154</v>
       </c>
@@ -16924,7 +16927,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" s="20">
         <v>46154</v>
       </c>
@@ -16953,7 +16956,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="335" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" s="20">
         <v>46154</v>
       </c>
@@ -16982,7 +16985,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="336" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" s="20">
         <v>46154</v>
       </c>
@@ -17011,7 +17014,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" s="20">
         <v>46155</v>
       </c>
@@ -17040,7 +17043,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" s="20">
         <v>46155</v>
       </c>
@@ -17069,7 +17072,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" s="20">
         <v>46155</v>
       </c>
@@ -17098,7 +17101,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" s="20">
         <v>46155</v>
       </c>
@@ -17127,7 +17130,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="341" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" s="20">
         <v>46155</v>
       </c>
@@ -17156,7 +17159,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" s="20">
         <v>46155</v>
       </c>
@@ -17185,7 +17188,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" s="20">
         <v>46156</v>
       </c>
@@ -17214,7 +17217,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="344" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" s="20">
         <v>46156</v>
       </c>
@@ -17243,7 +17246,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" s="20">
         <v>46157</v>
       </c>
@@ -17272,7 +17275,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" s="20">
         <v>46157</v>
       </c>
@@ -17301,7 +17304,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" s="28">
         <v>46157</v>
       </c>
@@ -17330,7 +17333,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" s="20">
         <v>46157</v>
       </c>
@@ -17359,7 +17362,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" s="20">
         <v>46160</v>
       </c>
@@ -17388,7 +17391,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="350" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" s="20">
         <v>46160</v>
       </c>
@@ -17417,7 +17420,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="351" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" s="20">
         <v>46160</v>
       </c>
@@ -17446,7 +17449,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="352" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" s="20">
         <v>46160</v>
       </c>
@@ -17475,7 +17478,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="353" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" s="20">
         <v>46160</v>
       </c>
@@ -17504,7 +17507,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="354" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:9" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" s="20">
         <v>46160</v>
       </c>
@@ -17533,7 +17536,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="355" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" s="20">
         <v>46160</v>
       </c>
@@ -17562,7 +17565,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="356" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" s="20">
         <v>46160</v>
       </c>
@@ -17591,7 +17594,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="357" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" s="20">
         <v>46161</v>
       </c>
@@ -17620,7 +17623,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" s="20">
         <v>46161</v>
       </c>
@@ -17649,7 +17652,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="359" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" s="20">
         <v>46161</v>
       </c>
@@ -17678,7 +17681,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="360" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" s="20">
         <v>46161</v>
       </c>
@@ -17707,7 +17710,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="361" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" s="20">
         <v>46162</v>
       </c>
@@ -17736,7 +17739,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="362" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" s="20">
         <v>46162</v>
       </c>
@@ -17765,7 +17768,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="363" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" s="20">
         <v>46162</v>
       </c>
@@ -17794,7 +17797,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" s="20">
         <v>46162</v>
       </c>
@@ -17823,7 +17826,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="365" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:9" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" s="20">
         <v>46162</v>
       </c>
@@ -17852,7 +17855,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="366" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" s="20">
         <v>46162</v>
       </c>
@@ -17881,7 +17884,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="367" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" s="20">
         <v>46163</v>
       </c>
@@ -17910,7 +17913,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="368" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" s="20">
         <v>46163</v>
       </c>
@@ -17939,7 +17942,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369" s="20">
         <v>46163</v>
       </c>
@@ -17968,7 +17971,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="370" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" s="20">
         <v>46163</v>
       </c>
@@ -17997,7 +18000,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" s="20">
         <v>46164</v>
       </c>
@@ -18026,7 +18029,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="372" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:9" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" s="20">
         <v>46164</v>
       </c>
@@ -18055,7 +18058,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" s="20">
         <v>46164</v>
       </c>
@@ -18084,7 +18087,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" s="20">
         <v>46164</v>
       </c>
@@ -18113,7 +18116,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="375" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" s="20">
         <v>46164</v>
       </c>
@@ -18142,7 +18145,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" s="20">
         <v>46164</v>
       </c>
@@ -18171,7 +18174,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="377" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" s="20">
         <v>46164</v>
       </c>
@@ -18200,7 +18203,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" s="20">
         <v>46167</v>
       </c>
@@ -18229,7 +18232,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" s="20">
         <v>46167</v>
       </c>
@@ -18258,7 +18261,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="380" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" s="20">
         <v>46167</v>
       </c>
@@ -18287,7 +18290,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="381" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" s="20">
         <v>46167</v>
       </c>
@@ -18316,7 +18319,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="382" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" s="20">
         <v>46169</v>
       </c>
@@ -18345,7 +18348,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="383" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" s="20">
         <v>46168</v>
       </c>
@@ -18374,7 +18377,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="384" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384" s="20">
         <v>46168</v>
       </c>
@@ -18403,7 +18406,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="385" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" s="20">
         <v>46168</v>
       </c>
@@ -18432,7 +18435,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="386" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" s="20">
         <v>46168</v>
       </c>
@@ -18461,7 +18464,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="387" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:9" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" s="20">
         <v>46168</v>
       </c>
@@ -18490,7 +18493,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="388" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" s="20">
         <v>46168</v>
       </c>
@@ -18519,7 +18522,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="389" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" s="20">
         <v>46168</v>
       </c>
@@ -18548,7 +18551,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="390" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" s="20">
         <v>46169</v>
       </c>
@@ -18577,7 +18580,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="391" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" s="20">
         <v>46169</v>
       </c>
@@ -18606,7 +18609,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="392" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" s="20">
         <v>46169</v>
       </c>
@@ -18635,7 +18638,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="393" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" s="20">
         <v>46170</v>
       </c>
@@ -18664,7 +18667,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="394" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" s="20">
         <v>46170</v>
       </c>
@@ -18693,7 +18696,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="395" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" s="20">
         <v>46170</v>
       </c>
@@ -18722,7 +18725,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="396" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" s="20">
         <v>46170</v>
       </c>
@@ -18751,7 +18754,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="397" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:9" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" s="20">
         <v>46171</v>
       </c>
@@ -18780,7 +18783,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="398" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" s="20">
         <v>46171</v>
       </c>
@@ -18809,7 +18812,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="399" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:9" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" s="20">
         <v>46171</v>
       </c>
@@ -18852,13 +18855,13 @@
         <v>2</v>
       </c>
       <c r="E400" s="24" t="s">
+        <v>888</v>
+      </c>
+      <c r="F400" s="18" t="s">
+        <v>804</v>
+      </c>
+      <c r="G400" s="24" t="s">
         <v>889</v>
-      </c>
-      <c r="F400" s="18" t="s">
-        <v>861</v>
-      </c>
-      <c r="G400" s="24" t="s">
-        <v>890</v>
       </c>
       <c r="H400" s="18">
         <v>1</v>
@@ -18881,7 +18884,7 @@
         <v>0</v>
       </c>
       <c r="E401" s="24" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="F401" s="18" t="s">
         <v>804</v>
@@ -18904,19 +18907,19 @@
         <v>408</v>
       </c>
       <c r="C402" s="18" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="D402" s="18">
         <v>3</v>
       </c>
       <c r="E402" s="24" t="s">
+        <v>896</v>
+      </c>
+      <c r="F402" s="18" t="s">
+        <v>804</v>
+      </c>
+      <c r="G402" s="24" t="s">
         <v>897</v>
-      </c>
-      <c r="F402" s="18" t="s">
-        <v>861</v>
-      </c>
-      <c r="G402" s="24" t="s">
-        <v>898</v>
       </c>
       <c r="H402" s="18">
         <v>1</v>
@@ -18939,13 +18942,13 @@
         <v>2</v>
       </c>
       <c r="E403" s="24" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="F403" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G403" s="24" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H403" s="18">
         <v>1</v>
@@ -18968,13 +18971,13 @@
         <v>3</v>
       </c>
       <c r="E404" s="24" t="s">
+        <v>904</v>
+      </c>
+      <c r="F404" s="18" t="s">
+        <v>804</v>
+      </c>
+      <c r="G404" s="24" t="s">
         <v>905</v>
-      </c>
-      <c r="F404" s="18" t="s">
-        <v>861</v>
-      </c>
-      <c r="G404" s="24" t="s">
-        <v>906</v>
       </c>
       <c r="H404" s="18">
         <v>1</v>
@@ -18997,13 +19000,13 @@
         <v>2</v>
       </c>
       <c r="E405" s="24" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="F405" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G405" s="24" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H405" s="18">
         <v>1</v>
@@ -19026,13 +19029,13 @@
         <v>2</v>
       </c>
       <c r="E406" s="24" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="F406" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G406" s="24" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H406" s="18">
         <v>1</v>
@@ -19055,13 +19058,13 @@
         <v>2</v>
       </c>
       <c r="E407" s="24" t="s">
+        <v>1001</v>
+      </c>
+      <c r="F407" s="18" t="s">
+        <v>804</v>
+      </c>
+      <c r="G407" s="24" t="s">
         <v>1002</v>
-      </c>
-      <c r="F407" s="18" t="s">
-        <v>861</v>
-      </c>
-      <c r="G407" s="24" t="s">
-        <v>1003</v>
       </c>
       <c r="H407" s="18">
         <v>1</v>
@@ -19084,7 +19087,7 @@
         <v>0</v>
       </c>
       <c r="E408" s="24" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="F408" s="18" t="s">
         <v>804</v>
@@ -19104,7 +19107,7 @@
         <v>46177</v>
       </c>
       <c r="B409" s="18" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="C409" s="18" t="s">
         <v>74</v>
@@ -19113,7 +19116,7 @@
         <v>0</v>
       </c>
       <c r="E409" s="24" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="F409" s="18" t="s">
         <v>804</v>
@@ -19142,7 +19145,7 @@
         <v>0</v>
       </c>
       <c r="E410" s="24" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="F410" s="18" t="s">
         <v>804</v>
@@ -19171,10 +19174,10 @@
         <v>1</v>
       </c>
       <c r="E411" s="24" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="F411" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G411" s="24" t="s">
         <v>683</v>
@@ -19200,10 +19203,10 @@
         <v>1</v>
       </c>
       <c r="E412" s="24" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="F412" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G412" s="24" t="s">
         <v>683</v>
@@ -19229,7 +19232,7 @@
         <v>0</v>
       </c>
       <c r="E413" s="24" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="F413" s="18" t="s">
         <v>804</v>
@@ -19258,13 +19261,13 @@
         <v>2</v>
       </c>
       <c r="E414" s="24" t="s">
+        <v>870</v>
+      </c>
+      <c r="F414" s="18" t="s">
+        <v>804</v>
+      </c>
+      <c r="G414" s="24" t="s">
         <v>871</v>
-      </c>
-      <c r="F414" s="18" t="s">
-        <v>861</v>
-      </c>
-      <c r="G414" s="24" t="s">
-        <v>872</v>
       </c>
       <c r="H414" s="18">
         <v>1</v>
@@ -19287,10 +19290,10 @@
         <v>1</v>
       </c>
       <c r="E415" s="24" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="F415" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G415" s="24" t="s">
         <v>738</v>
@@ -19316,13 +19319,13 @@
         <v>2</v>
       </c>
       <c r="E416" s="24" t="s">
+        <v>902</v>
+      </c>
+      <c r="F416" s="18" t="s">
+        <v>804</v>
+      </c>
+      <c r="G416" s="24" t="s">
         <v>903</v>
-      </c>
-      <c r="F416" s="18" t="s">
-        <v>861</v>
-      </c>
-      <c r="G416" s="24" t="s">
-        <v>904</v>
       </c>
       <c r="H416" s="18">
         <v>1</v>
@@ -19345,13 +19348,13 @@
         <v>1</v>
       </c>
       <c r="E417" s="24" t="s">
+        <v>944</v>
+      </c>
+      <c r="F417" s="18" t="s">
+        <v>804</v>
+      </c>
+      <c r="G417" s="24" t="s">
         <v>945</v>
-      </c>
-      <c r="F417" s="18" t="s">
-        <v>861</v>
-      </c>
-      <c r="G417" s="24" t="s">
-        <v>946</v>
       </c>
       <c r="H417" s="18">
         <v>1</v>
@@ -19374,13 +19377,13 @@
         <v>1</v>
       </c>
       <c r="E418" s="24" t="s">
+        <v>868</v>
+      </c>
+      <c r="F418" s="18" t="s">
+        <v>804</v>
+      </c>
+      <c r="G418" s="24" t="s">
         <v>869</v>
-      </c>
-      <c r="F418" s="18" t="s">
-        <v>861</v>
-      </c>
-      <c r="G418" s="24" t="s">
-        <v>870</v>
       </c>
       <c r="H418" s="18">
         <v>1</v>
@@ -19394,7 +19397,7 @@
         <v>46181</v>
       </c>
       <c r="B419" s="18" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C419" s="18" t="s">
         <v>193</v>
@@ -19403,7 +19406,7 @@
         <v>0</v>
       </c>
       <c r="E419" s="24" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="F419" s="18" t="s">
         <v>804</v>
@@ -19423,7 +19426,7 @@
         <v>46181</v>
       </c>
       <c r="B420" s="18" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C420" s="18" t="s">
         <v>193</v>
@@ -19432,7 +19435,7 @@
         <v>0</v>
       </c>
       <c r="E420" s="24" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F420" s="18" t="s">
         <v>804</v>
@@ -19461,13 +19464,13 @@
         <v>1</v>
       </c>
       <c r="E421" s="24" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="F421" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G421" s="24" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="H421" s="18">
         <v>1</v>
@@ -19490,13 +19493,13 @@
         <v>2</v>
       </c>
       <c r="E422" s="24" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="F422" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G422" s="24" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H422" s="18">
         <v>1</v>
@@ -19519,13 +19522,13 @@
         <v>1</v>
       </c>
       <c r="E423" s="24" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="F423" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G423" s="24" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H423" s="18">
         <v>1</v>
@@ -19539,7 +19542,7 @@
         <v>46182</v>
       </c>
       <c r="B424" s="18" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="C424" s="18" t="s">
         <v>74</v>
@@ -19548,7 +19551,7 @@
         <v>0</v>
       </c>
       <c r="E424" s="24" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="F424" s="18" t="s">
         <v>804</v>
@@ -19577,13 +19580,13 @@
         <v>2</v>
       </c>
       <c r="E425" s="24" t="s">
+        <v>907</v>
+      </c>
+      <c r="F425" s="18" t="s">
+        <v>804</v>
+      </c>
+      <c r="G425" s="24" t="s">
         <v>908</v>
-      </c>
-      <c r="F425" s="18" t="s">
-        <v>861</v>
-      </c>
-      <c r="G425" s="24" t="s">
-        <v>909</v>
       </c>
       <c r="H425" s="18">
         <v>1</v>
@@ -19606,7 +19609,7 @@
         <v>0</v>
       </c>
       <c r="E426" s="24" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F426" s="18" t="s">
         <v>804</v>
@@ -19635,13 +19638,13 @@
         <v>2</v>
       </c>
       <c r="E427" s="24" t="s">
+        <v>910</v>
+      </c>
+      <c r="F427" s="18" t="s">
+        <v>804</v>
+      </c>
+      <c r="G427" s="24" t="s">
         <v>911</v>
-      </c>
-      <c r="F427" s="18" t="s">
-        <v>861</v>
-      </c>
-      <c r="G427" s="24" t="s">
-        <v>912</v>
       </c>
       <c r="H427" s="18">
         <v>1</v>
@@ -19664,13 +19667,13 @@
         <v>2</v>
       </c>
       <c r="E428" s="24" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="F428" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G428" s="24" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H428" s="18">
         <v>1</v>
@@ -19693,10 +19696,10 @@
         <v>1</v>
       </c>
       <c r="E429" s="24" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F429" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G429" s="24" t="s">
         <v>683</v>
@@ -19722,13 +19725,13 @@
         <v>2</v>
       </c>
       <c r="E430" s="24" t="s">
+        <v>913</v>
+      </c>
+      <c r="F430" s="18" t="s">
+        <v>804</v>
+      </c>
+      <c r="G430" s="24" t="s">
         <v>914</v>
-      </c>
-      <c r="F430" s="18" t="s">
-        <v>861</v>
-      </c>
-      <c r="G430" s="24" t="s">
-        <v>915</v>
       </c>
       <c r="H430" s="18">
         <v>1</v>
@@ -19745,19 +19748,19 @@
         <v>408</v>
       </c>
       <c r="C431" s="18" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="D431" s="18">
         <v>2</v>
       </c>
       <c r="E431" s="24" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="F431" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G431" s="24" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H431" s="18">
         <v>1</v>
@@ -19780,10 +19783,10 @@
         <v>1</v>
       </c>
       <c r="E432" s="24" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="F432" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G432" s="24" t="s">
         <v>683</v>
@@ -19809,13 +19812,13 @@
         <v>1</v>
       </c>
       <c r="E433" s="24" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="F433" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G433" s="24" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H433" s="18">
         <v>1</v>
@@ -19838,13 +19841,13 @@
         <v>2</v>
       </c>
       <c r="E434" s="24" t="s">
+        <v>898</v>
+      </c>
+      <c r="F434" s="18" t="s">
+        <v>804</v>
+      </c>
+      <c r="G434" s="24" t="s">
         <v>899</v>
-      </c>
-      <c r="F434" s="18" t="s">
-        <v>861</v>
-      </c>
-      <c r="G434" s="24" t="s">
-        <v>900</v>
       </c>
       <c r="H434" s="18">
         <v>1</v>
@@ -19867,13 +19870,13 @@
         <v>2</v>
       </c>
       <c r="E435" s="24" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="F435" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G435" s="24" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H435" s="18">
         <v>1</v>
@@ -19887,7 +19890,7 @@
         <v>46185</v>
       </c>
       <c r="B436" s="18" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C436" s="18" t="s">
         <v>193</v>
@@ -19896,7 +19899,7 @@
         <v>0</v>
       </c>
       <c r="E436" s="24" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="F436" s="18" t="s">
         <v>804</v>
@@ -19919,19 +19922,19 @@
         <v>247</v>
       </c>
       <c r="C437" s="18" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="D437" s="18">
         <v>1</v>
       </c>
       <c r="E437" s="24" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="F437" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G437" s="24" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H437" s="18">
         <v>1</v>
@@ -19945,7 +19948,7 @@
         <v>46185</v>
       </c>
       <c r="B438" s="18" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C438" s="18" t="s">
         <v>193</v>
@@ -19954,7 +19957,7 @@
         <v>0</v>
       </c>
       <c r="E438" s="24" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F438" s="18" t="s">
         <v>804</v>
@@ -19974,16 +19977,16 @@
         <v>46185</v>
       </c>
       <c r="B439" s="18" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C439" s="18" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="D439" s="18">
         <v>0</v>
       </c>
       <c r="E439" s="24" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="F439" s="18" t="s">
         <v>804</v>
@@ -20012,13 +20015,13 @@
         <v>1</v>
       </c>
       <c r="E440" s="24" t="s">
+        <v>884</v>
+      </c>
+      <c r="F440" s="18" t="s">
+        <v>804</v>
+      </c>
+      <c r="G440" s="24" t="s">
         <v>885</v>
-      </c>
-      <c r="F440" s="18" t="s">
-        <v>861</v>
-      </c>
-      <c r="G440" s="24" t="s">
-        <v>886</v>
       </c>
       <c r="H440" s="18">
         <v>1</v>
@@ -20041,13 +20044,13 @@
         <v>1</v>
       </c>
       <c r="E441" s="24" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="F441" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G441" s="24" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="H441" s="18">
         <v>1</v>
@@ -20064,16 +20067,16 @@
         <v>247</v>
       </c>
       <c r="C442" s="18" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="D442" s="18">
         <v>1</v>
       </c>
       <c r="E442" s="24" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F442" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G442" s="24" t="s">
         <v>762</v>
@@ -20093,19 +20096,19 @@
         <v>247</v>
       </c>
       <c r="C443" s="18" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="D443" s="18">
         <v>2</v>
       </c>
       <c r="E443" s="24" t="s">
+        <v>918</v>
+      </c>
+      <c r="F443" s="18" t="s">
+        <v>804</v>
+      </c>
+      <c r="G443" s="24" t="s">
         <v>919</v>
-      </c>
-      <c r="F443" s="18" t="s">
-        <v>861</v>
-      </c>
-      <c r="G443" s="24" t="s">
-        <v>920</v>
       </c>
       <c r="H443" s="18">
         <v>1</v>
@@ -20128,7 +20131,7 @@
         <v>0</v>
       </c>
       <c r="E444" s="24" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="F444" s="18" t="s">
         <v>804</v>
@@ -20157,7 +20160,7 @@
         <v>1</v>
       </c>
       <c r="E445" s="24" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="F445" s="18" t="s">
         <v>804</v>
@@ -20180,19 +20183,19 @@
         <v>412</v>
       </c>
       <c r="C446" s="18" t="s">
+        <v>865</v>
+      </c>
+      <c r="D446" s="18">
+        <v>1</v>
+      </c>
+      <c r="E446" s="24" t="s">
         <v>866</v>
       </c>
-      <c r="D446" s="18">
-        <v>1</v>
-      </c>
-      <c r="E446" s="24" t="s">
+      <c r="F446" s="18" t="s">
+        <v>804</v>
+      </c>
+      <c r="G446" s="24" t="s">
         <v>867</v>
-      </c>
-      <c r="F446" s="18" t="s">
-        <v>861</v>
-      </c>
-      <c r="G446" s="24" t="s">
-        <v>868</v>
       </c>
       <c r="H446" s="18">
         <v>1</v>
@@ -20215,13 +20218,13 @@
         <v>2</v>
       </c>
       <c r="E447" s="24" t="s">
+        <v>900</v>
+      </c>
+      <c r="F447" s="18" t="s">
+        <v>804</v>
+      </c>
+      <c r="G447" s="24" t="s">
         <v>901</v>
-      </c>
-      <c r="F447" s="18" t="s">
-        <v>861</v>
-      </c>
-      <c r="G447" s="24" t="s">
-        <v>902</v>
       </c>
       <c r="H447" s="18">
         <v>1</v>
@@ -20238,19 +20241,19 @@
         <v>247</v>
       </c>
       <c r="C448" s="18" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="D448" s="18">
         <v>2</v>
       </c>
       <c r="E448" s="24" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="F448" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G448" s="24" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H448" s="18">
         <v>1</v>
@@ -20267,13 +20270,13 @@
         <v>247</v>
       </c>
       <c r="C449" s="18" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="D449" s="18">
         <v>1</v>
       </c>
       <c r="E449" s="24" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="F449" s="18" t="s">
         <v>804</v>
@@ -20296,19 +20299,19 @@
         <v>247</v>
       </c>
       <c r="C450" s="18" t="s">
+        <v>922</v>
+      </c>
+      <c r="D450" s="18">
+        <v>1</v>
+      </c>
+      <c r="E450" s="24" t="s">
         <v>923</v>
       </c>
-      <c r="D450" s="18">
-        <v>1</v>
-      </c>
-      <c r="E450" s="24" t="s">
+      <c r="F450" s="18" t="s">
+        <v>804</v>
+      </c>
+      <c r="G450" s="24" t="s">
         <v>924</v>
-      </c>
-      <c r="F450" s="18" t="s">
-        <v>861</v>
-      </c>
-      <c r="G450" s="24" t="s">
-        <v>925</v>
       </c>
       <c r="H450" s="18">
         <v>1</v>
@@ -20325,19 +20328,19 @@
         <v>247</v>
       </c>
       <c r="C451" s="18" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="D451" s="18">
         <v>2</v>
       </c>
       <c r="E451" s="24" t="s">
+        <v>925</v>
+      </c>
+      <c r="F451" s="18" t="s">
+        <v>804</v>
+      </c>
+      <c r="G451" s="24" t="s">
         <v>926</v>
-      </c>
-      <c r="F451" s="18" t="s">
-        <v>861</v>
-      </c>
-      <c r="G451" s="24" t="s">
-        <v>927</v>
       </c>
       <c r="H451" s="18">
         <v>1</v>
@@ -20354,19 +20357,19 @@
         <v>247</v>
       </c>
       <c r="C452" s="18" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="D452" s="18">
         <v>2</v>
       </c>
       <c r="E452" s="24" t="s">
+        <v>927</v>
+      </c>
+      <c r="F452" s="18" t="s">
+        <v>804</v>
+      </c>
+      <c r="G452" s="24" t="s">
         <v>928</v>
-      </c>
-      <c r="F452" s="18" t="s">
-        <v>861</v>
-      </c>
-      <c r="G452" s="24" t="s">
-        <v>929</v>
       </c>
       <c r="H452" s="18">
         <v>1</v>
@@ -20383,19 +20386,19 @@
         <v>243</v>
       </c>
       <c r="C453" s="18" t="s">
+        <v>929</v>
+      </c>
+      <c r="D453" s="18">
+        <v>1</v>
+      </c>
+      <c r="E453" s="24" t="s">
         <v>930</v>
       </c>
-      <c r="D453" s="18">
-        <v>1</v>
-      </c>
-      <c r="E453" s="24" t="s">
+      <c r="F453" s="18" t="s">
+        <v>804</v>
+      </c>
+      <c r="G453" s="24" t="s">
         <v>931</v>
-      </c>
-      <c r="F453" s="18" t="s">
-        <v>861</v>
-      </c>
-      <c r="G453" s="24" t="s">
-        <v>932</v>
       </c>
       <c r="H453" s="18">
         <v>1</v>
@@ -20412,19 +20415,19 @@
         <v>243</v>
       </c>
       <c r="C454" s="18" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="D454" s="18">
         <v>1</v>
       </c>
       <c r="E454" s="24" t="s">
+        <v>932</v>
+      </c>
+      <c r="F454" s="18" t="s">
+        <v>804</v>
+      </c>
+      <c r="G454" s="24" t="s">
         <v>933</v>
-      </c>
-      <c r="F454" s="18" t="s">
-        <v>861</v>
-      </c>
-      <c r="G454" s="24" t="s">
-        <v>934</v>
       </c>
       <c r="H454" s="18">
         <v>1</v>
@@ -20441,19 +20444,19 @@
         <v>243</v>
       </c>
       <c r="C455" s="18" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="D455" s="18">
         <v>1</v>
       </c>
       <c r="E455" s="24" t="s">
+        <v>934</v>
+      </c>
+      <c r="F455" s="18" t="s">
+        <v>804</v>
+      </c>
+      <c r="G455" s="24" t="s">
         <v>935</v>
-      </c>
-      <c r="F455" s="18" t="s">
-        <v>861</v>
-      </c>
-      <c r="G455" s="24" t="s">
-        <v>936</v>
       </c>
       <c r="H455" s="18">
         <v>1</v>
@@ -20476,13 +20479,13 @@
         <v>1</v>
       </c>
       <c r="E456" s="24" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="F456" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G456" s="24" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H456" s="18">
         <v>1</v>
@@ -20505,13 +20508,13 @@
         <v>1</v>
       </c>
       <c r="E457" s="24" t="s">
+        <v>936</v>
+      </c>
+      <c r="F457" s="18" t="s">
+        <v>804</v>
+      </c>
+      <c r="G457" s="24" t="s">
         <v>937</v>
-      </c>
-      <c r="F457" s="18" t="s">
-        <v>861</v>
-      </c>
-      <c r="G457" s="24" t="s">
-        <v>938</v>
       </c>
       <c r="H457" s="18">
         <v>1</v>
@@ -20528,16 +20531,16 @@
         <v>247</v>
       </c>
       <c r="C458" s="18" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="D458" s="18">
         <v>1</v>
       </c>
       <c r="E458" s="24" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="F458" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G458" s="24" t="s">
         <v>762</v>
@@ -20557,19 +20560,19 @@
         <v>247</v>
       </c>
       <c r="C459" s="18" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="D459" s="18">
         <v>3</v>
       </c>
       <c r="E459" s="24" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="F459" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G459" s="24" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H459" s="18">
         <v>1</v>
@@ -20592,7 +20595,7 @@
         <v>0</v>
       </c>
       <c r="E460" s="24" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="F460" s="18" t="s">
         <v>804</v>
@@ -20621,7 +20624,7 @@
         <v>0</v>
       </c>
       <c r="E461" s="24" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="F461" s="18" t="s">
         <v>804</v>
@@ -20679,13 +20682,13 @@
         <v>2</v>
       </c>
       <c r="E463" s="24" t="s">
+        <v>863</v>
+      </c>
+      <c r="F463" s="18" t="s">
+        <v>804</v>
+      </c>
+      <c r="G463" s="24" t="s">
         <v>864</v>
-      </c>
-      <c r="F463" s="18" t="s">
-        <v>861</v>
-      </c>
-      <c r="G463" s="24" t="s">
-        <v>865</v>
       </c>
       <c r="H463" s="18">
         <v>1</v>
@@ -20708,13 +20711,13 @@
         <v>2</v>
       </c>
       <c r="E464" s="24" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="F464" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G464" s="24" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H464" s="18">
         <v>1</v>
@@ -20737,13 +20740,13 @@
         <v>2</v>
       </c>
       <c r="E465" s="24" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="F465" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G465" s="24" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H465" s="18">
         <v>1</v>
@@ -20760,19 +20763,19 @@
         <v>247</v>
       </c>
       <c r="C466" s="18" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="D466" s="18">
         <v>1</v>
       </c>
       <c r="E466" s="24" t="s">
+        <v>939</v>
+      </c>
+      <c r="F466" s="18" t="s">
+        <v>804</v>
+      </c>
+      <c r="G466" s="24" t="s">
         <v>940</v>
-      </c>
-      <c r="F466" s="18" t="s">
-        <v>804</v>
-      </c>
-      <c r="G466" s="24" t="s">
-        <v>941</v>
       </c>
       <c r="H466" s="18">
         <v>1</v>
@@ -20795,13 +20798,13 @@
         <v>2</v>
       </c>
       <c r="E467" s="24" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="F467" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G467" s="24" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="H467" s="18">
         <v>1</v>
@@ -20824,13 +20827,13 @@
         <v>4</v>
       </c>
       <c r="E468" s="24" t="s">
+        <v>999</v>
+      </c>
+      <c r="F468" s="18" t="s">
+        <v>804</v>
+      </c>
+      <c r="G468" s="24" t="s">
         <v>1000</v>
-      </c>
-      <c r="F468" s="18" t="s">
-        <v>861</v>
-      </c>
-      <c r="G468" s="24" t="s">
-        <v>1001</v>
       </c>
       <c r="H468" s="18">
         <v>1</v>
@@ -20853,10 +20856,10 @@
         <v>1</v>
       </c>
       <c r="E469" s="24" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="F469" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G469" s="24" t="s">
         <v>626</v>
@@ -20882,10 +20885,10 @@
         <v>1</v>
       </c>
       <c r="E470" s="24" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="F470" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G470" s="24" t="s">
         <v>625</v>
@@ -20911,10 +20914,10 @@
         <v>1</v>
       </c>
       <c r="E471" s="24" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="F471" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G471" s="24" t="s">
         <v>18</v>
@@ -20940,10 +20943,10 @@
         <v>1</v>
       </c>
       <c r="E472" s="24" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F472" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G472" s="24" t="s">
         <v>29</v>
@@ -20963,19 +20966,19 @@
         <v>247</v>
       </c>
       <c r="C473" s="18" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="D473" s="18">
         <v>1</v>
       </c>
       <c r="E473" s="24" t="s">
+        <v>997</v>
+      </c>
+      <c r="F473" s="18" t="s">
+        <v>804</v>
+      </c>
+      <c r="G473" s="24" t="s">
         <v>998</v>
-      </c>
-      <c r="F473" s="18" t="s">
-        <v>861</v>
-      </c>
-      <c r="G473" s="24" t="s">
-        <v>999</v>
       </c>
       <c r="H473" s="18">
         <v>1</v>
@@ -20998,10 +21001,10 @@
         <v>1</v>
       </c>
       <c r="E474" s="24" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="F474" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G474" s="24" t="s">
         <v>835</v>
@@ -21027,10 +21030,10 @@
         <v>1</v>
       </c>
       <c r="E475" s="24" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F475" s="18" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G475" s="24" t="s">
         <v>19</v>
@@ -21050,19 +21053,19 @@
         <v>247</v>
       </c>
       <c r="C476" s="18" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="D476" s="18">
         <v>3</v>
       </c>
       <c r="E476" s="24" t="s">
+        <v>990</v>
+      </c>
+      <c r="F476" s="18" t="s">
+        <v>804</v>
+      </c>
+      <c r="G476" s="24" t="s">
         <v>991</v>
-      </c>
-      <c r="F476" s="18" t="s">
-        <v>861</v>
-      </c>
-      <c r="G476" s="24" t="s">
-        <v>992</v>
       </c>
       <c r="H476" s="18">
         <v>1</v>
@@ -21076,22 +21079,22 @@
         <v>46201</v>
       </c>
       <c r="B477" s="18" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="C477" s="18" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="D477" s="18">
         <v>3</v>
       </c>
       <c r="E477" s="24" t="s">
+        <v>993</v>
+      </c>
+      <c r="F477" s="18" t="s">
+        <v>804</v>
+      </c>
+      <c r="G477" s="24" t="s">
         <v>994</v>
-      </c>
-      <c r="F477" s="18" t="s">
-        <v>861</v>
-      </c>
-      <c r="G477" s="24" t="s">
-        <v>995</v>
       </c>
       <c r="H477" s="18">
         <v>1</v>
@@ -21105,7 +21108,7 @@
         <v>46203</v>
       </c>
       <c r="B478" s="18" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="C478" s="18" t="s">
         <v>10</v>
@@ -21114,13 +21117,13 @@
         <v>2</v>
       </c>
       <c r="E478" s="24" t="s">
+        <v>987</v>
+      </c>
+      <c r="F478" s="18" t="s">
+        <v>804</v>
+      </c>
+      <c r="G478" s="24" t="s">
         <v>988</v>
-      </c>
-      <c r="F478" s="18" t="s">
-        <v>861</v>
-      </c>
-      <c r="G478" s="24" t="s">
-        <v>989</v>
       </c>
       <c r="H478" s="18">
         <v>1</v>
@@ -21134,7 +21137,7 @@
         <v>46203</v>
       </c>
       <c r="B479" s="18" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C479" s="18" t="s">
         <v>193</v>
@@ -21158,7 +21161,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="480" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480" s="20"/>
       <c r="B480" s="18"/>
       <c r="C480" s="18"/>
@@ -21171,7 +21174,7 @@
       <c r="H480" s="18"/>
       <c r="I480" s="18"/>
     </row>
-    <row r="481" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481" s="20"/>
       <c r="B481" s="18"/>
       <c r="C481" s="18"/>
@@ -21184,7 +21187,7 @@
       <c r="H481" s="18"/>
       <c r="I481" s="18"/>
     </row>
-    <row r="482" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482" s="20"/>
       <c r="B482" s="18"/>
       <c r="C482" s="18"/>
@@ -21197,7 +21200,7 @@
       <c r="H482" s="18"/>
       <c r="I482" s="18"/>
     </row>
-    <row r="483" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483" s="20"/>
       <c r="B483" s="18"/>
       <c r="C483" s="18"/>
@@ -21210,7 +21213,7 @@
       <c r="H483" s="18"/>
       <c r="I483" s="18"/>
     </row>
-    <row r="484" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484" s="20"/>
       <c r="B484" s="18"/>
       <c r="C484" s="18"/>
@@ -21223,7 +21226,7 @@
       <c r="H484" s="18"/>
       <c r="I484" s="18"/>
     </row>
-    <row r="485" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485" s="20"/>
       <c r="B485" s="18"/>
       <c r="C485" s="18"/>
@@ -21236,7 +21239,7 @@
       <c r="H485" s="18"/>
       <c r="I485" s="18"/>
     </row>
-    <row r="486" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486" s="20"/>
       <c r="B486" s="18"/>
       <c r="C486" s="18"/>
@@ -21249,7 +21252,7 @@
       <c r="H486" s="18"/>
       <c r="I486" s="18"/>
     </row>
-    <row r="487" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487" s="20"/>
       <c r="B487" s="18"/>
       <c r="C487" s="18"/>
@@ -21262,7 +21265,7 @@
       <c r="H487" s="18"/>
       <c r="I487" s="18"/>
     </row>
-    <row r="488" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488" s="20"/>
       <c r="B488" s="18"/>
       <c r="C488" s="18"/>
@@ -21275,7 +21278,7 @@
       <c r="H488" s="18"/>
       <c r="I488" s="18"/>
     </row>
-    <row r="489" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489" s="20"/>
       <c r="B489" s="18"/>
       <c r="C489" s="18"/>
@@ -21288,7 +21291,7 @@
       <c r="H489" s="18"/>
       <c r="I489" s="18"/>
     </row>
-    <row r="490" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490" s="20"/>
       <c r="B490" s="18"/>
       <c r="C490" s="18"/>
@@ -21301,7 +21304,7 @@
       <c r="H490" s="18"/>
       <c r="I490" s="18"/>
     </row>
-    <row r="491" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A491" s="20"/>
       <c r="B491" s="18"/>
       <c r="C491" s="18"/>
@@ -21314,7 +21317,7 @@
       <c r="H491" s="18"/>
       <c r="I491" s="18"/>
     </row>
-    <row r="492" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A492" s="20"/>
       <c r="B492" s="18"/>
       <c r="C492" s="18"/>
@@ -21327,7 +21330,7 @@
       <c r="H492" s="18"/>
       <c r="I492" s="18"/>
     </row>
-    <row r="493" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493" s="20"/>
       <c r="B493" s="18"/>
       <c r="C493" s="18"/>
@@ -21340,7 +21343,7 @@
       <c r="H493" s="18"/>
       <c r="I493" s="18"/>
     </row>
-    <row r="494" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A494" s="20"/>
       <c r="B494" s="18"/>
       <c r="C494" s="18"/>
@@ -21353,7 +21356,7 @@
       <c r="H494" s="18"/>
       <c r="I494" s="18"/>
     </row>
-    <row r="495" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A495" s="20"/>
       <c r="B495" s="18"/>
       <c r="C495" s="18"/>
@@ -21366,7 +21369,7 @@
       <c r="H495" s="18"/>
       <c r="I495" s="18"/>
     </row>
-    <row r="496" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A496" s="20"/>
       <c r="B496" s="18"/>
       <c r="C496" s="18"/>
@@ -21379,7 +21382,7 @@
       <c r="H496" s="18"/>
       <c r="I496" s="18"/>
     </row>
-    <row r="497" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A497" s="20"/>
       <c r="B497" s="18"/>
       <c r="C497" s="18"/>
@@ -21392,7 +21395,7 @@
       <c r="H497" s="18"/>
       <c r="I497" s="18"/>
     </row>
-    <row r="498" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A498" s="20"/>
       <c r="B498" s="18"/>
       <c r="C498" s="18"/>
@@ -21405,7 +21408,7 @@
       <c r="H498" s="18"/>
       <c r="I498" s="18"/>
     </row>
-    <row r="499" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A499" s="20"/>
       <c r="B499" s="18"/>
       <c r="C499" s="18"/>
@@ -21418,7 +21421,7 @@
       <c r="H499" s="18"/>
       <c r="I499" s="18"/>
     </row>
-    <row r="500" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A500" s="20"/>
       <c r="B500" s="18"/>
       <c r="C500" s="18"/>
@@ -21431,7 +21434,7 @@
       <c r="H500" s="18"/>
       <c r="I500" s="18"/>
     </row>
-    <row r="501" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A501" s="20"/>
       <c r="B501" s="18"/>
       <c r="C501" s="18"/>
@@ -21444,7 +21447,7 @@
       <c r="H501" s="18"/>
       <c r="I501" s="18"/>
     </row>
-    <row r="502" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A502" s="20"/>
       <c r="B502" s="18"/>
       <c r="C502" s="18"/>
@@ -21457,7 +21460,7 @@
       <c r="H502" s="18"/>
       <c r="I502" s="18"/>
     </row>
-    <row r="503" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A503" s="20"/>
       <c r="B503" s="18"/>
       <c r="C503" s="18"/>
@@ -21470,7 +21473,7 @@
       <c r="H503" s="18"/>
       <c r="I503" s="18"/>
     </row>
-    <row r="504" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A504" s="20"/>
       <c r="B504" s="18"/>
       <c r="C504" s="18"/>
@@ -21483,7 +21486,7 @@
       <c r="H504" s="18"/>
       <c r="I504" s="18"/>
     </row>
-    <row r="505" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A505" s="20"/>
       <c r="B505" s="18"/>
       <c r="C505" s="18"/>
@@ -21496,7 +21499,7 @@
       <c r="H505" s="18"/>
       <c r="I505" s="18"/>
     </row>
-    <row r="506" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A506" s="20"/>
       <c r="B506" s="18"/>
       <c r="C506" s="18"/>
@@ -21509,7 +21512,7 @@
       <c r="H506" s="18"/>
       <c r="I506" s="18"/>
     </row>
-    <row r="507" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A507" s="20"/>
       <c r="B507" s="18"/>
       <c r="C507" s="18"/>
@@ -21522,7 +21525,7 @@
       <c r="H507" s="18"/>
       <c r="I507" s="18"/>
     </row>
-    <row r="508" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A508" s="20"/>
       <c r="B508" s="18"/>
       <c r="C508" s="18"/>
@@ -21535,7 +21538,7 @@
       <c r="H508" s="18"/>
       <c r="I508" s="18"/>
     </row>
-    <row r="509" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A509" s="20"/>
       <c r="B509" s="18"/>
       <c r="C509" s="18"/>
@@ -21548,7 +21551,7 @@
       <c r="H509" s="18"/>
       <c r="I509" s="18"/>
     </row>
-    <row r="510" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A510" s="20"/>
       <c r="B510" s="18"/>
       <c r="C510" s="18"/>
@@ -21561,7 +21564,7 @@
       <c r="H510" s="18"/>
       <c r="I510" s="18"/>
     </row>
-    <row r="511" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511" s="20"/>
       <c r="B511" s="18"/>
       <c r="C511" s="18"/>
@@ -21574,7 +21577,7 @@
       <c r="H511" s="18"/>
       <c r="I511" s="18"/>
     </row>
-    <row r="512" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A512" s="20"/>
       <c r="B512" s="18"/>
       <c r="C512" s="18"/>
@@ -21587,7 +21590,7 @@
       <c r="H512" s="18"/>
       <c r="I512" s="18"/>
     </row>
-    <row r="513" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A513" s="20"/>
       <c r="B513" s="18"/>
       <c r="C513" s="18"/>
@@ -21600,7 +21603,7 @@
       <c r="H513" s="18"/>
       <c r="I513" s="18"/>
     </row>
-    <row r="514" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514" s="20"/>
       <c r="B514" s="18"/>
       <c r="C514" s="18"/>
@@ -21613,7 +21616,7 @@
       <c r="H514" s="18"/>
       <c r="I514" s="18"/>
     </row>
-    <row r="515" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515" s="20"/>
       <c r="B515" s="18"/>
       <c r="C515" s="18"/>
@@ -21626,7 +21629,7 @@
       <c r="H515" s="18"/>
       <c r="I515" s="18"/>
     </row>
-    <row r="516" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516" s="20"/>
       <c r="B516" s="18"/>
       <c r="C516" s="18"/>
@@ -21639,7 +21642,7 @@
       <c r="H516" s="18"/>
       <c r="I516" s="18"/>
     </row>
-    <row r="517" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A517" s="20"/>
       <c r="B517" s="18"/>
       <c r="C517" s="18"/>
@@ -21652,7 +21655,7 @@
       <c r="H517" s="18"/>
       <c r="I517" s="18"/>
     </row>
-    <row r="518" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A518" s="20"/>
       <c r="B518" s="18"/>
       <c r="C518" s="18"/>
@@ -21665,7 +21668,7 @@
       <c r="H518" s="18"/>
       <c r="I518" s="18"/>
     </row>
-    <row r="519" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A519" s="20"/>
       <c r="B519" s="18"/>
       <c r="C519" s="18"/>
@@ -21678,7 +21681,7 @@
       <c r="H519" s="18"/>
       <c r="I519" s="18"/>
     </row>
-    <row r="520" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A520" s="20"/>
       <c r="B520" s="18"/>
       <c r="C520" s="18"/>
@@ -21691,7 +21694,7 @@
       <c r="H520" s="18"/>
       <c r="I520" s="18"/>
     </row>
-    <row r="521" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521" s="20"/>
       <c r="B521" s="18"/>
       <c r="C521" s="18"/>
@@ -21704,7 +21707,7 @@
       <c r="H521" s="18"/>
       <c r="I521" s="18"/>
     </row>
-    <row r="522" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A522" s="20"/>
       <c r="B522" s="18"/>
       <c r="C522" s="18"/>
@@ -21717,7 +21720,7 @@
       <c r="H522" s="18"/>
       <c r="I522" s="18"/>
     </row>
-    <row r="523" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A523" s="20"/>
       <c r="B523" s="18"/>
       <c r="C523" s="18"/>
@@ -21730,7 +21733,7 @@
       <c r="H523" s="18"/>
       <c r="I523" s="18"/>
     </row>
-    <row r="524" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A524" s="20"/>
       <c r="B524" s="18"/>
       <c r="C524" s="18"/>
@@ -21743,7 +21746,7 @@
       <c r="H524" s="18"/>
       <c r="I524" s="18"/>
     </row>
-    <row r="525" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A525" s="20"/>
       <c r="B525" s="18"/>
       <c r="C525" s="18"/>
@@ -21756,7 +21759,7 @@
       <c r="H525" s="18"/>
       <c r="I525" s="18"/>
     </row>
-    <row r="526" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A526" s="20"/>
       <c r="B526" s="18"/>
       <c r="C526" s="18"/>
@@ -21769,7 +21772,7 @@
       <c r="H526" s="18"/>
       <c r="I526" s="18"/>
     </row>
-    <row r="527" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A527" s="20"/>
       <c r="B527" s="18"/>
       <c r="C527" s="18"/>
@@ -21782,7 +21785,7 @@
       <c r="H527" s="18"/>
       <c r="I527" s="18"/>
     </row>
-    <row r="528" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A528" s="20"/>
       <c r="B528" s="18"/>
       <c r="C528" s="18"/>
@@ -21795,7 +21798,7 @@
       <c r="H528" s="18"/>
       <c r="I528" s="18"/>
     </row>
-    <row r="529" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A529" s="20"/>
       <c r="B529" s="18"/>
       <c r="C529" s="18"/>
@@ -21808,7 +21811,7 @@
       <c r="H529" s="18"/>
       <c r="I529" s="18"/>
     </row>
-    <row r="530" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A530" s="20"/>
       <c r="B530" s="18"/>
       <c r="C530" s="18"/>
@@ -21821,7 +21824,7 @@
       <c r="H530" s="18"/>
       <c r="I530" s="18"/>
     </row>
-    <row r="531" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A531" s="20"/>
       <c r="B531" s="18"/>
       <c r="C531" s="18"/>
@@ -21834,7 +21837,7 @@
       <c r="H531" s="18"/>
       <c r="I531" s="18"/>
     </row>
-    <row r="532" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A532" s="20"/>
       <c r="B532" s="18"/>
       <c r="C532" s="18"/>
@@ -21847,7 +21850,7 @@
       <c r="H532" s="18"/>
       <c r="I532" s="18"/>
     </row>
-    <row r="533" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A533" s="20"/>
       <c r="B533" s="18"/>
       <c r="C533" s="18"/>
@@ -21860,7 +21863,7 @@
       <c r="H533" s="18"/>
       <c r="I533" s="18"/>
     </row>
-    <row r="534" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A534" s="20"/>
       <c r="B534" s="18"/>
       <c r="C534" s="18"/>
@@ -21873,7 +21876,7 @@
       <c r="H534" s="18"/>
       <c r="I534" s="18"/>
     </row>
-    <row r="535" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A535" s="20"/>
       <c r="B535" s="18"/>
       <c r="C535" s="18"/>
@@ -21886,7 +21889,7 @@
       <c r="H535" s="18"/>
       <c r="I535" s="18"/>
     </row>
-    <row r="536" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A536" s="20"/>
       <c r="B536" s="18"/>
       <c r="C536" s="18"/>
@@ -21899,7 +21902,7 @@
       <c r="H536" s="18"/>
       <c r="I536" s="18"/>
     </row>
-    <row r="537" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A537" s="20"/>
       <c r="B537" s="18"/>
       <c r="C537" s="18"/>
@@ -21912,7 +21915,7 @@
       <c r="H537" s="18"/>
       <c r="I537" s="18"/>
     </row>
-    <row r="538" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A538" s="20"/>
       <c r="B538" s="18"/>
       <c r="C538" s="18"/>
@@ -21925,7 +21928,7 @@
       <c r="H538" s="18"/>
       <c r="I538" s="18"/>
     </row>
-    <row r="539" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A539" s="20"/>
       <c r="B539" s="18"/>
       <c r="C539" s="18"/>
@@ -21938,7 +21941,7 @@
       <c r="H539" s="18"/>
       <c r="I539" s="18"/>
     </row>
-    <row r="540" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A540" s="20"/>
       <c r="B540" s="18"/>
       <c r="C540" s="18"/>
@@ -21951,7 +21954,7 @@
       <c r="H540" s="18"/>
       <c r="I540" s="18"/>
     </row>
-    <row r="541" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A541" s="20"/>
       <c r="B541" s="18"/>
       <c r="C541" s="18"/>
@@ -21964,7 +21967,7 @@
       <c r="H541" s="18"/>
       <c r="I541" s="18"/>
     </row>
-    <row r="542" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A542" s="20"/>
       <c r="B542" s="18"/>
       <c r="C542" s="18"/>
@@ -21977,7 +21980,7 @@
       <c r="H542" s="18"/>
       <c r="I542" s="18"/>
     </row>
-    <row r="543" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A543" s="20"/>
       <c r="B543" s="18"/>
       <c r="C543" s="18"/>
@@ -21990,7 +21993,7 @@
       <c r="H543" s="18"/>
       <c r="I543" s="18"/>
     </row>
-    <row r="544" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A544" s="20"/>
       <c r="B544" s="18"/>
       <c r="C544" s="18"/>
@@ -22003,7 +22006,7 @@
       <c r="H544" s="18"/>
       <c r="I544" s="18"/>
     </row>
-    <row r="545" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A545" s="20"/>
       <c r="B545" s="18"/>
       <c r="C545" s="18"/>
@@ -22016,7 +22019,7 @@
       <c r="H545" s="18"/>
       <c r="I545" s="18"/>
     </row>
-    <row r="546" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A546" s="20"/>
       <c r="B546" s="18"/>
       <c r="C546" s="18"/>
@@ -22029,7 +22032,7 @@
       <c r="H546" s="18"/>
       <c r="I546" s="18"/>
     </row>
-    <row r="547" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A547" s="20"/>
       <c r="B547" s="18"/>
       <c r="C547" s="18"/>
@@ -22042,7 +22045,7 @@
       <c r="H547" s="18"/>
       <c r="I547" s="18"/>
     </row>
-    <row r="548" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A548" s="20"/>
       <c r="B548" s="18"/>
       <c r="C548" s="18"/>
@@ -22055,7 +22058,7 @@
       <c r="H548" s="18"/>
       <c r="I548" s="18"/>
     </row>
-    <row r="549" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A549" s="20"/>
       <c r="B549" s="18"/>
       <c r="C549" s="18"/>
@@ -22068,7 +22071,7 @@
       <c r="H549" s="18"/>
       <c r="I549" s="18"/>
     </row>
-    <row r="550" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A550" s="20"/>
       <c r="B550" s="18"/>
       <c r="C550" s="18"/>
@@ -22081,7 +22084,7 @@
       <c r="H550" s="18"/>
       <c r="I550" s="18"/>
     </row>
-    <row r="551" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A551" s="20"/>
       <c r="B551" s="18"/>
       <c r="C551" s="18"/>
@@ -22094,7 +22097,7 @@
       <c r="H551" s="18"/>
       <c r="I551" s="18"/>
     </row>
-    <row r="552" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A552" s="20"/>
       <c r="B552" s="18"/>
       <c r="C552" s="18"/>
@@ -22107,7 +22110,7 @@
       <c r="H552" s="18"/>
       <c r="I552" s="18"/>
     </row>
-    <row r="553" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A553" s="20"/>
       <c r="B553" s="18"/>
       <c r="C553" s="18"/>
@@ -22120,7 +22123,7 @@
       <c r="H553" s="18"/>
       <c r="I553" s="18"/>
     </row>
-    <row r="554" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A554" s="20"/>
       <c r="B554" s="18"/>
       <c r="C554" s="18"/>
@@ -22133,7 +22136,7 @@
       <c r="H554" s="18"/>
       <c r="I554" s="18"/>
     </row>
-    <row r="555" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A555" s="20"/>
       <c r="B555" s="18"/>
       <c r="C555" s="18"/>
@@ -22146,7 +22149,7 @@
       <c r="H555" s="18"/>
       <c r="I555" s="18"/>
     </row>
-    <row r="556" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A556" s="20"/>
       <c r="B556" s="18"/>
       <c r="C556" s="18"/>
@@ -22159,7 +22162,7 @@
       <c r="H556" s="18"/>
       <c r="I556" s="18"/>
     </row>
-    <row r="557" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A557" s="20"/>
       <c r="B557" s="18"/>
       <c r="C557" s="18"/>
@@ -22172,7 +22175,7 @@
       <c r="H557" s="18"/>
       <c r="I557" s="18"/>
     </row>
-    <row r="558" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558" s="20"/>
       <c r="B558" s="18"/>
       <c r="C558" s="18"/>
@@ -22185,7 +22188,7 @@
       <c r="H558" s="18"/>
       <c r="I558" s="18"/>
     </row>
-    <row r="559" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A559" s="20"/>
       <c r="B559" s="18"/>
       <c r="C559" s="18"/>
@@ -22198,7 +22201,7 @@
       <c r="H559" s="18"/>
       <c r="I559" s="18"/>
     </row>
-    <row r="560" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A560" s="20"/>
       <c r="B560" s="18"/>
       <c r="C560" s="18"/>
@@ -22211,7 +22214,7 @@
       <c r="H560" s="18"/>
       <c r="I560" s="18"/>
     </row>
-    <row r="561" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A561" s="20"/>
       <c r="B561" s="18"/>
       <c r="C561" s="18"/>
@@ -22224,7 +22227,7 @@
       <c r="H561" s="18"/>
       <c r="I561" s="18"/>
     </row>
-    <row r="562" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A562" s="20"/>
       <c r="B562" s="18"/>
       <c r="C562" s="18"/>
@@ -22237,7 +22240,7 @@
       <c r="H562" s="18"/>
       <c r="I562" s="18"/>
     </row>
-    <row r="563" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A563" s="20"/>
       <c r="B563" s="18"/>
       <c r="C563" s="18"/>
@@ -22250,7 +22253,7 @@
       <c r="H563" s="18"/>
       <c r="I563" s="18"/>
     </row>
-    <row r="564" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A564" s="20"/>
       <c r="B564" s="18"/>
       <c r="C564" s="18"/>
@@ -22263,7 +22266,7 @@
       <c r="H564" s="18"/>
       <c r="I564" s="18"/>
     </row>
-    <row r="565" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A565" s="20"/>
       <c r="B565" s="18"/>
       <c r="C565" s="18"/>
@@ -22276,7 +22279,7 @@
       <c r="H565" s="18"/>
       <c r="I565" s="18"/>
     </row>
-    <row r="566" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A566" s="20"/>
       <c r="B566" s="18"/>
       <c r="C566" s="18"/>
@@ -22289,7 +22292,7 @@
       <c r="H566" s="18"/>
       <c r="I566" s="18"/>
     </row>
-    <row r="567" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A567" s="20"/>
       <c r="B567" s="18"/>
       <c r="C567" s="18"/>
@@ -22302,7 +22305,7 @@
       <c r="H567" s="18"/>
       <c r="I567" s="18"/>
     </row>
-    <row r="568" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A568" s="20"/>
       <c r="B568" s="18"/>
       <c r="C568" s="18"/>
@@ -22315,7 +22318,7 @@
       <c r="H568" s="18"/>
       <c r="I568" s="18"/>
     </row>
-    <row r="569" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A569" s="20"/>
       <c r="B569" s="18"/>
       <c r="C569" s="18"/>
@@ -22328,7 +22331,7 @@
       <c r="H569" s="18"/>
       <c r="I569" s="18"/>
     </row>
-    <row r="570" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A570" s="20"/>
       <c r="B570" s="18"/>
       <c r="C570" s="18"/>
@@ -22341,7 +22344,7 @@
       <c r="H570" s="18"/>
       <c r="I570" s="18"/>
     </row>
-    <row r="571" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A571" s="20"/>
       <c r="B571" s="18"/>
       <c r="C571" s="18"/>
@@ -22354,7 +22357,7 @@
       <c r="H571" s="18"/>
       <c r="I571" s="18"/>
     </row>
-    <row r="572" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A572" s="20"/>
       <c r="B572" s="18"/>
       <c r="C572" s="18"/>
@@ -22367,7 +22370,7 @@
       <c r="H572" s="18"/>
       <c r="I572" s="18"/>
     </row>
-    <row r="573" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A573" s="20"/>
       <c r="B573" s="18"/>
       <c r="C573" s="18"/>
@@ -22380,7 +22383,7 @@
       <c r="H573" s="18"/>
       <c r="I573" s="18"/>
     </row>
-    <row r="574" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A574" s="20"/>
       <c r="B574" s="18"/>
       <c r="C574" s="18"/>
@@ -22393,7 +22396,7 @@
       <c r="H574" s="18"/>
       <c r="I574" s="18"/>
     </row>
-    <row r="575" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A575" s="20"/>
       <c r="B575" s="18"/>
       <c r="C575" s="18"/>
@@ -22406,7 +22409,7 @@
       <c r="H575" s="18"/>
       <c r="I575" s="18"/>
     </row>
-    <row r="576" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A576" s="20"/>
       <c r="B576" s="18"/>
       <c r="C576" s="18"/>
@@ -22419,7 +22422,7 @@
       <c r="H576" s="18"/>
       <c r="I576" s="18"/>
     </row>
-    <row r="577" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A577" s="20"/>
       <c r="B577" s="18"/>
       <c r="C577" s="18"/>
@@ -22432,7 +22435,7 @@
       <c r="H577" s="18"/>
       <c r="I577" s="18"/>
     </row>
-    <row r="578" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A578" s="20"/>
       <c r="B578" s="18"/>
       <c r="C578" s="18"/>
@@ -22445,7 +22448,7 @@
       <c r="H578" s="18"/>
       <c r="I578" s="18"/>
     </row>
-    <row r="579" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A579" s="20"/>
       <c r="B579" s="18"/>
       <c r="C579" s="18"/>
@@ -22458,7 +22461,7 @@
       <c r="H579" s="18"/>
       <c r="I579" s="18"/>
     </row>
-    <row r="580" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A580" s="20"/>
       <c r="B580" s="18"/>
       <c r="C580" s="18"/>
@@ -22471,7 +22474,7 @@
       <c r="H580" s="18"/>
       <c r="I580" s="18"/>
     </row>
-    <row r="581" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A581" s="20"/>
       <c r="B581" s="18"/>
       <c r="C581" s="18"/>
@@ -22484,7 +22487,7 @@
       <c r="H581" s="18"/>
       <c r="I581" s="18"/>
     </row>
-    <row r="582" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A582" s="20"/>
       <c r="B582" s="18"/>
       <c r="C582" s="18"/>
@@ -22497,7 +22500,7 @@
       <c r="H582" s="18"/>
       <c r="I582" s="18"/>
     </row>
-    <row r="583" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A583" s="20"/>
       <c r="B583" s="18"/>
       <c r="C583" s="18"/>
@@ -22510,7 +22513,7 @@
       <c r="H583" s="18"/>
       <c r="I583" s="18"/>
     </row>
-    <row r="584" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A584" s="20"/>
       <c r="B584" s="18"/>
       <c r="C584" s="18"/>
@@ -22523,7 +22526,7 @@
       <c r="H584" s="18"/>
       <c r="I584" s="18"/>
     </row>
-    <row r="585" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A585" s="20"/>
       <c r="B585" s="18"/>
       <c r="C585" s="18"/>
@@ -22536,7 +22539,7 @@
       <c r="H585" s="18"/>
       <c r="I585" s="18"/>
     </row>
-    <row r="586" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A586" s="20"/>
       <c r="B586" s="18"/>
       <c r="C586" s="18"/>
@@ -22549,7 +22552,7 @@
       <c r="H586" s="18"/>
       <c r="I586" s="18"/>
     </row>
-    <row r="587" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A587" s="20"/>
       <c r="B587" s="18"/>
       <c r="C587" s="18"/>
@@ -22562,7 +22565,7 @@
       <c r="H587" s="18"/>
       <c r="I587" s="18"/>
     </row>
-    <row r="588" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A588" s="20"/>
       <c r="B588" s="18"/>
       <c r="C588" s="18"/>
@@ -22575,7 +22578,7 @@
       <c r="H588" s="18"/>
       <c r="I588" s="18"/>
     </row>
-    <row r="589" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A589" s="20"/>
       <c r="B589" s="18"/>
       <c r="C589" s="18"/>
@@ -22588,7 +22591,7 @@
       <c r="H589" s="18"/>
       <c r="I589" s="18"/>
     </row>
-    <row r="590" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A590" s="20"/>
       <c r="B590" s="18"/>
       <c r="C590" s="18"/>
@@ -22601,7 +22604,7 @@
       <c r="H590" s="18"/>
       <c r="I590" s="18"/>
     </row>
-    <row r="591" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A591" s="20"/>
       <c r="B591" s="18"/>
       <c r="C591" s="18"/>
@@ -22614,7 +22617,7 @@
       <c r="H591" s="18"/>
       <c r="I591" s="18"/>
     </row>
-    <row r="592" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A592" s="20"/>
       <c r="B592" s="18"/>
       <c r="C592" s="18"/>
@@ -22627,7 +22630,7 @@
       <c r="H592" s="18"/>
       <c r="I592" s="18"/>
     </row>
-    <row r="593" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A593" s="20"/>
       <c r="B593" s="18"/>
       <c r="C593" s="18"/>
@@ -22640,7 +22643,7 @@
       <c r="H593" s="18"/>
       <c r="I593" s="18"/>
     </row>
-    <row r="594" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A594" s="20"/>
       <c r="B594" s="18"/>
       <c r="C594" s="18"/>
@@ -22653,7 +22656,7 @@
       <c r="H594" s="18"/>
       <c r="I594" s="18"/>
     </row>
-    <row r="595" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A595" s="20"/>
       <c r="B595" s="18"/>
       <c r="C595" s="18"/>
@@ -22666,7 +22669,7 @@
       <c r="H595" s="18"/>
       <c r="I595" s="18"/>
     </row>
-    <row r="596" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A596" s="20"/>
       <c r="B596" s="18"/>
       <c r="C596" s="18"/>
@@ -22679,7 +22682,7 @@
       <c r="H596" s="18"/>
       <c r="I596" s="18"/>
     </row>
-    <row r="597" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A597" s="20"/>
       <c r="B597" s="18"/>
       <c r="C597" s="18"/>
@@ -22692,7 +22695,7 @@
       <c r="H597" s="18"/>
       <c r="I597" s="18"/>
     </row>
-    <row r="598" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A598" s="20"/>
       <c r="B598" s="18"/>
       <c r="C598" s="18"/>
@@ -22705,7 +22708,7 @@
       <c r="H598" s="18"/>
       <c r="I598" s="18"/>
     </row>
-    <row r="599" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A599" s="20"/>
       <c r="B599" s="18"/>
       <c r="C599" s="18"/>
@@ -22718,7 +22721,7 @@
       <c r="H599" s="18"/>
       <c r="I599" s="18"/>
     </row>
-    <row r="600" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A600" s="20"/>
       <c r="B600" s="18"/>
       <c r="C600" s="18"/>
@@ -22737,11 +22740,11 @@
       </c>
       <c r="B601" s="33">
         <f>SUBTOTAL(103,Tabela5[LOCAL])</f>
-        <v>478</v>
+        <v>80</v>
       </c>
       <c r="C601" s="33">
         <f>SUBTOTAL(103,Tabela5[ENCARREGADO OU LIDER DE EQUIPE])</f>
-        <v>478</v>
+        <v>80</v>
       </c>
       <c r="D601" s="33">
         <f>SUM(D2:D600)</f>
@@ -22749,20 +22752,20 @@
       </c>
       <c r="E601" s="33">
         <f>SUBTOTAL(103,Tabela5[DESCRIÇÃO])</f>
-        <v>478</v>
+        <v>80</v>
       </c>
       <c r="F601" s="33"/>
       <c r="G601" s="33">
         <f>SUBTOTAL(103,Tabela5[CLASSIFICAÇÃO])</f>
-        <v>478</v>
+        <v>80</v>
       </c>
       <c r="H601" s="33">
         <f>SUBTOTAL(109,Tabela5[QUANTIDADE INSPEÇÕES])</f>
-        <v>478</v>
+        <v>80</v>
       </c>
       <c r="I601" s="33">
         <f>SUBTOTAL(103,Tabela5[TÉCNICO DE SEGURANÇA  APLICADOR])</f>
-        <v>478</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -22808,92 +22811,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="89" t="s">
         <v>808</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
+      <c r="B1" s="89"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="89"/>
+      <c r="I1" s="89"/>
     </row>
     <row r="2" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="85" t="s">
+      <c r="A2" s="79" t="s">
         <v>809</v>
       </c>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
       <c r="F2" s="40" t="s">
         <v>824</v>
       </c>
-      <c r="G2" s="85" t="s">
+      <c r="G2" s="79" t="s">
         <v>820</v>
       </c>
-      <c r="H2" s="85"/>
+      <c r="H2" s="79"/>
       <c r="I2" s="34" t="s">
         <v>822</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="85" t="s">
+      <c r="A3" s="79" t="s">
         <v>810</v>
       </c>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="85"/>
-      <c r="E3" s="85"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
       <c r="F3" s="40" t="s">
         <v>823</v>
       </c>
-      <c r="G3" s="85" t="s">
+      <c r="G3" s="79" t="s">
         <v>821</v>
       </c>
-      <c r="H3" s="85"/>
+      <c r="H3" s="79"/>
       <c r="I3" s="22"/>
     </row>
     <row r="4" spans="1:9" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="82" t="s">
+      <c r="A4" s="110" t="s">
         <v>819</v>
       </c>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
+      <c r="B4" s="111"/>
+      <c r="C4" s="111"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="79" t="s">
+      <c r="A5" s="107" t="s">
         <v>811</v>
       </c>
-      <c r="B5" s="80"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="81"/>
+      <c r="B5" s="108"/>
+      <c r="C5" s="108"/>
+      <c r="D5" s="108"/>
+      <c r="E5" s="108"/>
+      <c r="F5" s="108"/>
+      <c r="G5" s="108"/>
+      <c r="H5" s="108"/>
+      <c r="I5" s="109"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="76" t="s">
+      <c r="A6" s="104" t="s">
         <v>812</v>
       </c>
-      <c r="B6" s="77"/>
-      <c r="C6" s="77"/>
-      <c r="D6" s="77"/>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77"/>
-      <c r="H6" s="77"/>
-      <c r="I6" s="78"/>
+      <c r="B6" s="105"/>
+      <c r="C6" s="105"/>
+      <c r="D6" s="105"/>
+      <c r="E6" s="105"/>
+      <c r="F6" s="105"/>
+      <c r="G6" s="105"/>
+      <c r="H6" s="105"/>
+      <c r="I6" s="106"/>
     </row>
     <row r="7" spans="1:9" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="53"/>
@@ -22934,16 +22937,16 @@
       <c r="I9" s="39"/>
     </row>
     <row r="10" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="86" t="s">
+      <c r="A10" s="100" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="86"/>
-      <c r="C10" s="86"/>
-      <c r="D10" s="86" t="s">
+      <c r="B10" s="100"/>
+      <c r="C10" s="100"/>
+      <c r="D10" s="100" t="s">
         <v>832</v>
       </c>
-      <c r="E10" s="86"/>
-      <c r="F10" s="86"/>
+      <c r="E10" s="100"/>
+      <c r="F10" s="100"/>
       <c r="G10" s="19" t="s">
         <v>641</v>
       </c>
@@ -23033,11 +23036,11 @@
       <c r="F16" s="48" t="s">
         <v>674</v>
       </c>
-      <c r="G16" s="86" t="s">
+      <c r="G16" s="100" t="s">
         <v>619</v>
       </c>
-      <c r="H16" s="86"/>
-      <c r="I16" s="86"/>
+      <c r="H16" s="100"/>
+      <c r="I16" s="100"/>
     </row>
     <row r="17" spans="1:9" ht="4.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="60"/>
@@ -23199,11 +23202,11 @@
       <c r="I27" s="61"/>
     </row>
     <row r="28" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="86" t="s">
+      <c r="A28" s="100" t="s">
         <v>831</v>
       </c>
-      <c r="B28" s="86"/>
-      <c r="C28" s="86"/>
+      <c r="B28" s="100"/>
+      <c r="C28" s="100"/>
       <c r="D28" s="46" t="s">
         <v>833</v>
       </c>
@@ -23266,11 +23269,11 @@
       <c r="F32" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="G32" s="86" t="s">
+      <c r="G32" s="100" t="s">
         <v>834</v>
       </c>
-      <c r="H32" s="86"/>
-      <c r="I32" s="86"/>
+      <c r="H32" s="100"/>
+      <c r="I32" s="100"/>
     </row>
     <row r="33" spans="1:9" ht="4.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="60"/>
@@ -23345,11 +23348,11 @@
       <c r="C38" s="48" t="s">
         <v>649</v>
       </c>
-      <c r="D38" s="86" t="s">
+      <c r="D38" s="100" t="s">
         <v>618</v>
       </c>
-      <c r="E38" s="86"/>
-      <c r="F38" s="86"/>
+      <c r="E38" s="100"/>
+      <c r="F38" s="100"/>
       <c r="G38" s="19" t="s">
         <v>642</v>
       </c>
@@ -23415,95 +23418,95 @@
       <c r="I43" s="39"/>
     </row>
     <row r="44" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="87" t="s">
+      <c r="A44" s="101" t="s">
         <v>846</v>
       </c>
-      <c r="B44" s="88"/>
-      <c r="C44" s="88"/>
-      <c r="D44" s="88"/>
-      <c r="E44" s="88"/>
-      <c r="F44" s="88"/>
-      <c r="G44" s="88"/>
-      <c r="H44" s="88"/>
-      <c r="I44" s="89"/>
+      <c r="B44" s="102"/>
+      <c r="C44" s="102"/>
+      <c r="D44" s="102"/>
+      <c r="E44" s="102"/>
+      <c r="F44" s="102"/>
+      <c r="G44" s="102"/>
+      <c r="H44" s="102"/>
+      <c r="I44" s="103"/>
     </row>
     <row r="45" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="90" t="s">
+      <c r="A45" s="95" t="s">
         <v>847</v>
       </c>
-      <c r="B45" s="91"/>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
-      <c r="F45" s="91"/>
-      <c r="G45" s="91"/>
-      <c r="H45" s="91"/>
-      <c r="I45" s="92"/>
+      <c r="B45" s="96"/>
+      <c r="C45" s="96"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
+      <c r="F45" s="96"/>
+      <c r="G45" s="96"/>
+      <c r="H45" s="96"/>
+      <c r="I45" s="97"/>
     </row>
     <row r="46" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="93" t="s">
+      <c r="A46" s="98" t="s">
         <v>848</v>
       </c>
-      <c r="B46" s="93"/>
-      <c r="C46" s="93"/>
-      <c r="D46" s="93"/>
-      <c r="E46" s="93"/>
-      <c r="F46" s="93"/>
-      <c r="G46" s="93"/>
-      <c r="H46" s="93"/>
-      <c r="I46" s="93"/>
+      <c r="B46" s="98"/>
+      <c r="C46" s="98"/>
+      <c r="D46" s="98"/>
+      <c r="E46" s="98"/>
+      <c r="F46" s="98"/>
+      <c r="G46" s="98"/>
+      <c r="H46" s="98"/>
+      <c r="I46" s="98"/>
     </row>
     <row r="47" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="94"/>
-      <c r="B47" s="94"/>
-      <c r="C47" s="94"/>
-      <c r="D47" s="94"/>
-      <c r="E47" s="94"/>
-      <c r="F47" s="94"/>
-      <c r="G47" s="94"/>
-      <c r="H47" s="94"/>
-      <c r="I47" s="94"/>
+      <c r="A47" s="99"/>
+      <c r="B47" s="99"/>
+      <c r="C47" s="99"/>
+      <c r="D47" s="99"/>
+      <c r="E47" s="99"/>
+      <c r="F47" s="99"/>
+      <c r="G47" s="99"/>
+      <c r="H47" s="99"/>
+      <c r="I47" s="99"/>
     </row>
     <row r="48" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="94"/>
-      <c r="B48" s="94"/>
-      <c r="C48" s="94"/>
-      <c r="D48" s="94"/>
-      <c r="E48" s="94"/>
-      <c r="F48" s="94"/>
-      <c r="G48" s="94"/>
-      <c r="H48" s="94"/>
-      <c r="I48" s="94"/>
+      <c r="A48" s="99"/>
+      <c r="B48" s="99"/>
+      <c r="C48" s="99"/>
+      <c r="D48" s="99"/>
+      <c r="E48" s="99"/>
+      <c r="F48" s="99"/>
+      <c r="G48" s="99"/>
+      <c r="H48" s="99"/>
+      <c r="I48" s="99"/>
     </row>
     <row r="49" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="101" t="s">
+      <c r="A49" s="92" t="s">
         <v>849</v>
       </c>
-      <c r="B49" s="101"/>
-      <c r="C49" s="101"/>
-      <c r="D49" s="101"/>
-      <c r="E49" s="101"/>
-      <c r="F49" s="101" t="s">
+      <c r="B49" s="92"/>
+      <c r="C49" s="92"/>
+      <c r="D49" s="92"/>
+      <c r="E49" s="92"/>
+      <c r="F49" s="92" t="s">
         <v>850</v>
       </c>
-      <c r="G49" s="101"/>
-      <c r="H49" s="101"/>
-      <c r="I49" s="101"/>
+      <c r="G49" s="92"/>
+      <c r="H49" s="92"/>
+      <c r="I49" s="92"/>
     </row>
     <row r="50" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>851</v>
       </c>
       <c r="B50" s="22"/>
-      <c r="C50" s="97"/>
-      <c r="D50" s="98"/>
-      <c r="E50" s="98"/>
-      <c r="F50" s="102" t="s">
+      <c r="C50" s="76"/>
+      <c r="D50" s="77"/>
+      <c r="E50" s="77"/>
+      <c r="F50" s="93" t="s">
         <v>851</v>
       </c>
-      <c r="G50" s="102"/>
-      <c r="H50" s="102"/>
-      <c r="I50" s="103"/>
+      <c r="G50" s="93"/>
+      <c r="H50" s="93"/>
+      <c r="I50" s="94"/>
     </row>
     <row r="51" spans="1:9" ht="4.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4"/>
@@ -23517,15 +23520,15 @@
         <v>851</v>
       </c>
       <c r="B52" s="22"/>
-      <c r="C52" s="99"/>
-      <c r="D52" s="100"/>
-      <c r="E52" s="100"/>
-      <c r="F52" s="95" t="s">
+      <c r="C52" s="80"/>
+      <c r="D52" s="81"/>
+      <c r="E52" s="81"/>
+      <c r="F52" s="90" t="s">
         <v>851</v>
       </c>
-      <c r="G52" s="95"/>
-      <c r="H52" s="95"/>
-      <c r="I52" s="96"/>
+      <c r="G52" s="90"/>
+      <c r="H52" s="90"/>
+      <c r="I52" s="91"/>
     </row>
     <row r="53" spans="1:9" ht="4.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4"/>
@@ -23539,15 +23542,15 @@
         <v>851</v>
       </c>
       <c r="B54" s="22"/>
-      <c r="C54" s="99"/>
-      <c r="D54" s="100"/>
-      <c r="E54" s="100"/>
-      <c r="F54" s="95" t="s">
+      <c r="C54" s="80"/>
+      <c r="D54" s="81"/>
+      <c r="E54" s="81"/>
+      <c r="F54" s="90" t="s">
         <v>851</v>
       </c>
-      <c r="G54" s="95"/>
-      <c r="H54" s="95"/>
-      <c r="I54" s="96"/>
+      <c r="G54" s="90"/>
+      <c r="H54" s="90"/>
+      <c r="I54" s="91"/>
     </row>
     <row r="55" spans="1:9" ht="4.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4"/>
@@ -23561,15 +23564,15 @@
         <v>851</v>
       </c>
       <c r="B56" s="22"/>
-      <c r="C56" s="99"/>
-      <c r="D56" s="100"/>
-      <c r="E56" s="100"/>
-      <c r="F56" s="95" t="s">
+      <c r="C56" s="80"/>
+      <c r="D56" s="81"/>
+      <c r="E56" s="81"/>
+      <c r="F56" s="90" t="s">
         <v>851</v>
       </c>
-      <c r="G56" s="95"/>
-      <c r="H56" s="95"/>
-      <c r="I56" s="96"/>
+      <c r="G56" s="90"/>
+      <c r="H56" s="90"/>
+      <c r="I56" s="91"/>
     </row>
     <row r="57" spans="1:9" ht="4.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4"/>
@@ -23583,15 +23586,15 @@
         <v>851</v>
       </c>
       <c r="B58" s="22"/>
-      <c r="C58" s="99"/>
-      <c r="D58" s="100"/>
-      <c r="E58" s="100"/>
-      <c r="F58" s="95" t="s">
+      <c r="C58" s="80"/>
+      <c r="D58" s="81"/>
+      <c r="E58" s="81"/>
+      <c r="F58" s="90" t="s">
         <v>851</v>
       </c>
-      <c r="G58" s="95"/>
-      <c r="H58" s="95"/>
-      <c r="I58" s="96"/>
+      <c r="G58" s="90"/>
+      <c r="H58" s="90"/>
+      <c r="I58" s="91"/>
     </row>
     <row r="59" spans="1:9" ht="4.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4"/>
@@ -23605,32 +23608,32 @@
         <v>851</v>
       </c>
       <c r="B60" s="22"/>
-      <c r="C60" s="99"/>
-      <c r="D60" s="100"/>
-      <c r="E60" s="100"/>
-      <c r="F60" s="95" t="s">
+      <c r="C60" s="80"/>
+      <c r="D60" s="81"/>
+      <c r="E60" s="81"/>
+      <c r="F60" s="90" t="s">
         <v>851</v>
       </c>
-      <c r="G60" s="95"/>
-      <c r="H60" s="95"/>
-      <c r="I60" s="96"/>
+      <c r="G60" s="90"/>
+      <c r="H60" s="90"/>
+      <c r="I60" s="91"/>
     </row>
     <row r="61" spans="1:9" ht="4.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="57"/>
       <c r="I61" s="39"/>
     </row>
     <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="101" t="s">
+      <c r="A62" s="92" t="s">
         <v>852</v>
       </c>
-      <c r="B62" s="101"/>
-      <c r="C62" s="101"/>
-      <c r="D62" s="101"/>
-      <c r="E62" s="101"/>
-      <c r="F62" s="101"/>
-      <c r="G62" s="101"/>
-      <c r="H62" s="101"/>
-      <c r="I62" s="101"/>
+      <c r="B62" s="92"/>
+      <c r="C62" s="92"/>
+      <c r="D62" s="92"/>
+      <c r="E62" s="92"/>
+      <c r="F62" s="92"/>
+      <c r="G62" s="92"/>
+      <c r="H62" s="92"/>
+      <c r="I62" s="92"/>
     </row>
     <row r="63" spans="1:9" ht="3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="57"/>
@@ -23641,9 +23644,9 @@
         <v>851</v>
       </c>
       <c r="B64" s="22"/>
-      <c r="C64" s="99"/>
-      <c r="D64" s="100"/>
-      <c r="E64" s="100"/>
+      <c r="C64" s="80"/>
+      <c r="D64" s="81"/>
+      <c r="E64" s="81"/>
       <c r="F64" s="50" t="s">
         <v>851</v>
       </c>
@@ -23659,9 +23662,9 @@
         <v>851</v>
       </c>
       <c r="B66" s="22"/>
-      <c r="C66" s="99"/>
-      <c r="D66" s="100"/>
-      <c r="E66" s="100"/>
+      <c r="C66" s="80"/>
+      <c r="D66" s="81"/>
+      <c r="E66" s="81"/>
       <c r="F66" s="50" t="s">
         <v>851</v>
       </c>
@@ -23677,9 +23680,9 @@
         <v>851</v>
       </c>
       <c r="B68" s="22"/>
-      <c r="C68" s="99"/>
-      <c r="D68" s="100"/>
-      <c r="E68" s="100"/>
+      <c r="C68" s="80"/>
+      <c r="D68" s="81"/>
+      <c r="E68" s="81"/>
       <c r="F68" s="50" t="s">
         <v>851</v>
       </c>
@@ -23690,100 +23693,100 @@
       <c r="I69" s="39"/>
     </row>
     <row r="70" spans="1:9" ht="1.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="104" t="s">
+      <c r="A70" s="82" t="s">
         <v>853</v>
       </c>
-      <c r="B70" s="105"/>
-      <c r="C70" s="105"/>
-      <c r="D70" s="105"/>
-      <c r="E70" s="105"/>
-      <c r="F70" s="105"/>
-      <c r="G70" s="105"/>
-      <c r="H70" s="105"/>
-      <c r="I70" s="106"/>
+      <c r="B70" s="83"/>
+      <c r="C70" s="83"/>
+      <c r="D70" s="83"/>
+      <c r="E70" s="83"/>
+      <c r="F70" s="83"/>
+      <c r="G70" s="83"/>
+      <c r="H70" s="83"/>
+      <c r="I70" s="84"/>
     </row>
     <row r="71" spans="1:9" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="107"/>
-      <c r="B71" s="105"/>
-      <c r="C71" s="105"/>
-      <c r="D71" s="105"/>
-      <c r="E71" s="105"/>
-      <c r="F71" s="105"/>
-      <c r="G71" s="105"/>
-      <c r="H71" s="105"/>
-      <c r="I71" s="106"/>
+      <c r="A71" s="85"/>
+      <c r="B71" s="83"/>
+      <c r="C71" s="83"/>
+      <c r="D71" s="83"/>
+      <c r="E71" s="83"/>
+      <c r="F71" s="83"/>
+      <c r="G71" s="83"/>
+      <c r="H71" s="83"/>
+      <c r="I71" s="84"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A72" s="108"/>
-      <c r="B72" s="109"/>
-      <c r="C72" s="109"/>
-      <c r="D72" s="109"/>
-      <c r="E72" s="109"/>
-      <c r="F72" s="109"/>
-      <c r="G72" s="109"/>
-      <c r="H72" s="109"/>
-      <c r="I72" s="110"/>
+      <c r="A72" s="86"/>
+      <c r="B72" s="87"/>
+      <c r="C72" s="87"/>
+      <c r="D72" s="87"/>
+      <c r="E72" s="87"/>
+      <c r="F72" s="87"/>
+      <c r="G72" s="87"/>
+      <c r="H72" s="87"/>
+      <c r="I72" s="88"/>
     </row>
     <row r="73" spans="1:9" ht="5.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="74" spans="1:9" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="84" t="s">
+      <c r="A74" s="89" t="s">
         <v>808</v>
       </c>
-      <c r="B74" s="84"/>
-      <c r="C74" s="84"/>
-      <c r="D74" s="84"/>
-      <c r="E74" s="84"/>
-      <c r="F74" s="84"/>
-      <c r="G74" s="84"/>
-      <c r="H74" s="84"/>
-      <c r="I74" s="84"/>
+      <c r="B74" s="89"/>
+      <c r="C74" s="89"/>
+      <c r="D74" s="89"/>
+      <c r="E74" s="89"/>
+      <c r="F74" s="89"/>
+      <c r="G74" s="89"/>
+      <c r="H74" s="89"/>
+      <c r="I74" s="89"/>
     </row>
     <row r="75" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="85" t="s">
+      <c r="A75" s="79" t="s">
         <v>809</v>
       </c>
-      <c r="B75" s="85"/>
-      <c r="C75" s="85"/>
-      <c r="D75" s="85"/>
-      <c r="E75" s="85"/>
+      <c r="B75" s="79"/>
+      <c r="C75" s="79"/>
+      <c r="D75" s="79"/>
+      <c r="E75" s="79"/>
       <c r="F75" s="40" t="s">
         <v>824</v>
       </c>
-      <c r="G75" s="85" t="s">
+      <c r="G75" s="79" t="s">
         <v>820</v>
       </c>
-      <c r="H75" s="85"/>
+      <c r="H75" s="79"/>
       <c r="I75" s="34" t="s">
         <v>822</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="85" t="s">
+      <c r="A76" s="79" t="s">
         <v>810</v>
       </c>
-      <c r="B76" s="85"/>
-      <c r="C76" s="85"/>
-      <c r="D76" s="85"/>
-      <c r="E76" s="85"/>
+      <c r="B76" s="79"/>
+      <c r="C76" s="79"/>
+      <c r="D76" s="79"/>
+      <c r="E76" s="79"/>
       <c r="F76" s="40" t="s">
         <v>823</v>
       </c>
-      <c r="G76" s="85" t="s">
+      <c r="G76" s="79" t="s">
         <v>821</v>
       </c>
-      <c r="H76" s="85"/>
+      <c r="H76" s="79"/>
       <c r="I76" s="22"/>
     </row>
     <row r="77" spans="1:9" ht="282.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="97"/>
-      <c r="B77" s="98"/>
-      <c r="C77" s="98"/>
-      <c r="D77" s="98"/>
-      <c r="E77" s="111"/>
-      <c r="F77" s="98"/>
-      <c r="G77" s="98"/>
-      <c r="H77" s="98"/>
-      <c r="I77" s="111"/>
+      <c r="A77" s="76"/>
+      <c r="B77" s="77"/>
+      <c r="C77" s="77"/>
+      <c r="D77" s="77"/>
+      <c r="E77" s="78"/>
+      <c r="F77" s="77"/>
+      <c r="G77" s="77"/>
+      <c r="H77" s="77"/>
+      <c r="I77" s="78"/>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" s="63" t="s">
@@ -23799,15 +23802,15 @@
       <c r="I78" s="39"/>
     </row>
     <row r="79" spans="1:9" ht="282.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="97"/>
-      <c r="B79" s="98"/>
-      <c r="C79" s="98"/>
-      <c r="D79" s="98"/>
-      <c r="E79" s="111"/>
-      <c r="F79" s="98"/>
-      <c r="G79" s="98"/>
-      <c r="H79" s="98"/>
-      <c r="I79" s="111"/>
+      <c r="A79" s="76"/>
+      <c r="B79" s="77"/>
+      <c r="C79" s="77"/>
+      <c r="D79" s="77"/>
+      <c r="E79" s="78"/>
+      <c r="F79" s="77"/>
+      <c r="G79" s="77"/>
+      <c r="H79" s="77"/>
+      <c r="I79" s="78"/>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" s="63" t="s">
@@ -23823,15 +23826,15 @@
       <c r="I80" s="39"/>
     </row>
     <row r="81" spans="1:9" ht="282.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="97"/>
-      <c r="B81" s="98"/>
-      <c r="C81" s="98"/>
-      <c r="D81" s="98"/>
-      <c r="E81" s="111"/>
-      <c r="F81" s="98"/>
-      <c r="G81" s="98"/>
-      <c r="H81" s="98"/>
-      <c r="I81" s="111"/>
+      <c r="A81" s="76"/>
+      <c r="B81" s="77"/>
+      <c r="C81" s="77"/>
+      <c r="D81" s="77"/>
+      <c r="E81" s="78"/>
+      <c r="F81" s="77"/>
+      <c r="G81" s="77"/>
+      <c r="H81" s="77"/>
+      <c r="I81" s="78"/>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" s="63" t="s">
@@ -23850,12 +23853,40 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="A77:E77"/>
-    <mergeCell ref="F77:I77"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="F79:I79"/>
-    <mergeCell ref="A81:E81"/>
-    <mergeCell ref="F81:I81"/>
+    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A44:I44"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="A45:I45"/>
+    <mergeCell ref="A46:I46"/>
+    <mergeCell ref="A47:I47"/>
+    <mergeCell ref="A48:I48"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="F56:I56"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="F49:I49"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="F52:I52"/>
+    <mergeCell ref="F54:I54"/>
+    <mergeCell ref="F58:I58"/>
+    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="A62:I62"/>
+    <mergeCell ref="C58:E58"/>
+    <mergeCell ref="C60:E60"/>
     <mergeCell ref="A75:E75"/>
     <mergeCell ref="G75:H75"/>
     <mergeCell ref="A76:E76"/>
@@ -23865,40 +23896,12 @@
     <mergeCell ref="C68:E68"/>
     <mergeCell ref="A70:I72"/>
     <mergeCell ref="A74:I74"/>
-    <mergeCell ref="F58:I58"/>
-    <mergeCell ref="F60:I60"/>
-    <mergeCell ref="A62:I62"/>
-    <mergeCell ref="C58:E58"/>
-    <mergeCell ref="C60:E60"/>
-    <mergeCell ref="A49:E49"/>
-    <mergeCell ref="F49:I49"/>
-    <mergeCell ref="F50:I50"/>
-    <mergeCell ref="F52:I52"/>
-    <mergeCell ref="F54:I54"/>
-    <mergeCell ref="F56:I56"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="A45:I45"/>
-    <mergeCell ref="A46:I46"/>
-    <mergeCell ref="A47:I47"/>
-    <mergeCell ref="A48:I48"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A44:I44"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="A6:I6"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="F77:I77"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="F79:I79"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="F81:I81"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" scale="73" fitToHeight="0" orientation="portrait" r:id="rId1"/>
@@ -23918,25 +23921,25 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="112" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B1" s="112"/>
       <c r="C1" s="112"/>
     </row>
     <row r="2" spans="1:3" s="19" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A2" s="67" t="s">
+        <v>982</v>
+      </c>
+      <c r="B2" s="67" t="s">
         <v>983</v>
       </c>
-      <c r="B2" s="67" t="s">
+      <c r="C2" s="67" t="s">
         <v>984</v>
-      </c>
-      <c r="C2" s="67" t="s">
-        <v>985</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B3" s="69">
         <v>295</v>
@@ -23947,7 +23950,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B4" s="69">
         <v>260</v>
@@ -23958,7 +23961,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="22" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B5" s="69">
         <v>410</v>
@@ -23969,7 +23972,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B6" s="69">
         <v>196</v>
@@ -23980,7 +23983,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="22" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B7" s="69">
         <v>301</v>
@@ -23991,49 +23994,53 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
-        <v>976</v>
-      </c>
-      <c r="B8" s="69"/>
-      <c r="C8" s="69"/>
+        <v>975</v>
+      </c>
+      <c r="B8" s="69">
+        <v>195</v>
+      </c>
+      <c r="C8" s="69">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="22" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B9" s="69"/>
       <c r="C9" s="69"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B10" s="69"/>
       <c r="C10" s="69"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="22" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B11" s="69"/>
       <c r="C11" s="69"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B12" s="69"/>
       <c r="C12" s="69"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="22" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B13" s="69"/>
       <c r="C13" s="69"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="22" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B14" s="69"/>
       <c r="C14" s="69"/>
@@ -24045,11 +24052,11 @@
       <c r="B15" s="14">
         <f>SUBTOTAL(109,Tabela1[QUANTIDADE
 DDS])</f>
-        <v>1462</v>
+        <v>1657</v>
       </c>
       <c r="C15" s="70">
         <f>SUBTOTAL(109,Tabela1[QUANTIDADE CAMPANHAS])</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="771" ht="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -24535,6 +24542,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100547A52244DFCC9488E5B66DD2EAE55E4" ma:contentTypeVersion="18" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="936731ce312a4e8ead8ad97bcf9b70b3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="84c92d79-736b-434d-a6de-4a5b6bb0f72c" xmlns:ns3="de022bf3-4aff-41f6-a825-e7793343a5a1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fdc18dfd3044d82758640420f33afd2f" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -24790,15 +24806,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -24821,6 +24828,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B012FB3-DD8F-4CAA-8133-13B526BC83FE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A86827D-F12F-464B-8BAA-37C9BCDB40FD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -24840,14 +24855,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B012FB3-DD8F-4CAA-8133-13B526BC83FE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F09844F-2517-46B1-8B13-9F10D5CE2474}">
   <ds:schemaRefs>
